--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="173">
   <si>
     <t>Дата</t>
   </si>
@@ -53,36 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-10</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
   </si>
   <si>
     <t>В0549НТ</t>
@@ -569,8 +539,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -656,11 +627,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -668,9 +640,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1024,20 +996,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46146</v>
       </c>
       <c r="B2">
         <v>1146</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>4.778</v>
@@ -1055,7 +1027,7 @@
         <v>8.6</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1065,20 +1037,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="A3" s="2">
+        <v>46146</v>
       </c>
       <c r="B3">
         <v>1158</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -1096,7 +1068,7 @@
         <v>10.8</v>
       </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1106,20 +1078,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>13</v>
+      <c r="A4" s="2">
+        <v>46146</v>
       </c>
       <c r="B4">
         <v>1158</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F4">
         <v>8.728</v>
@@ -1137,7 +1109,7 @@
         <v>15.71</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1147,20 +1119,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>13</v>
+      <c r="A5" s="2">
+        <v>46146</v>
       </c>
       <c r="B5">
         <v>1158</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F5">
         <v>3.539</v>
@@ -1178,7 +1150,7 @@
         <v>6.37</v>
       </c>
       <c r="K5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1188,20 +1160,20 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>13</v>
+      <c r="A6" s="2">
+        <v>46146</v>
       </c>
       <c r="B6">
         <v>1158</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F6">
         <v>8.978</v>
@@ -1219,7 +1191,7 @@
         <v>16.16</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1229,20 +1201,20 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>13</v>
+      <c r="A7" s="2">
+        <v>46146</v>
       </c>
       <c r="B7">
         <v>1158</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -1260,7 +1232,7 @@
         <v>5.4</v>
       </c>
       <c r="K7" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1270,20 +1242,20 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>13</v>
+      <c r="A8" s="2">
+        <v>46146</v>
       </c>
       <c r="B8">
         <v>1158</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F8">
         <v>35</v>
@@ -1301,7 +1273,7 @@
         <v>63</v>
       </c>
       <c r="K8" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1311,20 +1283,20 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>13</v>
+      <c r="A9" s="2">
+        <v>46146</v>
       </c>
       <c r="B9">
         <v>1158</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F9">
         <v>15</v>
@@ -1342,7 +1314,7 @@
         <v>27</v>
       </c>
       <c r="K9" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1352,20 +1324,20 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>13</v>
+      <c r="A10" s="2">
+        <v>46146</v>
       </c>
       <c r="B10">
         <v>1158</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F10">
         <v>6.778</v>
@@ -1383,7 +1355,7 @@
         <v>12.2</v>
       </c>
       <c r="K10" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1393,20 +1365,20 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>13</v>
+      <c r="A11" s="2">
+        <v>46146</v>
       </c>
       <c r="B11">
         <v>1911</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F11">
         <v>27.807</v>
@@ -1424,7 +1396,7 @@
         <v>23.08</v>
       </c>
       <c r="K11" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1434,20 +1406,20 @@
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>14</v>
+      <c r="A12" s="2">
+        <v>46147</v>
       </c>
       <c r="B12">
         <v>1146</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F12">
         <v>4.839</v>
@@ -1465,7 +1437,7 @@
         <v>8.710000000000001</v>
       </c>
       <c r="K12" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1475,20 +1447,20 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>14</v>
+      <c r="A13" s="2">
+        <v>46147</v>
       </c>
       <c r="B13">
         <v>1147</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F13">
         <v>29</v>
@@ -1506,7 +1478,7 @@
         <v>52.2</v>
       </c>
       <c r="K13" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1516,20 +1488,20 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>14</v>
+      <c r="A14" s="2">
+        <v>46147</v>
       </c>
       <c r="B14">
         <v>1158</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F14">
         <v>10.761</v>
@@ -1547,7 +1519,7 @@
         <v>19.37</v>
       </c>
       <c r="K14" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1557,20 +1529,20 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>14</v>
+      <c r="A15" s="2">
+        <v>46147</v>
       </c>
       <c r="B15">
         <v>1158</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F15">
         <v>7.161</v>
@@ -1588,7 +1560,7 @@
         <v>12.89</v>
       </c>
       <c r="K15" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1598,20 +1570,20 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>14</v>
+      <c r="A16" s="2">
+        <v>46147</v>
       </c>
       <c r="B16">
         <v>1158</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F16">
         <v>5.911</v>
@@ -1629,7 +1601,7 @@
         <v>10.64</v>
       </c>
       <c r="K16" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1639,20 +1611,20 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>14</v>
+      <c r="A17" s="2">
+        <v>46147</v>
       </c>
       <c r="B17">
         <v>1158</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -1670,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="K17" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1680,20 +1652,20 @@
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>14</v>
+      <c r="A18" s="2">
+        <v>46147</v>
       </c>
       <c r="B18">
         <v>1158</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F18">
         <v>24</v>
@@ -1711,7 +1683,7 @@
         <v>43.2</v>
       </c>
       <c r="K18" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1721,20 +1693,20 @@
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" t="s">
-        <v>14</v>
+      <c r="A19" s="2">
+        <v>46147</v>
       </c>
       <c r="B19">
         <v>1158</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F19">
         <v>9.300000000000001</v>
@@ -1752,7 +1724,7 @@
         <v>16.74</v>
       </c>
       <c r="K19" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1762,20 +1734,20 @@
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>14</v>
+      <c r="A20" s="2">
+        <v>46147</v>
       </c>
       <c r="B20">
         <v>1158</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F20">
         <v>9.010999999999999</v>
@@ -1793,7 +1765,7 @@
         <v>16.22</v>
       </c>
       <c r="K20" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1803,20 +1775,20 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>14</v>
+      <c r="A21" s="2">
+        <v>46147</v>
       </c>
       <c r="B21">
         <v>1158</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F21">
         <v>9</v>
@@ -1834,7 +1806,7 @@
         <v>16.2</v>
       </c>
       <c r="K21" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1844,20 +1816,20 @@
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" t="s">
-        <v>15</v>
+      <c r="A22" s="2">
+        <v>46149</v>
       </c>
       <c r="B22">
         <v>1146</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F22">
         <v>3.522</v>
@@ -1875,7 +1847,7 @@
         <v>6.34</v>
       </c>
       <c r="K22" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1885,20 +1857,20 @@
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" t="s">
-        <v>15</v>
+      <c r="A23" s="2">
+        <v>46149</v>
       </c>
       <c r="B23">
         <v>1148</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F23">
         <v>13.75</v>
@@ -1916,7 +1888,7 @@
         <v>24.75</v>
       </c>
       <c r="K23" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1926,20 +1898,20 @@
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" t="s">
-        <v>15</v>
+      <c r="A24" s="2">
+        <v>46149</v>
       </c>
       <c r="B24">
         <v>1148</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F24">
         <v>15.7</v>
@@ -1957,7 +1929,7 @@
         <v>28.26</v>
       </c>
       <c r="K24" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1967,20 +1939,20 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" t="s">
-        <v>15</v>
+      <c r="A25" s="2">
+        <v>46149</v>
       </c>
       <c r="B25">
         <v>1148</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F25">
         <v>6</v>
@@ -1998,7 +1970,7 @@
         <v>10.8</v>
       </c>
       <c r="K25" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2008,20 +1980,20 @@
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" t="s">
-        <v>15</v>
+      <c r="A26" s="2">
+        <v>46149</v>
       </c>
       <c r="B26">
         <v>1148</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F26">
         <v>4.2</v>
@@ -2039,7 +2011,7 @@
         <v>7.56</v>
       </c>
       <c r="K26" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2049,20 +2021,20 @@
       </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" t="s">
-        <v>15</v>
+      <c r="A27" s="2">
+        <v>46149</v>
       </c>
       <c r="B27">
         <v>1148</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F27">
         <v>6.672</v>
@@ -2080,7 +2052,7 @@
         <v>12.01</v>
       </c>
       <c r="K27" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2090,20 +2062,20 @@
       </c>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" t="s">
-        <v>15</v>
+      <c r="A28" s="2">
+        <v>46149</v>
       </c>
       <c r="B28">
         <v>1158</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F28">
         <v>10.022</v>
@@ -2121,7 +2093,7 @@
         <v>18.04</v>
       </c>
       <c r="K28" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2131,20 +2103,20 @@
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" t="s">
-        <v>15</v>
+      <c r="A29" s="2">
+        <v>46149</v>
       </c>
       <c r="B29">
         <v>1199</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F29">
         <v>31.989</v>
@@ -2162,7 +2134,7 @@
         <v>57.58</v>
       </c>
       <c r="K29" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2172,20 +2144,20 @@
       </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" t="s">
-        <v>16</v>
+      <c r="A30" s="2">
+        <v>46150</v>
       </c>
       <c r="B30">
         <v>1146</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F30">
         <v>9.641999999999999</v>
@@ -2203,7 +2175,7 @@
         <v>17.26</v>
       </c>
       <c r="K30" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2213,20 +2185,20 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>16</v>
+      <c r="A31" s="2">
+        <v>46150</v>
       </c>
       <c r="B31">
         <v>1148</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F31">
         <v>6.458</v>
@@ -2244,7 +2216,7 @@
         <v>11.56</v>
       </c>
       <c r="K31" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2254,20 +2226,20 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" t="s">
-        <v>16</v>
+      <c r="A32" s="2">
+        <v>46150</v>
       </c>
       <c r="B32">
         <v>1148</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F32">
         <v>2.737</v>
@@ -2285,7 +2257,7 @@
         <v>4.9</v>
       </c>
       <c r="K32" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2295,20 +2267,20 @@
       </c>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" t="s">
-        <v>16</v>
+      <c r="A33" s="2">
+        <v>46150</v>
       </c>
       <c r="B33">
         <v>1148</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F33">
         <v>5.48</v>
@@ -2326,7 +2298,7 @@
         <v>9.81</v>
       </c>
       <c r="K33" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2336,20 +2308,20 @@
       </c>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>16</v>
+      <c r="A34" s="2">
+        <v>46150</v>
       </c>
       <c r="B34">
         <v>1148</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F34">
         <v>21</v>
@@ -2367,7 +2339,7 @@
         <v>37.59</v>
       </c>
       <c r="K34" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2377,20 +2349,20 @@
       </c>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>16</v>
+      <c r="A35" s="2">
+        <v>46150</v>
       </c>
       <c r="B35">
         <v>1148</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F35">
         <v>5.307</v>
@@ -2408,7 +2380,7 @@
         <v>9.5</v>
       </c>
       <c r="K35" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -2418,20 +2390,20 @@
       </c>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" t="s">
-        <v>16</v>
+      <c r="A36" s="2">
+        <v>46150</v>
       </c>
       <c r="B36">
         <v>1148</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F36">
         <v>62</v>
@@ -2449,7 +2421,7 @@
         <v>110.98</v>
       </c>
       <c r="K36" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2459,20 +2431,20 @@
       </c>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" t="s">
-        <v>16</v>
+      <c r="A37" s="2">
+        <v>46150</v>
       </c>
       <c r="B37">
         <v>1148</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F37">
         <v>3.698</v>
@@ -2490,7 +2462,7 @@
         <v>6.62</v>
       </c>
       <c r="K37" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -2500,20 +2472,20 @@
       </c>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" t="s">
-        <v>16</v>
+      <c r="A38" s="2">
+        <v>46150</v>
       </c>
       <c r="B38">
         <v>1148</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F38">
         <v>4.771</v>
@@ -2531,7 +2503,7 @@
         <v>8.539999999999999</v>
       </c>
       <c r="K38" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2541,20 +2513,20 @@
       </c>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" t="s">
-        <v>16</v>
+      <c r="A39" s="2">
+        <v>46150</v>
       </c>
       <c r="B39">
         <v>1158</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F39">
         <v>12.101</v>
@@ -2572,7 +2544,7 @@
         <v>21.66</v>
       </c>
       <c r="K39" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2582,20 +2554,20 @@
       </c>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" t="s">
-        <v>16</v>
+      <c r="A40" s="2">
+        <v>46150</v>
       </c>
       <c r="B40">
         <v>1158</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F40">
         <v>12.061</v>
@@ -2613,7 +2585,7 @@
         <v>21.59</v>
       </c>
       <c r="K40" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2623,20 +2595,20 @@
       </c>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" t="s">
-        <v>17</v>
+      <c r="A41" s="2">
+        <v>46152</v>
       </c>
       <c r="B41">
         <v>1158</v>
       </c>
       <c r="C41" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F41">
         <v>27.675</v>
@@ -2654,7 +2626,7 @@
         <v>22.97</v>
       </c>
       <c r="K41" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2664,20 +2636,20 @@
       </c>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" t="s">
-        <v>18</v>
+      <c r="A42" s="2">
+        <v>46153</v>
       </c>
       <c r="B42">
         <v>1146</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F42">
         <v>3.38</v>
@@ -2695,7 +2667,7 @@
         <v>6.05</v>
       </c>
       <c r="K42" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2705,20 +2677,20 @@
       </c>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" t="s">
-        <v>18</v>
+      <c r="A43" s="2">
+        <v>46153</v>
       </c>
       <c r="B43">
         <v>1146</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" t="s">
         <v>61</v>
-      </c>
-      <c r="E43" t="s">
-        <v>71</v>
       </c>
       <c r="F43">
         <v>5.13</v>
@@ -2736,7 +2708,7 @@
         <v>7.9</v>
       </c>
       <c r="K43" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2746,20 +2718,20 @@
       </c>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" t="s">
-        <v>18</v>
+      <c r="A44" s="2">
+        <v>46153</v>
       </c>
       <c r="B44">
         <v>1148</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F44">
         <v>4.318</v>
@@ -2777,7 +2749,7 @@
         <v>7.73</v>
       </c>
       <c r="K44" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2787,20 +2759,20 @@
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" t="s">
-        <v>18</v>
+      <c r="A45" s="2">
+        <v>46153</v>
       </c>
       <c r="B45">
         <v>1148</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F45">
         <v>11.358</v>
@@ -2818,7 +2790,7 @@
         <v>20.33</v>
       </c>
       <c r="K45" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2828,20 +2800,20 @@
       </c>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" t="s">
-        <v>18</v>
+      <c r="A46" s="2">
+        <v>46153</v>
       </c>
       <c r="B46">
         <v>1148</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E46" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F46">
         <v>8.407999999999999</v>
@@ -2859,7 +2831,7 @@
         <v>15.05</v>
       </c>
       <c r="K46" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2869,20 +2841,20 @@
       </c>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" t="s">
-        <v>18</v>
+      <c r="A47" s="2">
+        <v>46153</v>
       </c>
       <c r="B47">
         <v>1148</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F47">
         <v>11</v>
@@ -2900,7 +2872,7 @@
         <v>19.69</v>
       </c>
       <c r="K47" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2910,20 +2882,20 @@
       </c>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" t="s">
-        <v>18</v>
+      <c r="A48" s="2">
+        <v>46153</v>
       </c>
       <c r="B48">
         <v>1148</v>
       </c>
       <c r="C48" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E48" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F48">
         <v>5.402</v>
@@ -2941,7 +2913,7 @@
         <v>9.67</v>
       </c>
       <c r="K48" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2951,20 +2923,20 @@
       </c>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" t="s">
-        <v>18</v>
+      <c r="A49" s="2">
+        <v>46153</v>
       </c>
       <c r="B49">
         <v>1148</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F49">
         <v>7.05</v>
@@ -2982,7 +2954,7 @@
         <v>12.62</v>
       </c>
       <c r="K49" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2992,20 +2964,20 @@
       </c>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" t="s">
-        <v>18</v>
+      <c r="A50" s="2">
+        <v>46153</v>
       </c>
       <c r="B50">
         <v>1158</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F50">
         <v>20</v>
@@ -3023,7 +2995,7 @@
         <v>35.8</v>
       </c>
       <c r="K50" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -3033,20 +3005,20 @@
       </c>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" t="s">
-        <v>18</v>
+      <c r="A51" s="2">
+        <v>46153</v>
       </c>
       <c r="B51">
         <v>1158</v>
       </c>
       <c r="C51" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F51">
         <v>7</v>
@@ -3064,7 +3036,7 @@
         <v>12.53</v>
       </c>
       <c r="K51" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -3074,20 +3046,20 @@
       </c>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" t="s">
-        <v>18</v>
+      <c r="A52" s="2">
+        <v>46153</v>
       </c>
       <c r="B52">
         <v>1158</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E52" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F52">
         <v>8.073</v>
@@ -3105,7 +3077,7 @@
         <v>14.45</v>
       </c>
       <c r="K52" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -3115,20 +3087,20 @@
       </c>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" t="s">
-        <v>18</v>
+      <c r="A53" s="2">
+        <v>46153</v>
       </c>
       <c r="B53">
         <v>1158</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E53" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F53">
         <v>35</v>
@@ -3146,7 +3118,7 @@
         <v>62.65</v>
       </c>
       <c r="K53" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -3156,20 +3128,20 @@
       </c>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" t="s">
-        <v>18</v>
+      <c r="A54" s="2">
+        <v>46153</v>
       </c>
       <c r="B54">
         <v>1158</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F54">
         <v>5.788</v>
@@ -3187,7 +3159,7 @@
         <v>10.36</v>
       </c>
       <c r="K54" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -3197,20 +3169,20 @@
       </c>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" t="s">
-        <v>18</v>
+      <c r="A55" s="2">
+        <v>46153</v>
       </c>
       <c r="B55">
         <v>1158</v>
       </c>
       <c r="C55" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E55" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F55">
         <v>80</v>
@@ -3228,7 +3200,7 @@
         <v>163.2</v>
       </c>
       <c r="K55" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -3238,20 +3210,20 @@
       </c>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" t="s">
-        <v>18</v>
+      <c r="A56" s="2">
+        <v>46153</v>
       </c>
       <c r="B56">
         <v>1158</v>
       </c>
       <c r="C56" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E56" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F56">
         <v>100.02</v>
@@ -3269,7 +3241,7 @@
         <v>204.04</v>
       </c>
       <c r="K56" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -3279,20 +3251,20 @@
       </c>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" t="s">
-        <v>18</v>
+      <c r="A57" s="2">
+        <v>46153</v>
       </c>
       <c r="B57">
         <v>1158</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E57" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F57">
         <v>200.058</v>
@@ -3310,7 +3282,7 @@
         <v>308.09</v>
       </c>
       <c r="K57" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -3320,20 +3292,20 @@
       </c>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" t="s">
-        <v>18</v>
+      <c r="A58" s="2">
+        <v>46153</v>
       </c>
       <c r="B58">
         <v>1199</v>
       </c>
       <c r="C58" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E58" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F58">
         <v>49.659</v>
@@ -3351,7 +3323,7 @@
         <v>88.89</v>
       </c>
       <c r="K58" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -3361,20 +3333,20 @@
       </c>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" t="s">
-        <v>19</v>
+      <c r="A59" s="2">
+        <v>46154</v>
       </c>
       <c r="B59">
         <v>1146</v>
       </c>
       <c r="C59" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E59" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F59">
         <v>3.872</v>
@@ -3392,7 +3364,7 @@
         <v>6.93</v>
       </c>
       <c r="K59" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -3402,20 +3374,20 @@
       </c>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" t="s">
-        <v>19</v>
+      <c r="A60" s="2">
+        <v>46154</v>
       </c>
       <c r="B60">
         <v>1148</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E60" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F60">
         <v>17.011</v>
@@ -3433,7 +3405,7 @@
         <v>30.45</v>
       </c>
       <c r="K60" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -3443,20 +3415,20 @@
       </c>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" t="s">
-        <v>19</v>
+      <c r="A61" s="2">
+        <v>46154</v>
       </c>
       <c r="B61">
         <v>1148</v>
       </c>
       <c r="C61" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D61" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E61" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F61">
         <v>3.268</v>
@@ -3474,7 +3446,7 @@
         <v>5.85</v>
       </c>
       <c r="K61" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -3484,20 +3456,20 @@
       </c>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" t="s">
-        <v>19</v>
+      <c r="A62" s="2">
+        <v>46154</v>
       </c>
       <c r="B62">
         <v>1148</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E62" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F62">
         <v>13</v>
@@ -3515,7 +3487,7 @@
         <v>23.27</v>
       </c>
       <c r="K62" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -3525,20 +3497,20 @@
       </c>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" t="s">
-        <v>19</v>
+      <c r="A63" s="2">
+        <v>46154</v>
       </c>
       <c r="B63">
         <v>1148</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E63" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F63">
         <v>5.698</v>
@@ -3556,7 +3528,7 @@
         <v>10.2</v>
       </c>
       <c r="K63" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -3566,20 +3538,20 @@
       </c>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" t="s">
-        <v>19</v>
+      <c r="A64" s="2">
+        <v>46154</v>
       </c>
       <c r="B64">
         <v>1148</v>
       </c>
       <c r="C64" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E64" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F64">
         <v>6.899</v>
@@ -3597,7 +3569,7 @@
         <v>12.35</v>
       </c>
       <c r="K64" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -3607,20 +3579,20 @@
       </c>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" t="s">
-        <v>19</v>
+      <c r="A65" s="2">
+        <v>46154</v>
       </c>
       <c r="B65">
         <v>1148</v>
       </c>
       <c r="C65" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F65">
         <v>6.011</v>
@@ -3638,7 +3610,7 @@
         <v>10.76</v>
       </c>
       <c r="K65" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -3648,20 +3620,20 @@
       </c>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" t="s">
-        <v>19</v>
+      <c r="A66" s="2">
+        <v>46154</v>
       </c>
       <c r="B66">
         <v>1148</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E66" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F66">
         <v>5.101</v>
@@ -3679,7 +3651,7 @@
         <v>9.130000000000001</v>
       </c>
       <c r="K66" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -3689,20 +3661,20 @@
       </c>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" t="s">
-        <v>19</v>
+      <c r="A67" s="2">
+        <v>46154</v>
       </c>
       <c r="B67">
         <v>1158</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D67" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E67" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F67">
         <v>20</v>
@@ -3720,7 +3692,7 @@
         <v>35.8</v>
       </c>
       <c r="K67" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -3730,20 +3702,20 @@
       </c>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" t="s">
-        <v>19</v>
+      <c r="A68" s="2">
+        <v>46154</v>
       </c>
       <c r="B68">
         <v>1158</v>
       </c>
       <c r="C68" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D68" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E68" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F68">
         <v>3.402</v>
@@ -3761,7 +3733,7 @@
         <v>6.09</v>
       </c>
       <c r="K68" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -3771,20 +3743,20 @@
       </c>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" t="s">
-        <v>19</v>
+      <c r="A69" s="2">
+        <v>46154</v>
       </c>
       <c r="B69">
         <v>1158</v>
       </c>
       <c r="C69" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E69" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F69">
         <v>4.631</v>
@@ -3802,7 +3774,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="K69" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -3812,20 +3784,20 @@
       </c>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" t="s">
-        <v>19</v>
+      <c r="A70" s="2">
+        <v>46154</v>
       </c>
       <c r="B70">
         <v>1158</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E70" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F70">
         <v>8.340999999999999</v>
@@ -3843,7 +3815,7 @@
         <v>14.93</v>
       </c>
       <c r="K70" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -3853,20 +3825,20 @@
       </c>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" t="s">
-        <v>19</v>
+      <c r="A71" s="2">
+        <v>46154</v>
       </c>
       <c r="B71">
         <v>1199</v>
       </c>
       <c r="C71" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D71" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E71" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F71">
         <v>27.263</v>
@@ -3884,7 +3856,7 @@
         <v>48.8</v>
       </c>
       <c r="K71" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -3894,20 +3866,20 @@
       </c>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" t="s">
-        <v>20</v>
+      <c r="A72" s="2">
+        <v>46155</v>
       </c>
       <c r="B72">
         <v>1146</v>
       </c>
       <c r="C72" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D72" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E72" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F72">
         <v>2.798</v>
@@ -3925,7 +3897,7 @@
         <v>4.98</v>
       </c>
       <c r="K72" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -3935,20 +3907,20 @@
       </c>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" t="s">
-        <v>20</v>
+      <c r="A73" s="2">
+        <v>46155</v>
       </c>
       <c r="B73">
         <v>1146</v>
       </c>
       <c r="C73" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E73" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F73">
         <v>2.399</v>
@@ -3966,7 +3938,7 @@
         <v>4.27</v>
       </c>
       <c r="K73" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -3976,20 +3948,20 @@
       </c>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" t="s">
-        <v>20</v>
+      <c r="A74" s="2">
+        <v>46155</v>
       </c>
       <c r="B74">
         <v>1147</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E74" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F74">
         <v>5.91</v>
@@ -4007,7 +3979,7 @@
         <v>10.52</v>
       </c>
       <c r="K74" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -4017,20 +3989,20 @@
       </c>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" t="s">
-        <v>20</v>
+      <c r="A75" s="2">
+        <v>46155</v>
       </c>
       <c r="B75">
         <v>1148</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E75" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F75">
         <v>5.598</v>
@@ -4048,7 +4020,7 @@
         <v>10.02</v>
       </c>
       <c r="K75" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -4058,20 +4030,20 @@
       </c>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" t="s">
-        <v>20</v>
+      <c r="A76" s="2">
+        <v>46155</v>
       </c>
       <c r="B76">
         <v>1148</v>
       </c>
       <c r="C76" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D76" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E76" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F76">
         <v>3.32</v>
@@ -4089,7 +4061,7 @@
         <v>5.91</v>
       </c>
       <c r="K76" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -4099,20 +4071,20 @@
       </c>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" t="s">
-        <v>20</v>
+      <c r="A77" s="2">
+        <v>46155</v>
       </c>
       <c r="B77">
         <v>1148</v>
       </c>
       <c r="C77" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E77" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F77">
         <v>6.298</v>
@@ -4130,7 +4102,7 @@
         <v>11.21</v>
       </c>
       <c r="K77" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -4140,20 +4112,20 @@
       </c>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" t="s">
-        <v>20</v>
+      <c r="A78" s="2">
+        <v>46155</v>
       </c>
       <c r="B78">
         <v>1148</v>
       </c>
       <c r="C78" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D78" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E78" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F78">
         <v>3.157</v>
@@ -4171,7 +4143,7 @@
         <v>5.62</v>
       </c>
       <c r="K78" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -4181,20 +4153,20 @@
       </c>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" t="s">
-        <v>20</v>
+      <c r="A79" s="2">
+        <v>46155</v>
       </c>
       <c r="B79">
         <v>1148</v>
       </c>
       <c r="C79" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E79" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F79">
         <v>13.011</v>
@@ -4212,7 +4184,7 @@
         <v>23.16</v>
       </c>
       <c r="K79" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -4222,20 +4194,20 @@
       </c>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" t="s">
-        <v>20</v>
+      <c r="A80" s="2">
+        <v>46155</v>
       </c>
       <c r="B80">
         <v>1148</v>
       </c>
       <c r="C80" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E80" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F80">
         <v>7.618</v>
@@ -4253,7 +4225,7 @@
         <v>13.56</v>
       </c>
       <c r="K80" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -4263,20 +4235,20 @@
       </c>
     </row>
     <row r="81" spans="1:13">
-      <c r="A81" t="s">
-        <v>20</v>
+      <c r="A81" s="2">
+        <v>46155</v>
       </c>
       <c r="B81">
         <v>1148</v>
       </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E81" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F81">
         <v>5</v>
@@ -4294,7 +4266,7 @@
         <v>8.9</v>
       </c>
       <c r="K81" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -4304,20 +4276,20 @@
       </c>
     </row>
     <row r="82" spans="1:13">
-      <c r="A82" t="s">
-        <v>20</v>
+      <c r="A82" s="2">
+        <v>46155</v>
       </c>
       <c r="B82">
         <v>1158</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D82" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E82" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F82">
         <v>25</v>
@@ -4335,7 +4307,7 @@
         <v>44.5</v>
       </c>
       <c r="K82" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -4345,20 +4317,20 @@
       </c>
     </row>
     <row r="83" spans="1:13">
-      <c r="A83" t="s">
-        <v>20</v>
+      <c r="A83" s="2">
+        <v>46155</v>
       </c>
       <c r="B83">
         <v>1158</v>
       </c>
       <c r="C83" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D83" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E83" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F83">
         <v>4.331</v>
@@ -4376,7 +4348,7 @@
         <v>7.71</v>
       </c>
       <c r="K83" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -4386,20 +4358,20 @@
       </c>
     </row>
     <row r="84" spans="1:13">
-      <c r="A84" t="s">
-        <v>20</v>
+      <c r="A84" s="2">
+        <v>46155</v>
       </c>
       <c r="B84">
         <v>1158</v>
       </c>
       <c r="C84" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F84">
         <v>11</v>
@@ -4417,7 +4389,7 @@
         <v>19.58</v>
       </c>
       <c r="K84" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -4427,20 +4399,20 @@
       </c>
     </row>
     <row r="85" spans="1:13">
-      <c r="A85" t="s">
-        <v>20</v>
+      <c r="A85" s="2">
+        <v>46155</v>
       </c>
       <c r="B85">
         <v>1158</v>
       </c>
       <c r="C85" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D85" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E85" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F85">
         <v>27.469</v>
@@ -4458,7 +4430,7 @@
         <v>22.25</v>
       </c>
       <c r="K85" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -4468,20 +4440,20 @@
       </c>
     </row>
     <row r="86" spans="1:13">
-      <c r="A86" t="s">
-        <v>20</v>
+      <c r="A86" s="2">
+        <v>46155</v>
       </c>
       <c r="B86">
         <v>1199</v>
       </c>
       <c r="C86" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D86" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E86" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F86">
         <v>50.433</v>
@@ -4499,7 +4471,7 @@
         <v>89.77</v>
       </c>
       <c r="K86" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -4509,20 +4481,20 @@
       </c>
     </row>
     <row r="87" spans="1:13">
-      <c r="A87" t="s">
-        <v>20</v>
+      <c r="A87" s="2">
+        <v>46155</v>
       </c>
       <c r="B87">
         <v>1199</v>
       </c>
       <c r="C87" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D87" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E87" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F87">
         <v>25.41</v>
@@ -4540,7 +4512,7 @@
         <v>45.23</v>
       </c>
       <c r="K87" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -4550,20 +4522,20 @@
       </c>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" t="s">
-        <v>21</v>
+      <c r="A88" s="2">
+        <v>46156</v>
       </c>
       <c r="B88">
         <v>1146</v>
       </c>
       <c r="C88" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D88" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E88" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F88">
         <v>3.819</v>
@@ -4581,7 +4553,7 @@
         <v>6.76</v>
       </c>
       <c r="K88" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -4591,20 +4563,20 @@
       </c>
     </row>
     <row r="89" spans="1:13">
-      <c r="A89" t="s">
-        <v>21</v>
+      <c r="A89" s="2">
+        <v>46156</v>
       </c>
       <c r="B89">
         <v>1148</v>
       </c>
       <c r="C89" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D89" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E89" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F89">
         <v>4.989</v>
@@ -4622,7 +4594,7 @@
         <v>8.83</v>
       </c>
       <c r="K89" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -4632,20 +4604,20 @@
       </c>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" t="s">
-        <v>21</v>
+      <c r="A90" s="2">
+        <v>46156</v>
       </c>
       <c r="B90">
         <v>1148</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E90" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F90">
         <v>7.153</v>
@@ -4663,7 +4635,7 @@
         <v>12.66</v>
       </c>
       <c r="K90" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -4673,20 +4645,20 @@
       </c>
     </row>
     <row r="91" spans="1:13">
-      <c r="A91" t="s">
-        <v>21</v>
+      <c r="A91" s="2">
+        <v>46156</v>
       </c>
       <c r="B91">
         <v>1148</v>
       </c>
       <c r="C91" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D91" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E91" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F91">
         <v>4.102</v>
@@ -4704,7 +4676,7 @@
         <v>7.26</v>
       </c>
       <c r="K91" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -4714,20 +4686,20 @@
       </c>
     </row>
     <row r="92" spans="1:13">
-      <c r="A92" t="s">
-        <v>21</v>
+      <c r="A92" s="2">
+        <v>46156</v>
       </c>
       <c r="B92">
         <v>1148</v>
       </c>
       <c r="C92" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E92" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F92">
         <v>4.13</v>
@@ -4745,7 +4717,7 @@
         <v>7.31</v>
       </c>
       <c r="K92" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -4755,20 +4727,20 @@
       </c>
     </row>
     <row r="93" spans="1:13">
-      <c r="A93" t="s">
-        <v>21</v>
+      <c r="A93" s="2">
+        <v>46156</v>
       </c>
       <c r="B93">
         <v>1148</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E93" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F93">
         <v>30</v>
@@ -4786,7 +4758,7 @@
         <v>53.1</v>
       </c>
       <c r="K93" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -4796,20 +4768,20 @@
       </c>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" t="s">
-        <v>21</v>
+      <c r="A94" s="2">
+        <v>46156</v>
       </c>
       <c r="B94">
         <v>1148</v>
       </c>
       <c r="C94" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D94" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E94" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F94">
         <v>6.989</v>
@@ -4827,7 +4799,7 @@
         <v>12.37</v>
       </c>
       <c r="K94" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -4837,20 +4809,20 @@
       </c>
     </row>
     <row r="95" spans="1:13">
-      <c r="A95" t="s">
-        <v>21</v>
+      <c r="A95" s="2">
+        <v>46156</v>
       </c>
       <c r="B95">
         <v>1148</v>
       </c>
       <c r="C95" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D95" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E95" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F95">
         <v>5.898</v>
@@ -4868,7 +4840,7 @@
         <v>10.44</v>
       </c>
       <c r="K95" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -4878,20 +4850,20 @@
       </c>
     </row>
     <row r="96" spans="1:13">
-      <c r="A96" t="s">
-        <v>21</v>
+      <c r="A96" s="2">
+        <v>46156</v>
       </c>
       <c r="B96">
         <v>1158</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E96" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F96">
         <v>11.819</v>
@@ -4909,7 +4881,7 @@
         <v>20.92</v>
       </c>
       <c r="K96" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -4919,20 +4891,20 @@
       </c>
     </row>
     <row r="97" spans="1:13">
-      <c r="A97" t="s">
-        <v>21</v>
+      <c r="A97" s="2">
+        <v>46156</v>
       </c>
       <c r="B97">
         <v>1158</v>
       </c>
       <c r="C97" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E97" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F97">
         <v>6</v>
@@ -4950,7 +4922,7 @@
         <v>10.62</v>
       </c>
       <c r="K97" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -4960,20 +4932,20 @@
       </c>
     </row>
     <row r="98" spans="1:13">
-      <c r="A98" t="s">
-        <v>21</v>
+      <c r="A98" s="2">
+        <v>46156</v>
       </c>
       <c r="B98">
         <v>1158</v>
       </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E98" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F98">
         <v>7.808</v>
@@ -4991,7 +4963,7 @@
         <v>13.82</v>
       </c>
       <c r="K98" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -5001,20 +4973,20 @@
       </c>
     </row>
     <row r="99" spans="1:13">
-      <c r="A99" t="s">
-        <v>22</v>
+      <c r="A99" s="2">
+        <v>46157</v>
       </c>
       <c r="B99">
         <v>1146</v>
       </c>
       <c r="C99" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E99" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F99">
         <v>2.818</v>
@@ -5032,7 +5004,7 @@
         <v>4.96</v>
       </c>
       <c r="K99" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -5042,20 +5014,20 @@
       </c>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" t="s">
-        <v>22</v>
+      <c r="A100" s="2">
+        <v>46157</v>
       </c>
       <c r="B100">
         <v>1148</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E100" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F100">
         <v>13</v>
@@ -5073,7 +5045,7 @@
         <v>22.88</v>
       </c>
       <c r="K100" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -5083,20 +5055,20 @@
       </c>
     </row>
     <row r="101" spans="1:13">
-      <c r="A101" t="s">
-        <v>22</v>
+      <c r="A101" s="2">
+        <v>46157</v>
       </c>
       <c r="B101">
         <v>1148</v>
       </c>
       <c r="C101" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E101" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F101">
         <v>18</v>
@@ -5114,7 +5086,7 @@
         <v>31.68</v>
       </c>
       <c r="K101" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -5124,20 +5096,20 @@
       </c>
     </row>
     <row r="102" spans="1:13">
-      <c r="A102" t="s">
-        <v>22</v>
+      <c r="A102" s="2">
+        <v>46157</v>
       </c>
       <c r="B102">
         <v>1148</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E102" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F102">
         <v>5.29</v>
@@ -5155,7 +5127,7 @@
         <v>9.31</v>
       </c>
       <c r="K102" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -5165,20 +5137,20 @@
       </c>
     </row>
     <row r="103" spans="1:13">
-      <c r="A103" t="s">
-        <v>22</v>
+      <c r="A103" s="2">
+        <v>46157</v>
       </c>
       <c r="B103">
         <v>1148</v>
       </c>
       <c r="C103" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="E103" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F103">
         <v>30</v>
@@ -5196,7 +5168,7 @@
         <v>52.8</v>
       </c>
       <c r="K103" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -5206,20 +5178,20 @@
       </c>
     </row>
     <row r="104" spans="1:13">
-      <c r="A104" t="s">
-        <v>22</v>
+      <c r="A104" s="2">
+        <v>46157</v>
       </c>
       <c r="B104">
         <v>1148</v>
       </c>
       <c r="C104" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D104" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E104" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F104">
         <v>3.523</v>
@@ -5237,7 +5209,7 @@
         <v>6.2</v>
       </c>
       <c r="K104" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -5247,20 +5219,20 @@
       </c>
     </row>
     <row r="105" spans="1:13">
-      <c r="A105" t="s">
-        <v>22</v>
+      <c r="A105" s="2">
+        <v>46157</v>
       </c>
       <c r="B105">
         <v>1148</v>
       </c>
       <c r="C105" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D105" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E105" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F105">
         <v>3.58</v>
@@ -5278,7 +5250,7 @@
         <v>6.3</v>
       </c>
       <c r="K105" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -5288,20 +5260,20 @@
       </c>
     </row>
     <row r="106" spans="1:13">
-      <c r="A106" t="s">
-        <v>22</v>
+      <c r="A106" s="2">
+        <v>46157</v>
       </c>
       <c r="B106">
         <v>1148</v>
       </c>
       <c r="C106" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E106" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F106">
         <v>41</v>
@@ -5319,7 +5291,7 @@
         <v>72.16</v>
       </c>
       <c r="K106" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -5329,20 +5301,20 @@
       </c>
     </row>
     <row r="107" spans="1:13">
-      <c r="A107" t="s">
-        <v>22</v>
+      <c r="A107" s="2">
+        <v>46157</v>
       </c>
       <c r="B107">
         <v>1148</v>
       </c>
       <c r="C107" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D107" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E107" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F107">
         <v>7.523</v>
@@ -5360,7 +5332,7 @@
         <v>13.24</v>
       </c>
       <c r="K107" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -5370,20 +5342,20 @@
       </c>
     </row>
     <row r="108" spans="1:13">
-      <c r="A108" t="s">
-        <v>22</v>
+      <c r="A108" s="2">
+        <v>46157</v>
       </c>
       <c r="B108">
         <v>1148</v>
       </c>
       <c r="C108" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D108" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E108" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F108">
         <v>13.199</v>
@@ -5401,7 +5373,7 @@
         <v>23.23</v>
       </c>
       <c r="K108" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -5411,20 +5383,20 @@
       </c>
     </row>
     <row r="109" spans="1:13">
-      <c r="A109" t="s">
-        <v>22</v>
+      <c r="A109" s="2">
+        <v>46157</v>
       </c>
       <c r="B109">
         <v>1158</v>
       </c>
       <c r="C109" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E109" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -5442,7 +5414,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="K109" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -5452,20 +5424,20 @@
       </c>
     </row>
     <row r="110" spans="1:13">
-      <c r="A110" t="s">
-        <v>22</v>
+      <c r="A110" s="2">
+        <v>46157</v>
       </c>
       <c r="B110">
         <v>1158</v>
       </c>
       <c r="C110" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E110" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F110">
         <v>7.989</v>
@@ -5483,7 +5455,7 @@
         <v>14.06</v>
       </c>
       <c r="K110" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -5493,20 +5465,20 @@
       </c>
     </row>
     <row r="111" spans="1:13">
-      <c r="A111" t="s">
-        <v>22</v>
+      <c r="A111" s="2">
+        <v>46157</v>
       </c>
       <c r="B111">
         <v>1158</v>
       </c>
       <c r="C111" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D111" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E111" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F111">
         <v>8.852</v>
@@ -5524,7 +5496,7 @@
         <v>15.58</v>
       </c>
       <c r="K111" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -5534,20 +5506,20 @@
       </c>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" t="s">
-        <v>22</v>
+      <c r="A112" s="2">
+        <v>46157</v>
       </c>
       <c r="B112">
         <v>1158</v>
       </c>
       <c r="C112" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E112" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F112">
         <v>6.773</v>
@@ -5565,7 +5537,7 @@
         <v>11.92</v>
       </c>
       <c r="K112" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -5575,20 +5547,20 @@
       </c>
     </row>
     <row r="113" spans="1:13">
-      <c r="A113" t="s">
-        <v>22</v>
+      <c r="A113" s="2">
+        <v>46157</v>
       </c>
       <c r="B113">
         <v>1199</v>
       </c>
       <c r="C113" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E113" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F113">
         <v>57.528</v>
@@ -5606,7 +5578,7 @@
         <v>101.25</v>
       </c>
       <c r="K113" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -5616,149 +5588,149 @@
       </c>
     </row>
     <row r="116" spans="1:13">
-      <c r="A116" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
+      <c r="A116" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
     </row>
     <row r="117" spans="1:13">
-      <c r="A117" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>181</v>
+      <c r="A117" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="118" spans="1:13">
-      <c r="A118" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B118" s="5">
+      <c r="A118" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B118" s="6">
         <v>1231.892</v>
       </c>
-      <c r="C118" s="5">
+      <c r="C118" s="6">
         <v>105</v>
       </c>
-      <c r="D118" s="5">
+      <c r="D118" s="6">
         <v>1.7541</v>
       </c>
-      <c r="E118" s="5">
+      <c r="E118" s="6">
         <v>2160.89</v>
       </c>
-      <c r="F118" s="5">
+      <c r="F118" s="6">
         <v>2197.83</v>
       </c>
-      <c r="G118" s="5">
+      <c r="G118" s="6">
         <v>36.94</v>
       </c>
     </row>
     <row r="119" spans="1:13">
-      <c r="A119" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B119" s="5">
+      <c r="A119" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B119" s="6">
         <v>205.188</v>
       </c>
-      <c r="C119" s="5">
+      <c r="C119" s="6">
         <v>2</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D119" s="6">
         <v>1.51</v>
       </c>
-      <c r="E119" s="5">
+      <c r="E119" s="6">
         <v>309.84</v>
       </c>
-      <c r="F119" s="5">
+      <c r="F119" s="6">
         <v>315.99</v>
       </c>
-      <c r="G119" s="5">
+      <c r="G119" s="6">
         <v>6.15</v>
       </c>
     </row>
     <row r="120" spans="1:13">
-      <c r="A120" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B120" s="5">
+      <c r="A120" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B120" s="6">
         <v>180.02</v>
       </c>
-      <c r="C120" s="5">
+      <c r="C120" s="6">
         <v>2</v>
       </c>
-      <c r="D120" s="5">
+      <c r="D120" s="6">
         <v>2.04</v>
       </c>
-      <c r="E120" s="5">
+      <c r="E120" s="6">
         <v>367.24</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120" s="6">
         <v>367.24</v>
       </c>
-      <c r="G120" s="5">
+      <c r="G120" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:13">
-      <c r="A121" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B121" s="5">
+      <c r="A121" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B121" s="6">
         <v>82.95099999999999</v>
       </c>
-      <c r="C121" s="5">
+      <c r="C121" s="6">
         <v>3</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D121" s="6">
         <v>0.8134</v>
       </c>
-      <c r="E121" s="5">
+      <c r="E121" s="6">
         <v>67.47</v>
       </c>
-      <c r="F121" s="5">
+      <c r="F121" s="6">
         <v>68.3</v>
       </c>
-      <c r="G121" s="5">
+      <c r="G121" s="6">
         <v>0.83</v>
       </c>
     </row>
     <row r="122" spans="1:13">
-      <c r="A122" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B122" s="7">
+      <c r="A122" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B122" s="8">
         <v>1700.051</v>
       </c>
-      <c r="C122" s="7">
+      <c r="C122" s="8">
         <v>112</v>
       </c>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7">
+      <c r="D122" s="8"/>
+      <c r="E122" s="8">
         <v>2905.44</v>
       </c>
-      <c r="F122" s="7">
+      <c r="F122" s="8">
         <v>2949.36</v>
       </c>
-      <c r="G122" s="7">
+      <c r="G122" s="8">
         <v>43.92</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
@@ -950,7 +950,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -960,12 +960,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1016,17 +1010,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="166">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -58,7 +64,7 @@
     <t>Варна Сливница</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>Варна Варненчик</t>
@@ -203,6 +209,291 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>12:28</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>13:18</t>
+  </si>
+  <si>
+    <t>13:23</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>14:09</t>
+  </si>
+  <si>
+    <t>14:11</t>
+  </si>
+  <si>
+    <t>14:12</t>
+  </si>
+  <si>
+    <t>14:16</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>13:31</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>14:08</t>
+  </si>
+  <si>
+    <t>14:13</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>13:41</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>13:46</t>
+  </si>
+  <si>
+    <t>13:51</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>14:38</t>
+  </si>
+  <si>
+    <t>15:27</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>13:19</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>13:44</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:11</t>
+  </si>
+  <si>
+    <t>15:26</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>14:44</t>
+  </si>
+  <si>
+    <t>14:53</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>07:04</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>13:33</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>14:02</t>
+  </si>
+  <si>
+    <t>14:26</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>13:57</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>16:04</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>13:43</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>14:03</t>
+  </si>
+  <si>
+    <t>14:17</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>13:03</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
+    <t>13:29</t>
+  </si>
+  <si>
+    <t>14:01</t>
+  </si>
+  <si>
+    <t>14:06</t>
+  </si>
+  <si>
+    <t>14:21</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>13:06</t>
+  </si>
+  <si>
+    <t>13:07</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>14:29</t>
+  </si>
+  <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>13:54</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>14:27</t>
+  </si>
+  <si>
+    <t>14:28</t>
+  </si>
+  <si>
+    <t>15:04</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ</t>
@@ -622,7 +913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -635,10 +926,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -672,22 +965,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -704,25 +1003,31 @@
       <c r="J2">
         <v>5.07</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>213483</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -739,25 +1044,31 @@
       <c r="J3">
         <v>6.76</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3">
         <v>73292</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>105903</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46174</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F4">
         <v>5.56</v>
@@ -774,25 +1085,31 @@
       <c r="J4">
         <v>9.4</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4">
         <v>36128</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>213509</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46174</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F5">
         <v>2.3</v>
@@ -809,25 +1126,31 @@
       <c r="J5">
         <v>3.89</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5">
         <v>143169</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>213512</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46174</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6">
         <v>2.58</v>
@@ -844,25 +1167,31 @@
       <c r="J6">
         <v>4.36</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6">
         <v>43194</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>137452</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46174</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>10.43</v>
@@ -879,25 +1208,31 @@
       <c r="J7">
         <v>17.63</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7">
         <v>65327</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46174</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F8">
         <v>4.05</v>
@@ -914,25 +1249,31 @@
       <c r="J8">
         <v>6.84</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8">
         <v>82396</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M8">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46174</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F9">
         <v>2.55</v>
@@ -949,25 +1290,31 @@
       <c r="J9">
         <v>4.31</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9">
         <v>187218</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="M9">
+        <v>137463</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46174</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F10">
         <v>23</v>
@@ -984,25 +1331,31 @@
       <c r="J10">
         <v>38.87</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10">
         <v>76245</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M10">
+        <v>213532</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46174</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1019,25 +1372,31 @@
       <c r="J11">
         <v>8.449999999999999</v>
       </c>
-      <c r="K11">
-        <v>93762</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11">
+        <v>102519</v>
+      </c>
+      <c r="M11">
+        <v>105954</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46174</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -1054,25 +1413,31 @@
       <c r="J12">
         <v>18.59</v>
       </c>
-      <c r="K12">
-        <v>102519</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" t="s">
+        <v>75</v>
+      </c>
+      <c r="L12">
+        <v>93762</v>
+      </c>
+      <c r="M12">
+        <v>213534</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46174</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13">
         <v>3.5</v>
@@ -1089,25 +1454,31 @@
       <c r="J13">
         <v>5.92</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="s">
+        <v>76</v>
+      </c>
+      <c r="L13">
         <v>197870</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="M13">
+        <v>213541</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46174</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F14">
         <v>4.5</v>
@@ -1124,25 +1495,31 @@
       <c r="J14">
         <v>7.6</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14">
         <v>57045</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="M14">
+        <v>213562</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46175</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F15">
         <v>8.19</v>
@@ -1159,25 +1536,31 @@
       <c r="J15">
         <v>13.84</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15">
         <v>36179</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="M15">
+        <v>213973</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46175</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F16">
         <v>3.31</v>
@@ -1194,25 +1577,31 @@
       <c r="J16">
         <v>5.59</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16">
         <v>43217</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="M16">
+        <v>137768</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46175</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F17">
         <v>9.550000000000001</v>
@@ -1229,25 +1618,31 @@
       <c r="J17">
         <v>16.14</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L17">
         <v>93856</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="M17">
+        <v>106427</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46175</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F18">
         <v>2.02</v>
@@ -1264,25 +1659,31 @@
       <c r="J18">
         <v>3.41</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="s">
+        <v>81</v>
+      </c>
+      <c r="L18">
         <v>143180</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="M18">
+        <v>213984</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3">
         <v>46175</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -1299,25 +1700,31 @@
       <c r="J19">
         <v>8.449999999999999</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19">
         <v>175188</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="M19">
+        <v>213994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3">
         <v>46175</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F20">
         <v>2.44</v>
@@ -1334,25 +1741,31 @@
       <c r="J20">
         <v>4.12</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="s">
+        <v>71</v>
+      </c>
+      <c r="L20">
         <v>187240</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="M20">
+        <v>137789</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3">
         <v>46175</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F21">
         <v>3.62</v>
@@ -1369,25 +1782,31 @@
       <c r="J21">
         <v>6.12</v>
       </c>
-      <c r="K21">
-        <v>187892</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="K21" t="s">
+        <v>83</v>
+      </c>
+      <c r="L21">
+        <v>53811</v>
+      </c>
+      <c r="M21">
+        <v>214008</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="3">
         <v>46175</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F22">
         <v>31</v>
@@ -1404,25 +1823,31 @@
       <c r="J22">
         <v>52.39</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="s">
+        <v>84</v>
+      </c>
+      <c r="L22">
         <v>76338</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="M22">
+        <v>214013</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="3">
         <v>46175</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F23">
         <v>11</v>
@@ -1439,25 +1864,31 @@
       <c r="J23">
         <v>18.59</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="s">
+        <v>75</v>
+      </c>
+      <c r="L23">
         <v>102532</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="M23">
+        <v>214018</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="3">
         <v>46175</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F24">
         <v>4.89</v>
@@ -1474,25 +1905,31 @@
       <c r="J24">
         <v>8.26</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="s">
+        <v>75</v>
+      </c>
+      <c r="L24">
         <v>82432</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="M24">
+        <v>214020</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="3">
         <v>46175</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F25">
         <v>6.34</v>
@@ -1509,25 +1946,31 @@
       <c r="J25">
         <v>10.71</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="s">
+        <v>85</v>
+      </c>
+      <c r="L25">
         <v>73341</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="M25">
+        <v>106469</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="3">
         <v>46175</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F26">
         <v>8.699999999999999</v>
@@ -1544,25 +1987,31 @@
       <c r="J26">
         <v>14.7</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="s">
+        <v>76</v>
+      </c>
+      <c r="L26">
         <v>57115</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="M26">
+        <v>214025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="3">
         <v>46176</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F27">
         <v>40</v>
@@ -1579,25 +2028,31 @@
       <c r="J27">
         <v>62.8</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="s">
+        <v>86</v>
+      </c>
+      <c r="L27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="M27">
+        <v>214263</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="3">
         <v>46176</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F28">
         <v>160.03</v>
@@ -1614,25 +2069,31 @@
       <c r="J28">
         <v>251.25</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="s">
+        <v>87</v>
+      </c>
+      <c r="L28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="M28">
+        <v>214268</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="3">
         <v>46176</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F29">
         <v>43.19</v>
@@ -1649,25 +2110,31 @@
       <c r="J29">
         <v>72.98999999999999</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="s">
+        <v>88</v>
+      </c>
+      <c r="L29">
         <v>2174</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="M29">
+        <v>272147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="3">
         <v>46176</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F30">
         <v>17.57</v>
@@ -1684,25 +2151,31 @@
       <c r="J30">
         <v>29.69</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="s">
+        <v>89</v>
+      </c>
+      <c r="L30">
         <v>65474</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="M30">
+        <v>106942</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="3">
         <v>46176</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F31">
         <v>6.38</v>
@@ -1719,25 +2192,31 @@
       <c r="J31">
         <v>10.78</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="s">
+        <v>69</v>
+      </c>
+      <c r="L31">
         <v>36220</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="M31">
+        <v>214372</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="3">
         <v>46176</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F32">
         <v>3.19</v>
@@ -1754,25 +2233,31 @@
       <c r="J32">
         <v>5.39</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="s">
+        <v>90</v>
+      </c>
+      <c r="L32">
         <v>187275</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="M32">
+        <v>138143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="3">
         <v>46176</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F33">
         <v>2.04</v>
@@ -1789,25 +2274,31 @@
       <c r="J33">
         <v>3.45</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="s">
+        <v>90</v>
+      </c>
+      <c r="L33">
         <v>143192</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="M33">
+        <v>214380</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="3">
         <v>46176</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F34">
         <v>3.87</v>
@@ -1824,25 +2315,31 @@
       <c r="J34">
         <v>6.54</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="s">
+        <v>91</v>
+      </c>
+      <c r="L34">
         <v>187923</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="M34">
+        <v>214382</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="3">
         <v>46176</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -1859,25 +2356,31 @@
       <c r="J35">
         <v>8.449999999999999</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="s">
+        <v>92</v>
+      </c>
+      <c r="L35">
         <v>175225</v>
       </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="M35">
+        <v>214385</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="3">
         <v>46176</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F36">
         <v>28</v>
@@ -1894,25 +2397,31 @@
       <c r="J36">
         <v>47.32</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="s">
+        <v>93</v>
+      </c>
+      <c r="L36">
         <v>102596</v>
       </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="M36">
+        <v>214388</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="3">
         <v>46176</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F37">
         <v>3.08</v>
@@ -1929,25 +2438,31 @@
       <c r="J37">
         <v>5.21</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="s">
+        <v>72</v>
+      </c>
+      <c r="L37">
         <v>43242</v>
       </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="M37">
+        <v>138153</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="3">
         <v>46176</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F38">
         <v>8.94</v>
@@ -1964,25 +2479,31 @@
       <c r="J38">
         <v>15.11</v>
       </c>
-      <c r="K38">
+      <c r="K38" t="s">
+        <v>76</v>
+      </c>
+      <c r="L38">
         <v>93935</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="M38">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="3">
         <v>46176</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F39">
         <v>31.02</v>
@@ -1999,25 +2520,31 @@
       <c r="J39">
         <v>52.42</v>
       </c>
-      <c r="K39">
+      <c r="K39" t="s">
+        <v>94</v>
+      </c>
+      <c r="L39">
         <v>76419</v>
       </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="M39">
+        <v>214404</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="3">
         <v>46176</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F40">
         <v>6.26</v>
@@ -2034,25 +2561,31 @@
       <c r="J40">
         <v>10.58</v>
       </c>
-      <c r="K40">
+      <c r="K40" t="s">
+        <v>95</v>
+      </c>
+      <c r="L40">
         <v>57159</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="M40">
+        <v>214408</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="3">
         <v>46176</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F41">
         <v>7.55</v>
@@ -2069,25 +2602,31 @@
       <c r="J41">
         <v>12.76</v>
       </c>
-      <c r="K41">
+      <c r="K41" t="s">
+        <v>96</v>
+      </c>
+      <c r="L41">
         <v>82516</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="M41">
+        <v>214433</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="3">
         <v>46176</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F42">
         <v>3.51</v>
@@ -2104,25 +2643,31 @@
       <c r="J42">
         <v>5.93</v>
       </c>
-      <c r="K42">
+      <c r="K42" t="s">
+        <v>97</v>
+      </c>
+      <c r="L42">
         <v>73371</v>
       </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="M42">
+        <v>138227</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="3">
         <v>46177</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F43">
         <v>5.22</v>
@@ -2139,25 +2684,31 @@
       <c r="J43">
         <v>8.67</v>
       </c>
-      <c r="K43">
+      <c r="K43" t="s">
+        <v>98</v>
+      </c>
+      <c r="L43">
         <v>471</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="M43">
+        <v>214769</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="3">
         <v>46177</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F44">
         <v>5.59</v>
@@ -2174,25 +2725,31 @@
       <c r="J44">
         <v>9.279999999999999</v>
       </c>
-      <c r="K44">
-        <v>36242</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="K44" t="s">
+        <v>99</v>
+      </c>
+      <c r="L44">
+        <v>380</v>
+      </c>
+      <c r="M44">
+        <v>214800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="3">
         <v>46177</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E45" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F45">
         <v>8.01</v>
@@ -2209,25 +2766,31 @@
       <c r="J45">
         <v>13.3</v>
       </c>
-      <c r="K45">
+      <c r="K45" t="s">
+        <v>100</v>
+      </c>
+      <c r="L45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="M45">
+        <v>214802</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="3">
         <v>46177</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E46" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F46">
         <v>4.26</v>
@@ -2244,25 +2807,31 @@
       <c r="J46">
         <v>7.07</v>
       </c>
-      <c r="K46">
+      <c r="K46" t="s">
+        <v>101</v>
+      </c>
+      <c r="L46">
         <v>43278</v>
       </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="M46">
+        <v>138509</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="3">
         <v>46177</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F47">
         <v>13</v>
@@ -2279,25 +2848,31 @@
       <c r="J47">
         <v>21.58</v>
       </c>
-      <c r="K47">
+      <c r="K47" t="s">
+        <v>81</v>
+      </c>
+      <c r="L47">
         <v>102611</v>
       </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="M47">
+        <v>214807</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="3">
         <v>46177</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E48" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F48">
         <v>2.64</v>
@@ -2314,25 +2889,31 @@
       <c r="J48">
         <v>4.38</v>
       </c>
-      <c r="K48">
+      <c r="K48" t="s">
+        <v>102</v>
+      </c>
+      <c r="L48">
         <v>143206</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="M48">
+        <v>214816</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="3">
         <v>46177</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E49" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F49">
         <v>2.28</v>
@@ -2349,25 +2930,31 @@
       <c r="J49">
         <v>3.78</v>
       </c>
-      <c r="K49">
+      <c r="K49" t="s">
+        <v>92</v>
+      </c>
+      <c r="L49">
         <v>187296</v>
       </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="M49">
+        <v>138513</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="3">
         <v>46177</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E50" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F50">
         <v>4.54</v>
@@ -2384,25 +2971,31 @@
       <c r="J50">
         <v>7.54</v>
       </c>
-      <c r="K50">
+      <c r="K50" t="s">
+        <v>83</v>
+      </c>
+      <c r="L50">
         <v>177960</v>
       </c>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="M50">
+        <v>214828</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="3">
         <v>46177</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F51">
         <v>7.46</v>
@@ -2419,25 +3012,31 @@
       <c r="J51">
         <v>12.38</v>
       </c>
-      <c r="K51">
+      <c r="K51" t="s">
+        <v>73</v>
+      </c>
+      <c r="L51">
         <v>93961</v>
       </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="M51">
+        <v>107533</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="3">
         <v>46177</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F52">
         <v>38.05</v>
@@ -2454,25 +3053,31 @@
       <c r="J52">
         <v>63.16</v>
       </c>
-      <c r="K52">
+      <c r="K52" t="s">
+        <v>103</v>
+      </c>
+      <c r="L52">
         <v>76516</v>
       </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="M52">
+        <v>214835</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="3">
         <v>46177</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E53" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F53">
         <v>6.37</v>
@@ -2489,25 +3094,31 @@
       <c r="J53">
         <v>10.57</v>
       </c>
-      <c r="K53">
+      <c r="K53" t="s">
+        <v>104</v>
+      </c>
+      <c r="L53">
         <v>82559</v>
       </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="M53">
+        <v>214862</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="3">
         <v>46177</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E54" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F54">
         <v>4.49</v>
@@ -2524,25 +3135,31 @@
       <c r="J54">
         <v>7.45</v>
       </c>
-      <c r="K54">
+      <c r="K54" t="s">
+        <v>105</v>
+      </c>
+      <c r="L54">
         <v>57175</v>
       </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="M54">
+        <v>214872</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="3">
         <v>46177</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D55" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E55" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F55">
         <v>3.5</v>
@@ -2559,95 +3176,113 @@
       <c r="J55">
         <v>5.81</v>
       </c>
-      <c r="K55">
+      <c r="K55" t="s">
+        <v>106</v>
+      </c>
+      <c r="L55">
         <v>73405</v>
       </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="M55">
+        <v>138566</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="3">
         <v>46178</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E56" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F56">
-        <v>20</v>
+        <v>29.01</v>
       </c>
       <c r="G56" s="1">
-        <v>1.54</v>
+        <v>0.73</v>
       </c>
       <c r="H56">
-        <v>30.8</v>
+        <v>21.18</v>
       </c>
       <c r="I56" s="1">
-        <v>1.57</v>
+        <v>0.74</v>
       </c>
       <c r="J56">
-        <v>31.4</v>
-      </c>
-      <c r="K56">
+        <v>21.47</v>
+      </c>
+      <c r="K56" t="s">
+        <v>107</v>
+      </c>
+      <c r="L56">
         <v>178683</v>
       </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="M56">
+        <v>138831</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="3">
         <v>46178</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D57" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F57">
-        <v>29.01</v>
+        <v>20</v>
       </c>
       <c r="G57" s="1">
-        <v>0.73</v>
+        <v>1.54</v>
       </c>
       <c r="H57">
-        <v>21.18</v>
+        <v>30.8</v>
       </c>
       <c r="I57" s="1">
-        <v>0.74</v>
+        <v>1.57</v>
       </c>
       <c r="J57">
-        <v>21.47</v>
-      </c>
-      <c r="K57">
+        <v>31.4</v>
+      </c>
+      <c r="K57" t="s">
+        <v>107</v>
+      </c>
+      <c r="L57">
         <v>178683</v>
       </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="M57">
+        <v>138831</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="3">
         <v>46178</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E58" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F58">
         <v>4.2</v>
@@ -2664,25 +3299,31 @@
       <c r="J58">
         <v>6.97</v>
       </c>
-      <c r="K58">
-        <v>57211</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="K58" t="s">
+        <v>108</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>215190</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="3">
         <v>46178</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E59" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F59">
         <v>5.87</v>
@@ -2699,25 +3340,31 @@
       <c r="J59">
         <v>9.74</v>
       </c>
-      <c r="K59">
+      <c r="K59" t="s">
+        <v>109</v>
+      </c>
+      <c r="L59">
         <v>36275</v>
       </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="M59">
+        <v>215203</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="3">
         <v>46178</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F60">
         <v>5.34</v>
@@ -2734,25 +3381,31 @@
       <c r="J60">
         <v>8.859999999999999</v>
       </c>
-      <c r="K60">
+      <c r="K60" t="s">
+        <v>110</v>
+      </c>
+      <c r="L60">
         <v>175319</v>
       </c>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="M60">
+        <v>215212</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="3">
         <v>46178</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D61" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E61" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F61">
         <v>11</v>
@@ -2769,25 +3422,31 @@
       <c r="J61">
         <v>18.26</v>
       </c>
-      <c r="K61">
-        <v>76553</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="K61" t="s">
+        <v>68</v>
+      </c>
+      <c r="L61">
+        <v>82602</v>
+      </c>
+      <c r="M61">
+        <v>215228</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="3">
         <v>46178</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E62" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F62">
         <v>5.27</v>
@@ -2804,25 +3463,31 @@
       <c r="J62">
         <v>8.75</v>
       </c>
-      <c r="K62">
-        <v>82602</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="K62" t="s">
+        <v>68</v>
+      </c>
+      <c r="L62">
+        <v>76553</v>
+      </c>
+      <c r="M62">
+        <v>215230</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="3">
         <v>46178</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D63" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E63" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F63">
         <v>4.94</v>
@@ -2839,25 +3504,31 @@
       <c r="J63">
         <v>8.199999999999999</v>
       </c>
-      <c r="K63">
+      <c r="K63" t="s">
+        <v>111</v>
+      </c>
+      <c r="L63">
         <v>188002</v>
       </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="M63">
+        <v>215232</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="3">
         <v>46178</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D64" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E64" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F64">
         <v>8.65</v>
@@ -2874,25 +3545,31 @@
       <c r="J64">
         <v>14.36</v>
       </c>
-      <c r="K64">
+      <c r="K64" t="s">
+        <v>112</v>
+      </c>
+      <c r="L64">
         <v>43311</v>
       </c>
-    </row>
-    <row r="65" spans="1:11">
+      <c r="M64">
+        <v>215236</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="3">
         <v>46178</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E65" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F65">
         <v>27.01</v>
@@ -2909,25 +3586,31 @@
       <c r="J65">
         <v>44.84</v>
       </c>
-      <c r="K65">
+      <c r="K65" t="s">
+        <v>113</v>
+      </c>
+      <c r="L65">
         <v>102675</v>
       </c>
-    </row>
-    <row r="66" spans="1:11">
+      <c r="M65">
+        <v>215243</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="3">
         <v>46178</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F66">
         <v>2</v>
@@ -2944,25 +3627,31 @@
       <c r="J66">
         <v>3.32</v>
       </c>
-      <c r="K66">
+      <c r="K66" t="s">
+        <v>70</v>
+      </c>
+      <c r="L66">
         <v>143219</v>
       </c>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="M66">
+        <v>215256</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="3">
         <v>46178</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D67" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E67" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F67">
         <v>2.68</v>
@@ -2979,25 +3668,31 @@
       <c r="J67">
         <v>4.45</v>
       </c>
-      <c r="K67">
+      <c r="K67" t="s">
+        <v>114</v>
+      </c>
+      <c r="L67">
         <v>187322</v>
       </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="M67">
+        <v>138909</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="3">
         <v>46178</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E68" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F68">
         <v>9.25</v>
@@ -3014,25 +3709,31 @@
       <c r="J68">
         <v>15.35</v>
       </c>
-      <c r="K68">
+      <c r="K68" t="s">
+        <v>115</v>
+      </c>
+      <c r="L68">
         <v>94046</v>
       </c>
-    </row>
-    <row r="69" spans="1:11">
+      <c r="M68">
+        <v>108091</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="3">
         <v>46178</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E69" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F69">
         <v>14</v>
@@ -3049,25 +3750,31 @@
       <c r="J69">
         <v>23.24</v>
       </c>
-      <c r="K69">
+      <c r="K69" t="s">
+        <v>116</v>
+      </c>
+      <c r="L69">
         <v>65587</v>
       </c>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="M69">
+        <v>108107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="3">
         <v>46178</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D70" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E70" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F70">
         <v>3.7</v>
@@ -3084,25 +3791,31 @@
       <c r="J70">
         <v>6.14</v>
       </c>
-      <c r="K70">
+      <c r="K70" t="s">
+        <v>117</v>
+      </c>
+      <c r="L70">
         <v>73426</v>
       </c>
-    </row>
-    <row r="71" spans="1:11">
+      <c r="M70">
+        <v>138948</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="3">
         <v>46179</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E71" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F71">
         <v>4.9</v>
@@ -3119,25 +3832,31 @@
       <c r="J71">
         <v>8.039999999999999</v>
       </c>
-      <c r="K71">
+      <c r="K71" t="s">
+        <v>118</v>
+      </c>
+      <c r="L71">
         <v>36302</v>
       </c>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="M71">
+        <v>215562</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="3">
         <v>46181</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E72" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F72">
         <v>49.3</v>
@@ -3154,25 +3873,31 @@
       <c r="J72">
         <v>80.84999999999999</v>
       </c>
-      <c r="K72">
+      <c r="K72" t="s">
+        <v>119</v>
+      </c>
+      <c r="L72">
         <v>337833</v>
       </c>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="M72">
+        <v>113241</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="3">
         <v>46181</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E73" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F73">
         <v>1.69</v>
@@ -3189,25 +3914,31 @@
       <c r="J73">
         <v>2.77</v>
       </c>
-      <c r="K73">
+      <c r="K73" t="s">
+        <v>120</v>
+      </c>
+      <c r="L73">
         <v>143233</v>
       </c>
-    </row>
-    <row r="74" spans="1:11">
+      <c r="M73">
+        <v>216327</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="3">
         <v>46181</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C74" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D74" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F74">
         <v>2.59</v>
@@ -3224,25 +3955,31 @@
       <c r="J74">
         <v>4.25</v>
       </c>
-      <c r="K74">
+      <c r="K74" t="s">
+        <v>121</v>
+      </c>
+      <c r="L74">
         <v>43337</v>
       </c>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="M74">
+        <v>139876</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="3">
         <v>46181</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D75" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E75" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F75">
         <v>13</v>
@@ -3259,25 +3996,31 @@
       <c r="J75">
         <v>21.32</v>
       </c>
-      <c r="K75">
+      <c r="K75" t="s">
+        <v>91</v>
+      </c>
+      <c r="L75">
         <v>102704</v>
       </c>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="M75">
+        <v>216344</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="3">
         <v>46181</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E76" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F76">
         <v>4.22</v>
@@ -3294,25 +4037,31 @@
       <c r="J76">
         <v>6.92</v>
       </c>
-      <c r="K76">
+      <c r="K76" t="s">
+        <v>122</v>
+      </c>
+      <c r="L76">
         <v>188028</v>
       </c>
-    </row>
-    <row r="77" spans="1:11">
+      <c r="M76">
+        <v>216354</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="3">
         <v>46181</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D77" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E77" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F77">
         <v>8</v>
@@ -3329,25 +4078,31 @@
       <c r="J77">
         <v>13.12</v>
       </c>
-      <c r="K77">
+      <c r="K77" t="s">
+        <v>123</v>
+      </c>
+      <c r="L77">
         <v>175386</v>
       </c>
-    </row>
-    <row r="78" spans="1:11">
+      <c r="M77">
+        <v>216362</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="3">
         <v>46181</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D78" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E78" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F78">
         <v>6.92</v>
@@ -3364,25 +4119,31 @@
       <c r="J78">
         <v>11.35</v>
       </c>
-      <c r="K78">
+      <c r="K78" t="s">
+        <v>74</v>
+      </c>
+      <c r="L78">
         <v>82667</v>
       </c>
-    </row>
-    <row r="79" spans="1:11">
+      <c r="M78">
+        <v>216369</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="3">
         <v>46181</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E79" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F79">
         <v>2.73</v>
@@ -3399,25 +4160,31 @@
       <c r="J79">
         <v>4.48</v>
       </c>
-      <c r="K79">
+      <c r="K79" t="s">
+        <v>75</v>
+      </c>
+      <c r="L79">
         <v>187340</v>
       </c>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="M79">
+        <v>139896</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="3">
         <v>46181</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E80" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F80">
         <v>5.62</v>
@@ -3434,25 +4201,31 @@
       <c r="J80">
         <v>9.220000000000001</v>
       </c>
-      <c r="K80">
+      <c r="K80" t="s">
+        <v>76</v>
+      </c>
+      <c r="L80">
         <v>94102</v>
       </c>
-    </row>
-    <row r="81" spans="1:11">
+      <c r="M80">
+        <v>109632</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" s="3">
         <v>46181</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D81" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E81" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F81">
         <v>5.5</v>
@@ -3469,25 +4242,31 @@
       <c r="J81">
         <v>9.02</v>
       </c>
-      <c r="K81">
+      <c r="K81" t="s">
+        <v>103</v>
+      </c>
+      <c r="L81">
         <v>73485</v>
       </c>
-    </row>
-    <row r="82" spans="1:11">
+      <c r="M81">
+        <v>109634</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
       <c r="A82" s="3">
         <v>46181</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E82" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F82">
         <v>4.9</v>
@@ -3504,25 +4283,31 @@
       <c r="J82">
         <v>8.039999999999999</v>
       </c>
-      <c r="K82">
+      <c r="K82" t="s">
+        <v>124</v>
+      </c>
+      <c r="L82">
         <v>36316</v>
       </c>
-    </row>
-    <row r="83" spans="1:11">
+      <c r="M82">
+        <v>216377</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
       <c r="A83" s="3">
         <v>46181</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D83" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E83" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F83">
         <v>4.27</v>
@@ -3539,25 +4324,31 @@
       <c r="J83">
         <v>7</v>
       </c>
-      <c r="K83">
+      <c r="K83" t="s">
+        <v>125</v>
+      </c>
+      <c r="L83">
         <v>57235</v>
       </c>
-    </row>
-    <row r="84" spans="1:11">
+      <c r="M83">
+        <v>216392</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
       <c r="A84" s="3">
         <v>46182</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E84" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F84">
         <v>7.79</v>
@@ -3574,25 +4365,31 @@
       <c r="J84">
         <v>12.78</v>
       </c>
-      <c r="K84">
+      <c r="K84" t="s">
+        <v>126</v>
+      </c>
+      <c r="L84">
         <v>36362</v>
       </c>
-    </row>
-    <row r="85" spans="1:11">
+      <c r="M84">
+        <v>216819</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13">
       <c r="A85" s="3">
         <v>46182</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C85" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D85" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E85" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F85">
         <v>4.42</v>
@@ -3609,25 +4406,31 @@
       <c r="J85">
         <v>7.25</v>
       </c>
-      <c r="K85">
+      <c r="K85" t="s">
+        <v>112</v>
+      </c>
+      <c r="L85">
         <v>43370</v>
       </c>
-    </row>
-    <row r="86" spans="1:11">
+      <c r="M85">
+        <v>140268</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
       <c r="A86" s="3">
         <v>46182</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E86" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F86">
         <v>4</v>
@@ -3644,25 +4447,31 @@
       <c r="J86">
         <v>6.56</v>
       </c>
-      <c r="K86">
+      <c r="K86" t="s">
+        <v>92</v>
+      </c>
+      <c r="L86">
         <v>175407</v>
       </c>
-    </row>
-    <row r="87" spans="1:11">
+      <c r="M86">
+        <v>216832</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
       <c r="A87" s="3">
         <v>46182</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E87" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F87">
         <v>2.18</v>
@@ -3679,25 +4488,31 @@
       <c r="J87">
         <v>3.58</v>
       </c>
-      <c r="K87">
+      <c r="K87" t="s">
+        <v>93</v>
+      </c>
+      <c r="L87">
         <v>143244</v>
       </c>
-    </row>
-    <row r="88" spans="1:11">
+      <c r="M87">
+        <v>216836</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
       <c r="A88" s="3">
         <v>46182</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D88" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E88" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F88">
         <v>25</v>
@@ -3714,25 +4529,31 @@
       <c r="J88">
         <v>41</v>
       </c>
-      <c r="K88">
+      <c r="K88" t="s">
+        <v>127</v>
+      </c>
+      <c r="L88">
         <v>102757</v>
       </c>
-    </row>
-    <row r="89" spans="1:11">
+      <c r="M88">
+        <v>216841</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
       <c r="A89" s="3">
         <v>46182</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D89" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E89" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F89">
         <v>4.15</v>
@@ -3749,25 +4570,31 @@
       <c r="J89">
         <v>6.81</v>
       </c>
-      <c r="K89">
+      <c r="K89" t="s">
+        <v>128</v>
+      </c>
+      <c r="L89">
         <v>188055</v>
       </c>
-    </row>
-    <row r="90" spans="1:11">
+      <c r="M89">
+        <v>216843</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
       <c r="A90" s="3">
         <v>46182</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E90" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F90">
         <v>2.58</v>
@@ -3784,25 +4611,31 @@
       <c r="J90">
         <v>4.23</v>
       </c>
-      <c r="K90">
+      <c r="K90" t="s">
+        <v>71</v>
+      </c>
+      <c r="L90">
         <v>187357</v>
       </c>
-    </row>
-    <row r="91" spans="1:11">
+      <c r="M90">
+        <v>140285</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
       <c r="A91" s="3">
         <v>46182</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D91" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E91" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F91">
         <v>5.02</v>
@@ -3819,25 +4652,31 @@
       <c r="J91">
         <v>7.83</v>
       </c>
-      <c r="K91">
+      <c r="K91" t="s">
+        <v>123</v>
+      </c>
+      <c r="L91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:11">
+      <c r="M91">
+        <v>140287</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13">
       <c r="A92" s="3">
         <v>46182</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D92" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E92" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F92">
         <v>6.6</v>
@@ -3854,25 +4693,31 @@
       <c r="J92">
         <v>10.82</v>
       </c>
-      <c r="K92">
+      <c r="K92" t="s">
+        <v>73</v>
+      </c>
+      <c r="L92">
         <v>76565</v>
       </c>
-    </row>
-    <row r="93" spans="1:11">
+      <c r="M92">
+        <v>216847</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13">
       <c r="A93" s="3">
         <v>46182</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D93" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E93" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F93">
         <v>15.81</v>
@@ -3889,25 +4734,31 @@
       <c r="J93">
         <v>25.93</v>
       </c>
-      <c r="K93">
+      <c r="K93" t="s">
+        <v>74</v>
+      </c>
+      <c r="L93">
         <v>65710</v>
       </c>
-    </row>
-    <row r="94" spans="1:11">
+      <c r="M93">
+        <v>110188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13">
       <c r="A94" s="3">
         <v>46182</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D94" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E94" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F94">
         <v>5.32</v>
@@ -3924,25 +4775,31 @@
       <c r="J94">
         <v>8.720000000000001</v>
       </c>
-      <c r="K94">
+      <c r="K94" t="s">
+        <v>129</v>
+      </c>
+      <c r="L94">
         <v>82669</v>
       </c>
-    </row>
-    <row r="95" spans="1:11">
+      <c r="M94">
+        <v>216850</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13">
       <c r="A95" s="3">
         <v>46182</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E95" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F95">
         <v>6.35</v>
@@ -3959,25 +4816,31 @@
       <c r="J95">
         <v>10.41</v>
       </c>
-      <c r="K95">
+      <c r="K95" t="s">
+        <v>129</v>
+      </c>
+      <c r="L95">
         <v>94126</v>
       </c>
-    </row>
-    <row r="96" spans="1:11">
+      <c r="M95">
+        <v>110193</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13">
       <c r="A96" s="3">
         <v>46182</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D96" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E96" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F96">
         <v>5.9</v>
@@ -3994,25 +4857,31 @@
       <c r="J96">
         <v>9.68</v>
       </c>
-      <c r="K96">
+      <c r="K96" t="s">
+        <v>130</v>
+      </c>
+      <c r="L96">
         <v>57267</v>
       </c>
-    </row>
-    <row r="97" spans="1:11">
+      <c r="M96">
+        <v>216860</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13">
       <c r="A97" s="3">
         <v>46182</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E97" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F97">
         <v>4.5</v>
@@ -4029,25 +4898,31 @@
       <c r="J97">
         <v>7.38</v>
       </c>
-      <c r="K97">
+      <c r="K97" t="s">
+        <v>131</v>
+      </c>
+      <c r="L97">
         <v>73450</v>
       </c>
-    </row>
-    <row r="98" spans="1:11">
+      <c r="M97">
+        <v>140340</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13">
       <c r="A98" s="3">
         <v>46183</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D98" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E98" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F98">
         <v>28.51</v>
@@ -4064,25 +4939,31 @@
       <c r="J98">
         <v>20.24</v>
       </c>
-      <c r="K98">
+      <c r="K98" t="s">
+        <v>132</v>
+      </c>
+      <c r="L98">
         <v>179168</v>
       </c>
-    </row>
-    <row r="99" spans="1:11">
+      <c r="M98">
+        <v>110531</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13">
       <c r="A99" s="3">
         <v>46183</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E99" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F99">
         <v>3.18</v>
@@ -4099,25 +4980,31 @@
       <c r="J99">
         <v>5.18</v>
       </c>
-      <c r="K99">
+      <c r="K99" t="s">
+        <v>100</v>
+      </c>
+      <c r="L99">
         <v>187388</v>
       </c>
-    </row>
-    <row r="100" spans="1:11">
+      <c r="M99">
+        <v>140604</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13">
       <c r="A100" s="3">
         <v>46183</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D100" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E100" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F100">
         <v>2.65</v>
@@ -4134,25 +5021,31 @@
       <c r="J100">
         <v>4.32</v>
       </c>
-      <c r="K100">
+      <c r="K100" t="s">
+        <v>133</v>
+      </c>
+      <c r="L100">
         <v>188069</v>
       </c>
-    </row>
-    <row r="101" spans="1:11">
+      <c r="M100">
+        <v>217282</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13">
       <c r="A101" s="3">
         <v>46183</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E101" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F101">
         <v>1.79</v>
@@ -4169,25 +5062,31 @@
       <c r="J101">
         <v>2.92</v>
       </c>
-      <c r="K101">
+      <c r="K101" t="s">
+        <v>134</v>
+      </c>
+      <c r="L101">
         <v>143255</v>
       </c>
-    </row>
-    <row r="102" spans="1:11">
+      <c r="M101">
+        <v>217289</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13">
       <c r="A102" s="3">
         <v>46183</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E102" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F102">
         <v>4.87</v>
@@ -4204,25 +5103,31 @@
       <c r="J102">
         <v>7.94</v>
       </c>
-      <c r="K102">
+      <c r="K102" t="s">
+        <v>92</v>
+      </c>
+      <c r="L102">
         <v>36374</v>
       </c>
-    </row>
-    <row r="103" spans="1:11">
+      <c r="M102">
+        <v>217296</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13">
       <c r="A103" s="3">
         <v>46183</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D103" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E103" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F103">
         <v>5.59</v>
@@ -4239,25 +5144,31 @@
       <c r="J103">
         <v>9.109999999999999</v>
       </c>
-      <c r="K103">
+      <c r="K103" t="s">
+        <v>135</v>
+      </c>
+      <c r="L103">
         <v>82748</v>
       </c>
-    </row>
-    <row r="104" spans="1:11">
+      <c r="M103">
+        <v>217302</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
       <c r="A104" s="3">
         <v>46183</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E104" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F104">
         <v>4</v>
@@ -4274,25 +5185,31 @@
       <c r="J104">
         <v>6.52</v>
       </c>
-      <c r="K104">
+      <c r="K104" t="s">
+        <v>93</v>
+      </c>
+      <c r="L104">
         <v>175441</v>
       </c>
-    </row>
-    <row r="105" spans="1:11">
+      <c r="M104">
+        <v>217304</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13">
       <c r="A105" s="3">
         <v>46183</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D105" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E105" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F105">
         <v>5.73</v>
@@ -4309,25 +5226,31 @@
       <c r="J105">
         <v>9.34</v>
       </c>
-      <c r="K105">
+      <c r="K105" t="s">
+        <v>136</v>
+      </c>
+      <c r="L105">
         <v>43406</v>
       </c>
-    </row>
-    <row r="106" spans="1:11">
+      <c r="M105">
+        <v>140623</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13">
       <c r="A106" s="3">
         <v>46183</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D106" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E106" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F106">
         <v>4.56</v>
@@ -4344,25 +5267,31 @@
       <c r="J106">
         <v>7.43</v>
       </c>
-      <c r="K106">
+      <c r="K106" t="s">
+        <v>72</v>
+      </c>
+      <c r="L106">
         <v>94155</v>
       </c>
-    </row>
-    <row r="107" spans="1:11">
+      <c r="M106">
+        <v>110768</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13">
       <c r="A107" s="3">
         <v>46183</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D107" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E107" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F107">
         <v>10</v>
@@ -4379,25 +5308,31 @@
       <c r="J107">
         <v>16.3</v>
       </c>
-      <c r="K107">
+      <c r="K107" t="s">
+        <v>73</v>
+      </c>
+      <c r="L107">
         <v>73566</v>
       </c>
-    </row>
-    <row r="108" spans="1:11">
+      <c r="M107">
+        <v>110771</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13">
       <c r="A108" s="3">
         <v>46183</v>
       </c>
       <c r="B108" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D108" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E108" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F108">
         <v>15.94</v>
@@ -4414,25 +5349,31 @@
       <c r="J108">
         <v>25.98</v>
       </c>
-      <c r="K108">
+      <c r="K108" t="s">
+        <v>129</v>
+      </c>
+      <c r="L108">
         <v>76614</v>
       </c>
-    </row>
-    <row r="109" spans="1:11">
+      <c r="M108">
+        <v>217321</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13">
       <c r="A109" s="3">
         <v>46183</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D109" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E109" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F109">
         <v>4.81</v>
@@ -4449,25 +5390,31 @@
       <c r="J109">
         <v>7.84</v>
       </c>
-      <c r="K109">
+      <c r="K109" t="s">
+        <v>137</v>
+      </c>
+      <c r="L109">
         <v>57292</v>
       </c>
-    </row>
-    <row r="110" spans="1:11">
+      <c r="M109">
+        <v>217323</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13">
       <c r="A110" s="3">
         <v>46183</v>
       </c>
       <c r="B110" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D110" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E110" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F110">
         <v>50</v>
@@ -4484,25 +5431,31 @@
       <c r="J110">
         <v>81.5</v>
       </c>
-      <c r="K110">
+      <c r="K110" t="s">
+        <v>138</v>
+      </c>
+      <c r="L110">
         <v>102873</v>
       </c>
-    </row>
-    <row r="111" spans="1:11">
+      <c r="M110">
+        <v>217334</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13">
       <c r="A111" s="3">
         <v>46184</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C111" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D111" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E111" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F111">
         <v>100.08</v>
@@ -4519,25 +5472,31 @@
       <c r="J111">
         <v>162.13</v>
       </c>
-      <c r="K111">
+      <c r="K111" t="s">
+        <v>139</v>
+      </c>
+      <c r="L111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:11">
+      <c r="M111">
+        <v>111333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13">
       <c r="A112" s="3">
         <v>46184</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D112" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E112" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F112">
         <v>200</v>
@@ -4554,25 +5513,31 @@
       <c r="J112">
         <v>312</v>
       </c>
-      <c r="K112">
+      <c r="K112" t="s">
+        <v>140</v>
+      </c>
+      <c r="L112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:11">
+      <c r="M112">
+        <v>111340</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13">
       <c r="A113" s="3">
         <v>46184</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E113" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F113">
         <v>8.75</v>
@@ -4589,25 +5554,31 @@
       <c r="J113">
         <v>14.18</v>
       </c>
-      <c r="K113">
+      <c r="K113" t="s">
+        <v>141</v>
+      </c>
+      <c r="L113">
         <v>36418</v>
       </c>
-    </row>
-    <row r="114" spans="1:11">
+      <c r="M113">
+        <v>217770</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13">
       <c r="A114" s="3">
         <v>46184</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D114" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E114" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F114">
         <v>21.76</v>
@@ -4624,25 +5595,31 @@
       <c r="J114">
         <v>35.25</v>
       </c>
-      <c r="K114">
+      <c r="K114" t="s">
+        <v>134</v>
+      </c>
+      <c r="L114">
         <v>65882</v>
       </c>
-    </row>
-    <row r="115" spans="1:11">
+      <c r="M114">
+        <v>217779</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13">
       <c r="A115" s="3">
         <v>46184</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C115" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D115" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E115" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F115">
         <v>3.13</v>
@@ -4659,25 +5636,31 @@
       <c r="J115">
         <v>5.07</v>
       </c>
-      <c r="K115">
+      <c r="K115" t="s">
+        <v>102</v>
+      </c>
+      <c r="L115">
         <v>187438</v>
       </c>
-    </row>
-    <row r="116" spans="1:11">
+      <c r="M115">
+        <v>141007</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13">
       <c r="A116" s="3">
         <v>46184</v>
       </c>
       <c r="B116" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E116" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F116">
         <v>3</v>
@@ -4694,25 +5677,31 @@
       <c r="J116">
         <v>4.86</v>
       </c>
-      <c r="K116">
+      <c r="K116" t="s">
+        <v>127</v>
+      </c>
+      <c r="L116">
         <v>175462</v>
       </c>
-    </row>
-    <row r="117" spans="1:11">
+      <c r="M116">
+        <v>217789</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13">
       <c r="A117" s="3">
         <v>46184</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D117" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E117" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F117">
         <v>5.56</v>
@@ -4729,25 +5718,31 @@
       <c r="J117">
         <v>9.01</v>
       </c>
-      <c r="K117">
+      <c r="K117" t="s">
+        <v>142</v>
+      </c>
+      <c r="L117">
         <v>188112</v>
       </c>
-    </row>
-    <row r="118" spans="1:11">
+      <c r="M117">
+        <v>217797</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13">
       <c r="A118" s="3">
         <v>46184</v>
       </c>
       <c r="B118" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D118" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E118" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F118">
         <v>8.869999999999999</v>
@@ -4764,25 +5759,31 @@
       <c r="J118">
         <v>14.37</v>
       </c>
-      <c r="K118">
+      <c r="K118" t="s">
+        <v>83</v>
+      </c>
+      <c r="L118">
         <v>57367</v>
       </c>
-    </row>
-    <row r="119" spans="1:11">
+      <c r="M118">
+        <v>217801</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13">
       <c r="A119" s="3">
         <v>46184</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D119" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E119" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F119">
         <v>7.85</v>
@@ -4799,25 +5800,31 @@
       <c r="J119">
         <v>12.72</v>
       </c>
-      <c r="K119">
+      <c r="K119" t="s">
+        <v>143</v>
+      </c>
+      <c r="L119">
         <v>43434</v>
       </c>
-    </row>
-    <row r="120" spans="1:11">
+      <c r="M119">
+        <v>217803</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13">
       <c r="A120" s="3">
         <v>46184</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D120" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E120" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F120">
         <v>4.8</v>
@@ -4834,25 +5841,31 @@
       <c r="J120">
         <v>7.78</v>
       </c>
-      <c r="K120">
+      <c r="K120" t="s">
+        <v>84</v>
+      </c>
+      <c r="L120">
         <v>82781</v>
       </c>
-    </row>
-    <row r="121" spans="1:11">
+      <c r="M120">
+        <v>217806</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13">
       <c r="A121" s="3">
         <v>46184</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D121" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E121" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F121">
         <v>3.67</v>
@@ -4869,25 +5882,31 @@
       <c r="J121">
         <v>5.95</v>
       </c>
-      <c r="K121">
+      <c r="K121" t="s">
+        <v>84</v>
+      </c>
+      <c r="L121">
         <v>94177</v>
       </c>
-    </row>
-    <row r="122" spans="1:11">
+      <c r="M121">
+        <v>111386</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13">
       <c r="A122" s="3">
         <v>46184</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D122" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E122" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F122">
         <v>16.23</v>
@@ -4904,25 +5923,31 @@
       <c r="J122">
         <v>26.29</v>
       </c>
-      <c r="K122">
+      <c r="K122" t="s">
+        <v>73</v>
+      </c>
+      <c r="L122">
         <v>76629</v>
       </c>
-    </row>
-    <row r="123" spans="1:11">
+      <c r="M122">
+        <v>217809</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13">
       <c r="A123" s="3">
         <v>46184</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D123" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E123" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F123">
         <v>5.5</v>
@@ -4939,25 +5964,31 @@
       <c r="J123">
         <v>8.91</v>
       </c>
-      <c r="K123">
-        <v>73600</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+      <c r="K123" t="s">
+        <v>144</v>
+      </c>
+      <c r="L123">
+        <v>102975</v>
+      </c>
+      <c r="M123">
+        <v>217813</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13">
       <c r="A124" s="3">
         <v>46184</v>
       </c>
       <c r="B124" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D124" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E124" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F124">
         <v>39.01</v>
@@ -4974,25 +6005,31 @@
       <c r="J124">
         <v>63.2</v>
       </c>
-      <c r="K124">
-        <v>102975</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
+      <c r="K124" t="s">
+        <v>145</v>
+      </c>
+      <c r="L124">
+        <v>73600</v>
+      </c>
+      <c r="M124">
+        <v>217815</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13">
       <c r="A125" s="3">
         <v>46185</v>
       </c>
       <c r="B125" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D125" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E125" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F125">
         <v>4.37</v>
@@ -5009,25 +6046,31 @@
       <c r="J125">
         <v>7.04</v>
       </c>
-      <c r="K125">
+      <c r="K125" t="s">
+        <v>146</v>
+      </c>
+      <c r="L125">
         <v>43461</v>
       </c>
-    </row>
-    <row r="126" spans="1:11">
+      <c r="M125">
+        <v>218122</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13">
       <c r="A126" s="3">
         <v>46185</v>
       </c>
       <c r="B126" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E126" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F126">
         <v>3.41</v>
@@ -5044,25 +6087,31 @@
       <c r="J126">
         <v>5.49</v>
       </c>
-      <c r="K126">
-        <v>143275</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
+      <c r="K126" t="s">
+        <v>147</v>
+      </c>
+      <c r="L126">
+        <v>4502</v>
+      </c>
+      <c r="M126">
+        <v>218136</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13">
       <c r="A127" s="3">
         <v>46185</v>
       </c>
       <c r="B127" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D127" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E127" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F127">
         <v>10</v>
@@ -5079,25 +6128,31 @@
       <c r="J127">
         <v>16.1</v>
       </c>
-      <c r="K127">
+      <c r="K127" t="s">
+        <v>107</v>
+      </c>
+      <c r="L127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:11">
+      <c r="M127">
+        <v>218151</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13">
       <c r="A128" s="3">
         <v>46185</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C128" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D128" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E128" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F128">
         <v>6.44</v>
@@ -5114,25 +6169,31 @@
       <c r="J128">
         <v>10.37</v>
       </c>
-      <c r="K128">
+      <c r="K128" t="s">
+        <v>148</v>
+      </c>
+      <c r="L128">
         <v>65921</v>
       </c>
-    </row>
-    <row r="129" spans="1:11">
+      <c r="M128">
+        <v>111832</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13">
       <c r="A129" s="3">
         <v>46185</v>
       </c>
       <c r="B129" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D129" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E129" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F129">
         <v>5.22</v>
@@ -5149,25 +6210,31 @@
       <c r="J129">
         <v>8.4</v>
       </c>
-      <c r="K129">
+      <c r="K129" t="s">
+        <v>139</v>
+      </c>
+      <c r="L129">
         <v>36440</v>
       </c>
-    </row>
-    <row r="130" spans="1:11">
+      <c r="M129">
+        <v>218201</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13">
       <c r="A130" s="3">
         <v>46185</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D130" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E130" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F130">
         <v>25</v>
@@ -5184,25 +6251,31 @@
       <c r="J130">
         <v>40.25</v>
       </c>
-      <c r="K130">
+      <c r="K130" t="s">
+        <v>149</v>
+      </c>
+      <c r="L130">
         <v>103050</v>
       </c>
-    </row>
-    <row r="131" spans="1:11">
+      <c r="M130">
+        <v>218205</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13">
       <c r="A131" s="3">
         <v>46185</v>
       </c>
       <c r="B131" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C131" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D131" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E131" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F131">
         <v>4.85</v>
@@ -5219,25 +6292,31 @@
       <c r="J131">
         <v>7.81</v>
       </c>
-      <c r="K131">
+      <c r="K131" t="s">
+        <v>150</v>
+      </c>
+      <c r="L131">
         <v>188141</v>
       </c>
-    </row>
-    <row r="132" spans="1:11">
+      <c r="M131">
+        <v>218207</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13">
       <c r="A132" s="3">
         <v>46185</v>
       </c>
       <c r="B132" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D132" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E132" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F132">
         <v>7</v>
@@ -5254,25 +6333,31 @@
       <c r="J132">
         <v>11.27</v>
       </c>
-      <c r="K132">
+      <c r="K132" t="s">
+        <v>151</v>
+      </c>
+      <c r="L132">
         <v>73635</v>
       </c>
-    </row>
-    <row r="133" spans="1:11">
+      <c r="M132">
+        <v>218210</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13">
       <c r="A133" s="3">
         <v>46185</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D133" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E133" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F133">
         <v>3.14</v>
@@ -5289,25 +6374,31 @@
       <c r="J133">
         <v>5.06</v>
       </c>
-      <c r="K133">
+      <c r="K133" t="s">
+        <v>126</v>
+      </c>
+      <c r="L133">
         <v>187442</v>
       </c>
-    </row>
-    <row r="134" spans="1:11">
+      <c r="M133">
+        <v>141372</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13">
       <c r="A134" s="3">
         <v>46185</v>
       </c>
       <c r="B134" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D134" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E134" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F134">
         <v>11.41</v>
@@ -5324,25 +6415,31 @@
       <c r="J134">
         <v>18.37</v>
       </c>
-      <c r="K134">
-        <v>76644</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11">
+      <c r="K134" t="s">
+        <v>102</v>
+      </c>
+      <c r="L134">
+        <v>268935</v>
+      </c>
+      <c r="M134">
+        <v>218220</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13">
       <c r="A135" s="3">
         <v>46185</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D135" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E135" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F135">
         <v>6.4</v>
@@ -5359,25 +6456,31 @@
       <c r="J135">
         <v>10.3</v>
       </c>
-      <c r="K135">
-        <v>82839</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11">
+      <c r="K135" t="s">
+        <v>84</v>
+      </c>
+      <c r="L135">
+        <v>89913</v>
+      </c>
+      <c r="M135">
+        <v>218235</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13">
       <c r="A136" s="3">
         <v>46185</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D136" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E136" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F136">
         <v>3.66</v>
@@ -5394,25 +6497,31 @@
       <c r="J136">
         <v>5.89</v>
       </c>
-      <c r="K136">
+      <c r="K136" t="s">
+        <v>129</v>
+      </c>
+      <c r="L136">
         <v>94206</v>
       </c>
-    </row>
-    <row r="137" spans="1:11">
+      <c r="M136">
+        <v>111906</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13">
       <c r="A137" s="3">
         <v>46185</v>
       </c>
       <c r="B137" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C137" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D137" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E137" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F137">
         <v>6.1</v>
@@ -5429,25 +6538,31 @@
       <c r="J137">
         <v>9.82</v>
       </c>
-      <c r="K137">
+      <c r="K137" t="s">
+        <v>152</v>
+      </c>
+      <c r="L137">
         <v>57402</v>
       </c>
-    </row>
-    <row r="138" spans="1:11">
+      <c r="M137">
+        <v>218246</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13">
       <c r="A138" s="3">
         <v>46186</v>
       </c>
       <c r="B138" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D138" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E138" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F138">
         <v>5.2</v>
@@ -5464,25 +6579,31 @@
       <c r="J138">
         <v>8.32</v>
       </c>
-      <c r="K138">
+      <c r="K138" t="s">
+        <v>153</v>
+      </c>
+      <c r="L138">
         <v>36464</v>
       </c>
-    </row>
-    <row r="139" spans="1:11">
+      <c r="M138">
+        <v>218536</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13">
       <c r="A139" s="3">
         <v>46188</v>
       </c>
       <c r="B139" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C139" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D139" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E139" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F139">
         <v>45</v>
@@ -5499,25 +6620,31 @@
       <c r="J139">
         <v>72</v>
       </c>
-      <c r="K139">
+      <c r="K139" t="s">
+        <v>154</v>
+      </c>
+      <c r="L139">
         <v>2188</v>
       </c>
-    </row>
-    <row r="140" spans="1:11">
+      <c r="M139">
+        <v>275411</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13">
       <c r="A140" s="3">
         <v>46188</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E140" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F140">
         <v>4</v>
@@ -5534,25 +6661,31 @@
       <c r="J140">
         <v>6.4</v>
       </c>
-      <c r="K140">
+      <c r="K140" t="s">
+        <v>140</v>
+      </c>
+      <c r="L140">
         <v>175494</v>
       </c>
-    </row>
-    <row r="141" spans="1:11">
+      <c r="M140">
+        <v>219366</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13">
       <c r="A141" s="3">
         <v>46188</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C141" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D141" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E141" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F141">
         <v>2.97</v>
@@ -5569,25 +6702,31 @@
       <c r="J141">
         <v>4.75</v>
       </c>
-      <c r="K141">
+      <c r="K141" t="s">
+        <v>91</v>
+      </c>
+      <c r="L141">
         <v>43486</v>
       </c>
-    </row>
-    <row r="142" spans="1:11">
+      <c r="M141">
+        <v>142318</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13">
       <c r="A142" s="3">
         <v>46188</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C142" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D142" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E142" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F142">
         <v>2.51</v>
@@ -5604,25 +6743,31 @@
       <c r="J142">
         <v>4.02</v>
       </c>
-      <c r="K142">
+      <c r="K142" t="s">
+        <v>155</v>
+      </c>
+      <c r="L142">
         <v>187459</v>
       </c>
-    </row>
-    <row r="143" spans="1:11">
+      <c r="M142">
+        <v>142324</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13">
       <c r="A143" s="3">
         <v>46188</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D143" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E143" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F143">
         <v>3.38</v>
@@ -5639,25 +6784,31 @@
       <c r="J143">
         <v>5.41</v>
       </c>
-      <c r="K143">
+      <c r="K143" t="s">
+        <v>155</v>
+      </c>
+      <c r="L143">
         <v>73463</v>
       </c>
-    </row>
-    <row r="144" spans="1:11">
+      <c r="M143">
+        <v>113415</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13">
       <c r="A144" s="3">
         <v>46188</v>
       </c>
       <c r="B144" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D144" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E144" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F144">
         <v>13.47</v>
@@ -5674,25 +6825,31 @@
       <c r="J144">
         <v>21.55</v>
       </c>
-      <c r="K144">
+      <c r="K144" t="s">
+        <v>83</v>
+      </c>
+      <c r="L144">
         <v>76690</v>
       </c>
-    </row>
-    <row r="145" spans="1:11">
+      <c r="M144">
+        <v>219400</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13">
       <c r="A145" s="3">
         <v>46188</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D145" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E145" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F145">
         <v>4.59</v>
@@ -5709,25 +6866,31 @@
       <c r="J145">
         <v>7.34</v>
       </c>
-      <c r="K145">
+      <c r="K145" t="s">
+        <v>143</v>
+      </c>
+      <c r="L145">
         <v>82868</v>
       </c>
-    </row>
-    <row r="146" spans="1:11">
+      <c r="M145">
+        <v>219402</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13">
       <c r="A146" s="3">
         <v>46188</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C146" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D146" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E146" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F146">
         <v>8.630000000000001</v>
@@ -5744,25 +6907,31 @@
       <c r="J146">
         <v>13.81</v>
       </c>
-      <c r="K146">
+      <c r="K146" t="s">
+        <v>156</v>
+      </c>
+      <c r="L146">
         <v>94206</v>
       </c>
-    </row>
-    <row r="147" spans="1:11">
+      <c r="M146">
+        <v>113427</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13">
       <c r="A147" s="3">
         <v>46188</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D147" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E147" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F147">
         <v>4.94</v>
@@ -5779,25 +6948,31 @@
       <c r="J147">
         <v>7.9</v>
       </c>
-      <c r="K147">
+      <c r="K147" t="s">
+        <v>115</v>
+      </c>
+      <c r="L147">
         <v>188173</v>
       </c>
-    </row>
-    <row r="148" spans="1:11">
+      <c r="M147">
+        <v>219410</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13">
       <c r="A148" s="3">
         <v>46188</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C148" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D148" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E148" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F148">
         <v>29.71</v>
@@ -5814,25 +6989,31 @@
       <c r="J148">
         <v>20.2</v>
       </c>
-      <c r="K148">
+      <c r="K148" t="s">
+        <v>157</v>
+      </c>
+      <c r="L148">
         <v>179539</v>
       </c>
-    </row>
-    <row r="149" spans="1:11">
+      <c r="M148">
+        <v>113443</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13">
       <c r="A149" s="3">
         <v>46188</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D149" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E149" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F149">
         <v>5</v>
@@ -5849,25 +7030,31 @@
       <c r="J149">
         <v>8</v>
       </c>
-      <c r="K149">
+      <c r="K149" t="s">
+        <v>158</v>
+      </c>
+      <c r="L149">
         <v>36480</v>
       </c>
-    </row>
-    <row r="150" spans="1:11">
+      <c r="M149">
+        <v>219421</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13">
       <c r="A150" s="3">
         <v>46188</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D150" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E150" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F150">
         <v>7.5</v>
@@ -5884,13 +7071,19 @@
       <c r="J150">
         <v>12</v>
       </c>
-      <c r="K150">
+      <c r="K150" t="s">
+        <v>159</v>
+      </c>
+      <c r="L150">
         <v>56457</v>
       </c>
-    </row>
-    <row r="153" spans="1:11">
+      <c r="M150">
+        <v>219456</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13">
       <c r="A153" s="4" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -5898,18 +7091,18 @@
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:13">
       <c r="A154" s="5" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>66</v>
+        <v>163</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>7</v>
@@ -5918,9 +7111,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:13">
       <c r="A155" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B155" s="7">
         <v>1310.21</v>
@@ -5938,9 +7131,9 @@
         <v>2157.38</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:13">
       <c r="A156" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B156" s="7">
         <v>425.05</v>
@@ -5958,9 +7151,9 @@
         <v>665.28</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:13">
       <c r="A157" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B157" s="7">
         <v>87.23</v>
@@ -5978,9 +7171,9 @@
         <v>61.91</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:13">
       <c r="A158" s="9" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="B158" s="10">
         <v>1822.49</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
@@ -980,7 +980,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -7900,7 +7900,7 @@
         <v>140</v>
       </c>
       <c r="D152" s="8">
-        <v>1.6812</v>
+        <v>1.681171</v>
       </c>
       <c r="E152" s="7">
         <v>2694.9</v>
@@ -7920,7 +7920,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="8">
-        <v>1.5112</v>
+        <v>1.511206</v>
       </c>
       <c r="E153" s="7">
         <v>343.21</v>
@@ -7940,7 +7940,7 @@
         <v>3</v>
       </c>
       <c r="D154" s="8">
-        <v>0.63</v>
+        <v>0.629966</v>
       </c>
       <c r="E154" s="7">
         <v>52.64</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="320">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -1372,7 +1375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N155"/>
+  <dimension ref="A1:O155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1385,13 +1388,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1434,6434 +1437,6875 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2">
-        <v>33.08</v>
+        <v>33.081</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2">
+        <v>1.499</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.58</v>
       </c>
-      <c r="I2" s="1">
-        <v>52.27</v>
-      </c>
       <c r="J2">
+        <v>52.26798</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.61</v>
       </c>
-      <c r="K2" s="1">
-        <v>53.26</v>
-      </c>
-      <c r="L2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>53.26041</v>
+      </c>
+      <c r="M2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N2">
         <v>78167</v>
       </c>
-      <c r="N2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3">
-        <v>9.17</v>
+        <v>9.167999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H3">
+        <v>1.499</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.58</v>
       </c>
-      <c r="I3" s="1">
-        <v>14.49</v>
-      </c>
       <c r="J3">
+        <v>14.48544</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.61</v>
       </c>
-      <c r="K3" s="1">
-        <v>14.76</v>
-      </c>
-      <c r="L3" t="s">
-        <v>72</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>14.76048</v>
+      </c>
+      <c r="M3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3">
         <v>95281</v>
       </c>
-      <c r="N3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4">
-        <v>9.029999999999999</v>
+        <v>9.031000000000001</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4">
+        <v>1.499</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.58</v>
       </c>
-      <c r="I4" s="1">
-        <v>14.27</v>
-      </c>
       <c r="J4">
+        <v>14.26898</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.61</v>
       </c>
-      <c r="K4" s="1">
-        <v>14.54</v>
-      </c>
-      <c r="L4" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>14.53991</v>
+      </c>
+      <c r="M4" t="s">
+        <v>74</v>
+      </c>
+      <c r="N4">
         <v>175883</v>
       </c>
-      <c r="N4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46219</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5">
-        <v>5.85</v>
+        <v>5.851</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H5">
+        <v>1.499</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.58</v>
       </c>
-      <c r="I5" s="1">
-        <v>9.24</v>
-      </c>
       <c r="J5">
+        <v>9.244579999999999</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.61</v>
       </c>
-      <c r="K5" s="1">
-        <v>9.42</v>
-      </c>
-      <c r="L5" t="s">
-        <v>74</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>9.420109999999999</v>
+      </c>
+      <c r="M5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5">
         <v>83832</v>
       </c>
-      <c r="N5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46219</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6">
         <v>3.36</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6">
+        <v>1.499</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.58</v>
       </c>
-      <c r="I6" s="1">
-        <v>5.31</v>
-      </c>
       <c r="J6">
+        <v>5.3088</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.61</v>
       </c>
-      <c r="K6" s="1">
-        <v>5.41</v>
-      </c>
-      <c r="L6" t="s">
-        <v>75</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>5.4096</v>
+      </c>
+      <c r="M6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N6">
         <v>188731</v>
       </c>
-      <c r="N6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46219</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7">
-        <v>2.75</v>
+        <v>2.752</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7">
+        <v>1.499</v>
+      </c>
+      <c r="I7" s="1">
         <v>1.58</v>
       </c>
-      <c r="I7" s="1">
-        <v>4.35</v>
-      </c>
       <c r="J7">
+        <v>4.34816</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.61</v>
       </c>
-      <c r="K7" s="1">
-        <v>4.43</v>
-      </c>
-      <c r="L7" t="s">
-        <v>76</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>4.43072</v>
+      </c>
+      <c r="M7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7">
         <v>143654</v>
       </c>
-      <c r="N7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46219</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8">
-        <v>8.57</v>
+        <v>8.571</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8">
+        <v>1.499</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.58</v>
       </c>
-      <c r="I8" s="1">
-        <v>13.54</v>
-      </c>
       <c r="J8">
+        <v>13.54218</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.61</v>
       </c>
-      <c r="K8" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="L8" t="s">
-        <v>77</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>13.79931</v>
+      </c>
+      <c r="M8" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8">
         <v>38716</v>
       </c>
-      <c r="N8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46219</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9">
+        <v>1.499</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.58</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>17.38</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>1.61</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>17.71</v>
       </c>
-      <c r="L9" t="s">
-        <v>78</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9">
         <v>8186</v>
       </c>
-      <c r="N9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46219</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10">
-        <v>6.7</v>
+        <v>6.702</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10">
+        <v>1.499</v>
+      </c>
+      <c r="I10" s="1">
         <v>1.58</v>
       </c>
-      <c r="I10" s="1">
-        <v>10.59</v>
-      </c>
       <c r="J10">
+        <v>10.58916</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.61</v>
       </c>
-      <c r="K10" s="1">
-        <v>10.79</v>
-      </c>
-      <c r="L10" t="s">
-        <v>79</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>10.79022</v>
+      </c>
+      <c r="M10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N10">
         <v>58110</v>
       </c>
-      <c r="N10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46219</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11">
-        <v>4.11</v>
+        <v>4.112</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H11">
+        <v>1.499</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.58</v>
       </c>
-      <c r="I11" s="1">
-        <v>6.49</v>
-      </c>
       <c r="J11">
+        <v>6.49696</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.61</v>
       </c>
-      <c r="K11" s="1">
-        <v>6.62</v>
-      </c>
-      <c r="L11" t="s">
-        <v>80</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>6.62032</v>
+      </c>
+      <c r="M11" t="s">
+        <v>81</v>
+      </c>
+      <c r="N11">
         <v>44138</v>
       </c>
-      <c r="N11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46219</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12">
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12">
+        <v>1.499</v>
+      </c>
+      <c r="I12" s="1">
         <v>1.58</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>9.48</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>1.61</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>9.66</v>
       </c>
-      <c r="L12" t="s">
-        <v>80</v>
-      </c>
-      <c r="M12">
+      <c r="M12" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12">
         <v>1170</v>
       </c>
-      <c r="N12" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46219</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13">
-        <v>4.5</v>
+        <v>4.503</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H13">
+        <v>1.499</v>
+      </c>
+      <c r="I13" s="1">
         <v>1.58</v>
       </c>
-      <c r="I13" s="1">
-        <v>7.11</v>
-      </c>
       <c r="J13">
+        <v>7.11474</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.61</v>
       </c>
-      <c r="K13" s="1">
-        <v>7.24</v>
-      </c>
-      <c r="L13" t="s">
-        <v>81</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>7.24983</v>
+      </c>
+      <c r="M13" t="s">
+        <v>82</v>
+      </c>
+      <c r="N13">
         <v>74495</v>
       </c>
-      <c r="N13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46219</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14">
-        <v>17.01</v>
+        <v>17.012</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H14">
+        <v>1.499</v>
+      </c>
+      <c r="I14" s="1">
         <v>1.58</v>
       </c>
-      <c r="I14" s="1">
-        <v>26.88</v>
-      </c>
       <c r="J14">
+        <v>26.87896</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.61</v>
       </c>
-      <c r="K14" s="1">
-        <v>27.39</v>
-      </c>
-      <c r="L14" t="s">
-        <v>82</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>27.38932</v>
+      </c>
+      <c r="M14" t="s">
+        <v>83</v>
+      </c>
+      <c r="N14">
         <v>67651</v>
       </c>
-      <c r="N14" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46220</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15">
-        <v>2.87</v>
+        <v>2.871</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H15">
+        <v>1.499</v>
+      </c>
+      <c r="I15" s="1">
         <v>1.6</v>
       </c>
-      <c r="I15" s="1">
-        <v>4.59</v>
-      </c>
       <c r="J15">
+        <v>4.5936</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.63</v>
       </c>
-      <c r="K15" s="1">
-        <v>4.68</v>
-      </c>
-      <c r="L15" t="s">
-        <v>83</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="1">
+        <v>4.67973</v>
+      </c>
+      <c r="M15" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15">
         <v>187950</v>
       </c>
-      <c r="N15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46220</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16">
-        <v>5.93</v>
+        <v>5.933</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H16">
+        <v>1.499</v>
+      </c>
+      <c r="I16" s="1">
         <v>1.6</v>
       </c>
-      <c r="I16" s="1">
-        <v>9.49</v>
-      </c>
       <c r="J16">
+        <v>9.492800000000001</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.63</v>
       </c>
-      <c r="K16" s="1">
-        <v>9.67</v>
-      </c>
-      <c r="L16" t="s">
-        <v>84</v>
-      </c>
-      <c r="M16">
+      <c r="L16" s="1">
+        <v>9.67079</v>
+      </c>
+      <c r="M16" t="s">
+        <v>85</v>
+      </c>
+      <c r="N16">
         <v>1192</v>
       </c>
-      <c r="N16" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46220</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17">
-        <v>5.06</v>
+        <v>5.061</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H17">
+        <v>1.499</v>
+      </c>
+      <c r="I17" s="1">
         <v>1.6</v>
       </c>
-      <c r="I17" s="1">
-        <v>8.1</v>
-      </c>
       <c r="J17">
+        <v>8.0976</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.63</v>
       </c>
-      <c r="K17" s="1">
-        <v>8.25</v>
-      </c>
-      <c r="L17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="1">
+        <v>8.24943</v>
+      </c>
+      <c r="M17" t="s">
+        <v>86</v>
+      </c>
+      <c r="N17">
         <v>83871</v>
       </c>
-      <c r="N17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46220</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18">
-        <v>2.5</v>
+        <v>2.503</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H18">
+        <v>1.499</v>
+      </c>
+      <c r="I18" s="1">
         <v>1.6</v>
       </c>
-      <c r="I18" s="1">
-        <v>4</v>
-      </c>
       <c r="J18">
+        <v>4.0048</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.63</v>
       </c>
-      <c r="K18" s="1">
-        <v>4.07</v>
-      </c>
-      <c r="L18" t="s">
-        <v>86</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>4.07989</v>
+      </c>
+      <c r="M18" t="s">
+        <v>87</v>
+      </c>
+      <c r="N18">
         <v>188745</v>
       </c>
-      <c r="N18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3">
         <v>46220</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19">
-        <v>1.5</v>
+        <v>1.503</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H19">
+        <v>1.499</v>
+      </c>
+      <c r="I19" s="1">
         <v>1.6</v>
       </c>
-      <c r="I19" s="1">
-        <v>2.4</v>
-      </c>
       <c r="J19">
+        <v>2.4048</v>
+      </c>
+      <c r="K19" s="1">
         <v>1.63</v>
       </c>
-      <c r="K19" s="1">
-        <v>2.44</v>
-      </c>
-      <c r="L19" t="s">
-        <v>87</v>
-      </c>
-      <c r="M19">
+      <c r="L19" s="1">
+        <v>2.44989</v>
+      </c>
+      <c r="M19" t="s">
+        <v>88</v>
+      </c>
+      <c r="N19">
         <v>38742</v>
       </c>
-      <c r="N19" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3">
         <v>46220</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F20">
-        <v>6.83</v>
+        <v>6.828</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H20">
+        <v>1.499</v>
+      </c>
+      <c r="I20" s="1">
         <v>1.6</v>
       </c>
-      <c r="I20" s="1">
-        <v>10.93</v>
-      </c>
       <c r="J20">
+        <v>10.9248</v>
+      </c>
+      <c r="K20" s="1">
         <v>1.63</v>
       </c>
-      <c r="K20" s="1">
-        <v>11.13</v>
-      </c>
-      <c r="L20" t="s">
-        <v>88</v>
-      </c>
-      <c r="M20">
+      <c r="L20" s="1">
+        <v>11.12964</v>
+      </c>
+      <c r="M20" t="s">
+        <v>89</v>
+      </c>
+      <c r="N20">
         <v>44174</v>
       </c>
-      <c r="N20" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3">
         <v>46220</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21">
         <v>4.84</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H21">
+        <v>1.499</v>
+      </c>
+      <c r="I21" s="1">
         <v>1.6</v>
       </c>
-      <c r="I21" s="1">
-        <v>7.74</v>
-      </c>
       <c r="J21">
+        <v>7.744</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.63</v>
       </c>
-      <c r="K21" s="1">
-        <v>7.89</v>
-      </c>
-      <c r="L21" t="s">
-        <v>89</v>
-      </c>
-      <c r="M21">
+      <c r="L21" s="1">
+        <v>7.8892</v>
+      </c>
+      <c r="M21" t="s">
+        <v>90</v>
+      </c>
+      <c r="N21">
         <v>143686</v>
       </c>
-      <c r="N21" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3">
         <v>46220</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F22">
-        <v>10.01</v>
+        <v>10.012</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H22">
+        <v>1.499</v>
+      </c>
+      <c r="I22" s="1">
         <v>1.6</v>
       </c>
-      <c r="I22" s="1">
-        <v>16.02</v>
-      </c>
       <c r="J22">
+        <v>16.0192</v>
+      </c>
+      <c r="K22" s="1">
         <v>1.63</v>
       </c>
-      <c r="K22" s="1">
-        <v>16.32</v>
-      </c>
-      <c r="L22" t="s">
-        <v>90</v>
-      </c>
-      <c r="M22">
+      <c r="L22" s="1">
+        <v>16.31956</v>
+      </c>
+      <c r="M22" t="s">
+        <v>91</v>
+      </c>
+      <c r="N22">
         <v>8202</v>
       </c>
-      <c r="N22" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3">
         <v>46220</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F23">
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H23">
+        <v>1.499</v>
+      </c>
+      <c r="I23" s="1">
         <v>1.6</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23">
         <v>62.4</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="1">
         <v>1.63</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>63.57</v>
       </c>
-      <c r="L23" t="s">
-        <v>91</v>
-      </c>
-      <c r="M23">
+      <c r="M23" t="s">
+        <v>92</v>
+      </c>
+      <c r="N23">
         <v>78268</v>
       </c>
-      <c r="N23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="3">
         <v>46220</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F24">
-        <v>7.75</v>
+        <v>7.748</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H24">
+        <v>1.499</v>
+      </c>
+      <c r="I24" s="1">
         <v>1.6</v>
       </c>
-      <c r="I24" s="1">
-        <v>12.4</v>
-      </c>
       <c r="J24">
+        <v>12.3968</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.63</v>
       </c>
-      <c r="K24" s="1">
-        <v>12.63</v>
-      </c>
-      <c r="L24" t="s">
-        <v>89</v>
-      </c>
-      <c r="M24">
+      <c r="L24" s="1">
+        <v>12.62924</v>
+      </c>
+      <c r="M24" t="s">
+        <v>90</v>
+      </c>
+      <c r="N24">
         <v>95351</v>
       </c>
-      <c r="N24" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="3">
         <v>46220</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H25">
+        <v>1.499</v>
+      </c>
+      <c r="I25" s="1">
         <v>1.6</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25">
         <v>8</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="1">
         <v>1.63</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>8.15</v>
       </c>
-      <c r="L25" t="s">
-        <v>72</v>
-      </c>
-      <c r="M25">
+      <c r="M25" t="s">
+        <v>73</v>
+      </c>
+      <c r="N25">
         <v>74529</v>
       </c>
-      <c r="N25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="3">
         <v>46220</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F26">
-        <v>37.37</v>
+        <v>37.368</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H26">
+        <v>1.499</v>
+      </c>
+      <c r="I26" s="1">
         <v>1.6</v>
       </c>
-      <c r="I26" s="1">
-        <v>59.79</v>
-      </c>
       <c r="J26">
+        <v>59.7888</v>
+      </c>
+      <c r="K26" s="1">
         <v>1.63</v>
       </c>
-      <c r="K26" s="1">
-        <v>60.91</v>
-      </c>
-      <c r="L26" t="s">
-        <v>92</v>
-      </c>
-      <c r="M26">
+      <c r="L26" s="1">
+        <v>60.90984</v>
+      </c>
+      <c r="M26" t="s">
+        <v>93</v>
+      </c>
+      <c r="N26">
         <v>2236</v>
       </c>
-      <c r="N26" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="3">
         <v>46221</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F27">
-        <v>3.62</v>
+        <v>3.618</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H27">
+        <v>1.528</v>
+      </c>
+      <c r="I27" s="1">
         <v>1.62</v>
       </c>
-      <c r="I27" s="1">
-        <v>5.86</v>
-      </c>
       <c r="J27">
+        <v>5.86116</v>
+      </c>
+      <c r="K27" s="1">
         <v>1.65</v>
       </c>
-      <c r="K27" s="1">
-        <v>5.97</v>
-      </c>
-      <c r="L27" t="s">
-        <v>93</v>
-      </c>
-      <c r="M27">
+      <c r="L27" s="1">
+        <v>5.9697</v>
+      </c>
+      <c r="M27" t="s">
+        <v>94</v>
+      </c>
+      <c r="N27">
         <v>58121</v>
       </c>
-      <c r="N27" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="3">
         <v>46221</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F28">
-        <v>7.01</v>
+        <v>7.012</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H28">
+        <v>1.528</v>
+      </c>
+      <c r="I28" s="1">
         <v>1.62</v>
       </c>
-      <c r="I28" s="1">
-        <v>11.36</v>
-      </c>
       <c r="J28">
+        <v>11.35944</v>
+      </c>
+      <c r="K28" s="1">
         <v>1.65</v>
       </c>
-      <c r="K28" s="1">
-        <v>11.57</v>
-      </c>
-      <c r="L28" t="s">
-        <v>94</v>
-      </c>
-      <c r="M28">
+      <c r="L28" s="1">
+        <v>11.5698</v>
+      </c>
+      <c r="M28" t="s">
+        <v>95</v>
+      </c>
+      <c r="N28">
         <v>1224</v>
       </c>
-      <c r="N28" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="3">
         <v>46223</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F29">
-        <v>2.51</v>
+        <v>2.512</v>
       </c>
       <c r="G29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H29">
+        <v>1.546</v>
+      </c>
+      <c r="I29" s="1">
         <v>1.65</v>
       </c>
-      <c r="I29" s="1">
-        <v>4.14</v>
-      </c>
       <c r="J29">
+        <v>4.1448</v>
+      </c>
+      <c r="K29" s="1">
         <v>1.68</v>
       </c>
-      <c r="K29" s="1">
-        <v>4.22</v>
-      </c>
-      <c r="L29" t="s">
-        <v>95</v>
-      </c>
-      <c r="M29">
+      <c r="L29" s="1">
+        <v>4.22016</v>
+      </c>
+      <c r="M29" t="s">
+        <v>96</v>
+      </c>
+      <c r="N29">
         <v>187971</v>
       </c>
-      <c r="N29" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="3">
         <v>46223</v>
       </c>
       <c r="B30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F30">
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H30">
+        <v>1.546</v>
+      </c>
+      <c r="I30" s="1">
         <v>1.65</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30">
         <v>33</v>
       </c>
-      <c r="J30">
+      <c r="K30" s="1">
         <v>1.68</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>33.6</v>
       </c>
-      <c r="L30" t="s">
-        <v>96</v>
-      </c>
-      <c r="M30">
+      <c r="M30" t="s">
+        <v>97</v>
+      </c>
+      <c r="N30">
         <v>78316</v>
       </c>
-      <c r="N30" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="3">
         <v>46223</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F31">
-        <v>2.98</v>
+        <v>2.982</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H31">
+        <v>1.546</v>
+      </c>
+      <c r="I31" s="1">
         <v>1.65</v>
       </c>
-      <c r="I31" s="1">
-        <v>4.92</v>
-      </c>
       <c r="J31">
+        <v>4.9203</v>
+      </c>
+      <c r="K31" s="1">
         <v>1.68</v>
       </c>
-      <c r="K31" s="1">
-        <v>5.01</v>
-      </c>
-      <c r="L31" t="s">
-        <v>97</v>
-      </c>
-      <c r="M31">
+      <c r="L31" s="1">
+        <v>5.00976</v>
+      </c>
+      <c r="M31" t="s">
+        <v>98</v>
+      </c>
+      <c r="N31">
         <v>143704</v>
       </c>
-      <c r="N31" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="3">
         <v>46223</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F32">
-        <v>13.95</v>
+        <v>13.952</v>
       </c>
       <c r="G32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H32">
+        <v>1.546</v>
+      </c>
+      <c r="I32" s="1">
         <v>1.65</v>
       </c>
-      <c r="I32" s="1">
-        <v>23.02</v>
-      </c>
       <c r="J32">
+        <v>23.0208</v>
+      </c>
+      <c r="K32" s="1">
         <v>1.68</v>
       </c>
-      <c r="K32" s="1">
-        <v>23.44</v>
-      </c>
-      <c r="L32" t="s">
-        <v>98</v>
-      </c>
-      <c r="M32">
+      <c r="L32" s="1">
+        <v>23.43936</v>
+      </c>
+      <c r="M32" t="s">
+        <v>99</v>
+      </c>
+      <c r="N32">
         <v>67743</v>
       </c>
-      <c r="N32" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="3">
         <v>46223</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F33">
-        <v>5.6</v>
+        <v>5.601</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H33">
+        <v>1.546</v>
+      </c>
+      <c r="I33" s="1">
         <v>1.65</v>
       </c>
-      <c r="I33" s="1">
-        <v>9.24</v>
-      </c>
       <c r="J33">
+        <v>9.24165</v>
+      </c>
+      <c r="K33" s="1">
         <v>1.68</v>
       </c>
-      <c r="K33" s="1">
-        <v>9.41</v>
-      </c>
-      <c r="L33" t="s">
-        <v>99</v>
-      </c>
-      <c r="M33">
+      <c r="L33" s="1">
+        <v>9.40968</v>
+      </c>
+      <c r="M33" t="s">
+        <v>100</v>
+      </c>
+      <c r="N33">
         <v>44204</v>
       </c>
-      <c r="N33" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="3">
         <v>46223</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F34">
         <v>2.47</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H34">
+        <v>1.546</v>
+      </c>
+      <c r="I34" s="1">
         <v>1.65</v>
       </c>
-      <c r="I34" s="1">
-        <v>4.08</v>
-      </c>
       <c r="J34">
+        <v>4.0755</v>
+      </c>
+      <c r="K34" s="1">
         <v>1.68</v>
       </c>
-      <c r="K34" s="1">
-        <v>4.15</v>
-      </c>
-      <c r="L34" t="s">
-        <v>100</v>
-      </c>
-      <c r="M34">
+      <c r="L34" s="1">
+        <v>4.1496</v>
+      </c>
+      <c r="M34" t="s">
+        <v>101</v>
+      </c>
+      <c r="N34">
         <v>188762</v>
       </c>
-      <c r="N34" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="3">
         <v>46223</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F35">
-        <v>6.7</v>
+        <v>6.702</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H35">
+        <v>1.546</v>
+      </c>
+      <c r="I35" s="1">
         <v>1.65</v>
       </c>
-      <c r="I35" s="1">
-        <v>11.06</v>
-      </c>
       <c r="J35">
+        <v>11.0583</v>
+      </c>
+      <c r="K35" s="1">
         <v>1.68</v>
       </c>
-      <c r="K35" s="1">
-        <v>11.26</v>
-      </c>
-      <c r="L35" t="s">
-        <v>101</v>
-      </c>
-      <c r="M35">
+      <c r="L35" s="1">
+        <v>11.25936</v>
+      </c>
+      <c r="M35" t="s">
+        <v>102</v>
+      </c>
+      <c r="N35">
         <v>95389</v>
       </c>
-      <c r="N35" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="3">
         <v>46223</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F36">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H36">
+        <v>1.546</v>
+      </c>
+      <c r="I36" s="1">
         <v>1.65</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36">
         <v>18.15</v>
       </c>
-      <c r="J36">
+      <c r="K36" s="1">
         <v>1.68</v>
       </c>
-      <c r="K36" s="1">
+      <c r="L36" s="1">
         <v>18.48</v>
       </c>
-      <c r="L36" t="s">
-        <v>102</v>
-      </c>
-      <c r="M36">
+      <c r="M36" t="s">
+        <v>103</v>
+      </c>
+      <c r="N36">
         <v>8218</v>
       </c>
-      <c r="N36" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="3">
         <v>46223</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F37">
-        <v>6.66</v>
+        <v>6.661</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H37">
+        <v>1.546</v>
+      </c>
+      <c r="I37" s="1">
         <v>1.65</v>
       </c>
-      <c r="I37" s="1">
-        <v>10.99</v>
-      </c>
       <c r="J37">
+        <v>10.99065</v>
+      </c>
+      <c r="K37" s="1">
         <v>1.68</v>
       </c>
-      <c r="K37" s="1">
-        <v>11.19</v>
-      </c>
-      <c r="L37" t="s">
-        <v>95</v>
-      </c>
-      <c r="M37">
+      <c r="L37" s="1">
+        <v>11.19048</v>
+      </c>
+      <c r="M37" t="s">
+        <v>96</v>
+      </c>
+      <c r="N37">
         <v>1243</v>
       </c>
-      <c r="N37" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="3">
         <v>46223</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F38">
         <v>3.5</v>
       </c>
       <c r="G38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H38">
+        <v>1.546</v>
+      </c>
+      <c r="I38" s="1">
         <v>1.65</v>
       </c>
-      <c r="I38" s="1">
-        <v>5.78</v>
-      </c>
       <c r="J38">
+        <v>5.775</v>
+      </c>
+      <c r="K38" s="1">
         <v>1.68</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>5.88</v>
       </c>
-      <c r="L38" t="s">
-        <v>103</v>
-      </c>
-      <c r="M38">
+      <c r="M38" t="s">
+        <v>104</v>
+      </c>
+      <c r="N38">
         <v>74577</v>
       </c>
-      <c r="N38" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="3">
         <v>46223</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F39">
-        <v>26.86</v>
+        <v>26.859</v>
       </c>
       <c r="G39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
         <v>0.63</v>
       </c>
-      <c r="I39" s="1">
-        <v>16.92</v>
-      </c>
       <c r="J39">
+        <v>16.92117</v>
+      </c>
+      <c r="K39" s="1">
         <v>0.64</v>
       </c>
-      <c r="K39" s="1">
-        <v>17.19</v>
-      </c>
-      <c r="L39" t="s">
-        <v>104</v>
-      </c>
-      <c r="M39">
+      <c r="L39" s="1">
+        <v>17.18976</v>
+      </c>
+      <c r="M39" t="s">
+        <v>105</v>
+      </c>
+      <c r="N39">
         <v>181437</v>
       </c>
-      <c r="N39" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="3">
         <v>46224</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F40">
-        <v>11.88</v>
+        <v>11.881</v>
       </c>
       <c r="G40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H40">
+        <v>1.564</v>
+      </c>
+      <c r="I40" s="1">
         <v>1.65</v>
       </c>
-      <c r="I40" s="1">
-        <v>19.6</v>
-      </c>
       <c r="J40">
+        <v>19.60365</v>
+      </c>
+      <c r="K40" s="1">
         <v>1.68</v>
       </c>
-      <c r="K40" s="1">
-        <v>19.96</v>
-      </c>
-      <c r="L40" t="s">
-        <v>105</v>
-      </c>
-      <c r="M40">
+      <c r="L40" s="1">
+        <v>19.96008</v>
+      </c>
+      <c r="M40" t="s">
+        <v>106</v>
+      </c>
+      <c r="N40">
         <v>1332</v>
       </c>
-      <c r="N40" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="3">
         <v>46224</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41">
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H41">
+        <v>1.564</v>
+      </c>
+      <c r="I41" s="1">
         <v>1.65</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41">
         <v>18.15</v>
       </c>
-      <c r="J41">
+      <c r="K41" s="1">
         <v>1.68</v>
       </c>
-      <c r="K41" s="1">
+      <c r="L41" s="1">
         <v>18.48</v>
       </c>
-      <c r="L41" t="s">
-        <v>78</v>
-      </c>
-      <c r="M41">
+      <c r="M41" t="s">
+        <v>79</v>
+      </c>
+      <c r="N41">
         <v>8241</v>
       </c>
-      <c r="N41" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="3">
         <v>46224</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F42">
-        <v>3.96</v>
+        <v>3.958</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H42">
+        <v>1.564</v>
+      </c>
+      <c r="I42" s="1">
         <v>1.65</v>
       </c>
-      <c r="I42" s="1">
-        <v>6.53</v>
-      </c>
       <c r="J42">
+        <v>6.5307</v>
+      </c>
+      <c r="K42" s="1">
         <v>1.68</v>
       </c>
-      <c r="K42" s="1">
-        <v>6.65</v>
-      </c>
-      <c r="L42" t="s">
-        <v>106</v>
-      </c>
-      <c r="M42">
+      <c r="L42" s="1">
+        <v>6.64944</v>
+      </c>
+      <c r="M42" t="s">
+        <v>107</v>
+      </c>
+      <c r="N42">
         <v>143730</v>
       </c>
-      <c r="N42" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="3">
         <v>46224</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F43">
-        <v>3.86</v>
+        <v>3.857</v>
       </c>
       <c r="G43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H43">
+        <v>1.564</v>
+      </c>
+      <c r="I43" s="1">
         <v>1.65</v>
       </c>
-      <c r="I43" s="1">
-        <v>6.37</v>
-      </c>
       <c r="J43">
+        <v>6.36405</v>
+      </c>
+      <c r="K43" s="1">
         <v>1.68</v>
       </c>
-      <c r="K43" s="1">
-        <v>6.48</v>
-      </c>
-      <c r="L43" t="s">
-        <v>107</v>
-      </c>
-      <c r="M43">
+      <c r="L43" s="1">
+        <v>6.47976</v>
+      </c>
+      <c r="M43" t="s">
+        <v>108</v>
+      </c>
+      <c r="N43">
         <v>188792</v>
       </c>
-      <c r="N43" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="3">
         <v>46224</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F44">
-        <v>4.9</v>
+        <v>4.899</v>
       </c>
       <c r="G44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H44">
+        <v>1.564</v>
+      </c>
+      <c r="I44" s="1">
         <v>1.65</v>
       </c>
-      <c r="I44" s="1">
-        <v>8.09</v>
-      </c>
       <c r="J44">
+        <v>8.083349999999999</v>
+      </c>
+      <c r="K44" s="1">
         <v>1.68</v>
       </c>
-      <c r="K44" s="1">
-        <v>8.23</v>
-      </c>
-      <c r="L44" t="s">
-        <v>108</v>
-      </c>
-      <c r="M44">
+      <c r="L44" s="1">
+        <v>8.230320000000001</v>
+      </c>
+      <c r="M44" t="s">
+        <v>109</v>
+      </c>
+      <c r="N44">
         <v>58157</v>
       </c>
-      <c r="N44" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="3">
         <v>46224</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E45" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F45">
         <v>7</v>
       </c>
       <c r="G45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H45">
+        <v>1.564</v>
+      </c>
+      <c r="I45" s="1">
         <v>1.65</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45">
         <v>11.55</v>
       </c>
-      <c r="J45">
+      <c r="K45" s="1">
         <v>1.68</v>
       </c>
-      <c r="K45" s="1">
+      <c r="L45" s="1">
         <v>11.76</v>
       </c>
-      <c r="L45" t="s">
-        <v>109</v>
-      </c>
-      <c r="M45">
+      <c r="M45" t="s">
+        <v>110</v>
+      </c>
+      <c r="N45">
         <v>175931</v>
       </c>
-      <c r="N45" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="3">
         <v>46224</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F46">
-        <v>3.93</v>
+        <v>3.929</v>
       </c>
       <c r="G46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H46">
+        <v>1.564</v>
+      </c>
+      <c r="I46" s="1">
         <v>1.65</v>
       </c>
-      <c r="I46" s="1">
-        <v>6.48</v>
-      </c>
       <c r="J46">
+        <v>6.48285</v>
+      </c>
+      <c r="K46" s="1">
         <v>1.68</v>
       </c>
-      <c r="K46" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="L46" t="s">
-        <v>96</v>
-      </c>
-      <c r="M46">
+      <c r="L46" s="1">
+        <v>6.60072</v>
+      </c>
+      <c r="M46" t="s">
+        <v>97</v>
+      </c>
+      <c r="N46">
         <v>44228</v>
       </c>
-      <c r="N46" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="3">
         <v>46224</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F47">
-        <v>2.39</v>
+        <v>2.393</v>
       </c>
       <c r="G47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H47">
+        <v>1.564</v>
+      </c>
+      <c r="I47" s="1">
         <v>1.65</v>
       </c>
-      <c r="I47" s="1">
-        <v>3.94</v>
-      </c>
       <c r="J47">
+        <v>3.94845</v>
+      </c>
+      <c r="K47" s="1">
         <v>1.68</v>
       </c>
-      <c r="K47" s="1">
-        <v>4.02</v>
-      </c>
-      <c r="L47" t="s">
-        <v>110</v>
-      </c>
-      <c r="M47">
+      <c r="L47" s="1">
+        <v>4.02024</v>
+      </c>
+      <c r="M47" t="s">
+        <v>111</v>
+      </c>
+      <c r="N47">
         <v>187996</v>
       </c>
-      <c r="N47" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="3">
         <v>46224</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F48">
         <v>34</v>
       </c>
       <c r="G48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H48">
+        <v>1.564</v>
+      </c>
+      <c r="I48" s="1">
         <v>1.65</v>
       </c>
-      <c r="I48" s="1">
+      <c r="J48">
         <v>56.1</v>
       </c>
-      <c r="J48">
+      <c r="K48" s="1">
         <v>1.68</v>
       </c>
-      <c r="K48" s="1">
+      <c r="L48" s="1">
         <v>57.12</v>
       </c>
-      <c r="L48" t="s">
-        <v>111</v>
-      </c>
-      <c r="M48">
+      <c r="M48" t="s">
+        <v>112</v>
+      </c>
+      <c r="N48">
         <v>78404</v>
       </c>
-      <c r="N48" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="3">
         <v>46224</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F49">
-        <v>3.51</v>
+        <v>3.512</v>
       </c>
       <c r="G49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H49">
+        <v>1.564</v>
+      </c>
+      <c r="I49" s="1">
         <v>1.65</v>
       </c>
-      <c r="I49" s="1">
-        <v>5.79</v>
-      </c>
       <c r="J49">
+        <v>5.7948</v>
+      </c>
+      <c r="K49" s="1">
         <v>1.68</v>
       </c>
-      <c r="K49" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="L49" t="s">
-        <v>112</v>
-      </c>
-      <c r="M49">
+      <c r="L49" s="1">
+        <v>5.90016</v>
+      </c>
+      <c r="M49" t="s">
+        <v>113</v>
+      </c>
+      <c r="N49">
         <v>74615</v>
       </c>
-      <c r="N49" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="3">
         <v>46224</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F50">
         <v>4.94</v>
       </c>
       <c r="G50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H50">
+        <v>1.564</v>
+      </c>
+      <c r="I50" s="1">
         <v>1.65</v>
       </c>
-      <c r="I50" s="1">
-        <v>8.15</v>
-      </c>
       <c r="J50">
+        <v>8.151</v>
+      </c>
+      <c r="K50" s="1">
         <v>1.68</v>
       </c>
-      <c r="K50" s="1">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L50" t="s">
-        <v>113</v>
-      </c>
-      <c r="M50">
+      <c r="L50" s="1">
+        <v>8.299200000000001</v>
+      </c>
+      <c r="M50" t="s">
+        <v>114</v>
+      </c>
+      <c r="N50">
         <v>95427</v>
       </c>
-      <c r="N50" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="3">
         <v>46224</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F51">
         <v>33.28</v>
       </c>
       <c r="G51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H51">
+        <v>1.564</v>
+      </c>
+      <c r="I51" s="1">
         <v>1.65</v>
       </c>
-      <c r="I51" s="1">
-        <v>54.91</v>
-      </c>
       <c r="J51">
+        <v>54.912</v>
+      </c>
+      <c r="K51" s="1">
         <v>1.68</v>
       </c>
-      <c r="K51" s="1">
-        <v>55.91</v>
-      </c>
-      <c r="L51" t="s">
-        <v>114</v>
-      </c>
-      <c r="M51">
+      <c r="L51" s="1">
+        <v>55.9104</v>
+      </c>
+      <c r="M51" t="s">
+        <v>115</v>
+      </c>
+      <c r="N51">
         <v>2243</v>
       </c>
-      <c r="N51" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="3">
         <v>46225</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F52">
-        <v>3.7</v>
+        <v>3.698</v>
       </c>
       <c r="G52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H52">
+        <v>1.588</v>
+      </c>
+      <c r="I52" s="1">
         <v>1.66</v>
       </c>
-      <c r="I52" s="1">
-        <v>6.14</v>
-      </c>
       <c r="J52">
+        <v>6.13868</v>
+      </c>
+      <c r="K52" s="1">
         <v>1.69</v>
       </c>
-      <c r="K52" s="1">
-        <v>6.25</v>
-      </c>
-      <c r="L52" t="s">
-        <v>107</v>
-      </c>
-      <c r="M52">
+      <c r="L52" s="1">
+        <v>6.24962</v>
+      </c>
+      <c r="M52" t="s">
+        <v>108</v>
+      </c>
+      <c r="N52">
         <v>188027</v>
       </c>
-      <c r="N52" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="3">
         <v>46225</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F53">
-        <v>5.61</v>
+        <v>5.609</v>
       </c>
       <c r="G53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H53">
+        <v>1.588</v>
+      </c>
+      <c r="I53" s="1">
         <v>1.66</v>
       </c>
-      <c r="I53" s="1">
-        <v>9.31</v>
-      </c>
       <c r="J53">
+        <v>9.31094</v>
+      </c>
+      <c r="K53" s="1">
         <v>1.69</v>
       </c>
-      <c r="K53" s="1">
-        <v>9.48</v>
-      </c>
-      <c r="L53" t="s">
-        <v>107</v>
-      </c>
-      <c r="M53">
+      <c r="L53" s="1">
+        <v>9.47921</v>
+      </c>
+      <c r="M53" t="s">
+        <v>108</v>
+      </c>
+      <c r="N53">
         <v>44270</v>
       </c>
-      <c r="N53" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="3">
         <v>46225</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E54" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F54">
-        <v>9.75</v>
+        <v>9.750999999999999</v>
       </c>
       <c r="G54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H54">
+        <v>1.588</v>
+      </c>
+      <c r="I54" s="1">
         <v>1.66</v>
       </c>
-      <c r="I54" s="1">
-        <v>16.18</v>
-      </c>
       <c r="J54">
+        <v>16.18666</v>
+      </c>
+      <c r="K54" s="1">
         <v>1.69</v>
       </c>
-      <c r="K54" s="1">
-        <v>16.48</v>
-      </c>
-      <c r="L54" t="s">
-        <v>115</v>
-      </c>
-      <c r="M54">
+      <c r="L54" s="1">
+        <v>16.47919</v>
+      </c>
+      <c r="M54" t="s">
+        <v>116</v>
+      </c>
+      <c r="N54">
         <v>1351</v>
       </c>
-      <c r="N54" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="3">
         <v>46225</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F55">
         <v>3.45</v>
       </c>
       <c r="G55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H55">
+        <v>1.588</v>
+      </c>
+      <c r="I55" s="1">
         <v>1.66</v>
       </c>
-      <c r="I55" s="1">
-        <v>5.73</v>
-      </c>
       <c r="J55">
+        <v>5.727</v>
+      </c>
+      <c r="K55" s="1">
         <v>1.69</v>
       </c>
-      <c r="K55" s="1">
-        <v>5.83</v>
-      </c>
-      <c r="L55" t="s">
-        <v>116</v>
-      </c>
-      <c r="M55">
+      <c r="L55" s="1">
+        <v>5.8305</v>
+      </c>
+      <c r="M55" t="s">
+        <v>117</v>
+      </c>
+      <c r="N55">
         <v>143753</v>
       </c>
-      <c r="N55" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="3">
         <v>46225</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E56" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F56">
-        <v>24.01</v>
+        <v>24.012</v>
       </c>
       <c r="G56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H56">
+        <v>1.588</v>
+      </c>
+      <c r="I56" s="1">
         <v>1.66</v>
       </c>
-      <c r="I56" s="1">
-        <v>39.86</v>
-      </c>
       <c r="J56">
+        <v>39.85992</v>
+      </c>
+      <c r="K56" s="1">
         <v>1.69</v>
       </c>
-      <c r="K56" s="1">
-        <v>40.58</v>
-      </c>
-      <c r="L56" t="s">
-        <v>117</v>
-      </c>
-      <c r="M56">
+      <c r="L56" s="1">
+        <v>40.58028</v>
+      </c>
+      <c r="M56" t="s">
+        <v>118</v>
+      </c>
+      <c r="N56">
         <v>78470</v>
       </c>
-      <c r="N56" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="O56" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="3">
         <v>46225</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E57" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F57">
-        <v>17.75</v>
+        <v>17.751</v>
       </c>
       <c r="G57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H57">
+        <v>1.588</v>
+      </c>
+      <c r="I57" s="1">
         <v>1.66</v>
       </c>
-      <c r="I57" s="1">
-        <v>29.46</v>
-      </c>
       <c r="J57">
+        <v>29.46666</v>
+      </c>
+      <c r="K57" s="1">
         <v>1.69</v>
       </c>
-      <c r="K57" s="1">
-        <v>30</v>
-      </c>
-      <c r="L57" t="s">
-        <v>83</v>
-      </c>
-      <c r="M57">
+      <c r="L57" s="1">
+        <v>29.99919</v>
+      </c>
+      <c r="M57" t="s">
+        <v>84</v>
+      </c>
+      <c r="N57">
         <v>74692</v>
       </c>
-      <c r="N57" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="O57" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="3">
         <v>46225</v>
       </c>
       <c r="B58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E58" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F58">
         <v>10</v>
       </c>
       <c r="G58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H58">
+        <v>1.588</v>
+      </c>
+      <c r="I58" s="1">
         <v>1.66</v>
       </c>
-      <c r="I58" s="1">
+      <c r="J58">
         <v>16.6</v>
       </c>
-      <c r="J58">
+      <c r="K58" s="1">
         <v>1.69</v>
       </c>
-      <c r="K58" s="1">
+      <c r="L58" s="1">
         <v>16.9</v>
       </c>
-      <c r="L58" t="s">
-        <v>118</v>
-      </c>
-      <c r="M58">
+      <c r="M58" t="s">
+        <v>119</v>
+      </c>
+      <c r="N58">
         <v>8254</v>
       </c>
-      <c r="N58" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
+      <c r="O58" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" s="3">
         <v>46225</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E59" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F59">
-        <v>5.7</v>
+        <v>5.698</v>
       </c>
       <c r="G59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H59">
+        <v>1.588</v>
+      </c>
+      <c r="I59" s="1">
         <v>1.66</v>
       </c>
-      <c r="I59" s="1">
-        <v>9.460000000000001</v>
-      </c>
       <c r="J59">
+        <v>9.458679999999999</v>
+      </c>
+      <c r="K59" s="1">
         <v>1.69</v>
       </c>
-      <c r="K59" s="1">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="L59" t="s">
-        <v>119</v>
-      </c>
-      <c r="M59">
+      <c r="L59" s="1">
+        <v>9.629619999999999</v>
+      </c>
+      <c r="M59" t="s">
+        <v>120</v>
+      </c>
+      <c r="N59">
         <v>58194</v>
       </c>
-      <c r="N59" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+      <c r="O59" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" s="3">
         <v>46225</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E60" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F60">
-        <v>16.65</v>
+        <v>16.651</v>
       </c>
       <c r="G60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H60">
+        <v>1.588</v>
+      </c>
+      <c r="I60" s="1">
         <v>1.66</v>
       </c>
-      <c r="I60" s="1">
-        <v>27.64</v>
-      </c>
       <c r="J60">
+        <v>27.64066</v>
+      </c>
+      <c r="K60" s="1">
         <v>1.69</v>
       </c>
-      <c r="K60" s="1">
-        <v>28.14</v>
-      </c>
-      <c r="L60" t="s">
-        <v>120</v>
-      </c>
-      <c r="M60">
+      <c r="L60" s="1">
+        <v>28.14019</v>
+      </c>
+      <c r="M60" t="s">
+        <v>121</v>
+      </c>
+      <c r="N60">
         <v>67874</v>
       </c>
-      <c r="N60" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
+      <c r="O60" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61" s="3">
         <v>46226</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F61">
-        <v>1.42</v>
+        <v>1.418</v>
       </c>
       <c r="G61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H61">
+        <v>1.588</v>
+      </c>
+      <c r="I61" s="1">
         <v>1.67</v>
       </c>
-      <c r="I61" s="1">
-        <v>2.37</v>
-      </c>
       <c r="J61">
+        <v>2.36806</v>
+      </c>
+      <c r="K61" s="1">
         <v>1.7</v>
       </c>
-      <c r="K61" s="1">
-        <v>2.41</v>
-      </c>
-      <c r="L61" t="s">
-        <v>121</v>
-      </c>
-      <c r="M61">
+      <c r="L61" s="1">
+        <v>2.4106</v>
+      </c>
+      <c r="M61" t="s">
+        <v>122</v>
+      </c>
+      <c r="N61">
         <v>44285</v>
       </c>
-      <c r="N61" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
+      <c r="O61" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" s="3">
         <v>46226</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E62" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F62">
-        <v>2.48</v>
+        <v>2.482</v>
       </c>
       <c r="G62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H62">
+        <v>1.588</v>
+      </c>
+      <c r="I62" s="1">
         <v>1.67</v>
       </c>
-      <c r="I62" s="1">
-        <v>4.14</v>
-      </c>
       <c r="J62">
+        <v>4.14494</v>
+      </c>
+      <c r="K62" s="1">
         <v>1.7</v>
       </c>
-      <c r="K62" s="1">
-        <v>4.22</v>
-      </c>
-      <c r="L62" t="s">
-        <v>122</v>
-      </c>
-      <c r="M62">
+      <c r="L62" s="1">
+        <v>4.2194</v>
+      </c>
+      <c r="M62" t="s">
+        <v>123</v>
+      </c>
+      <c r="N62">
         <v>188047</v>
       </c>
-      <c r="N62" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="O62" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" s="3">
         <v>46226</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F63">
-        <v>32.02</v>
+        <v>32.018</v>
       </c>
       <c r="G63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H63">
+        <v>1.588</v>
+      </c>
+      <c r="I63" s="1">
         <v>1.67</v>
       </c>
-      <c r="I63" s="1">
-        <v>53.47</v>
-      </c>
       <c r="J63">
+        <v>53.47006</v>
+      </c>
+      <c r="K63" s="1">
         <v>1.7</v>
       </c>
-      <c r="K63" s="1">
-        <v>54.43</v>
-      </c>
-      <c r="L63" t="s">
-        <v>123</v>
-      </c>
-      <c r="M63">
+      <c r="L63" s="1">
+        <v>54.4306</v>
+      </c>
+      <c r="M63" t="s">
+        <v>124</v>
+      </c>
+      <c r="N63">
         <v>78551</v>
       </c>
-      <c r="N63" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="O63" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" s="3">
         <v>46226</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F64">
-        <v>5.13</v>
+        <v>5.129</v>
       </c>
       <c r="G64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H64">
+        <v>1.588</v>
+      </c>
+      <c r="I64" s="1">
         <v>1.67</v>
       </c>
-      <c r="I64" s="1">
-        <v>8.57</v>
-      </c>
       <c r="J64">
+        <v>8.565429999999999</v>
+      </c>
+      <c r="K64" s="1">
         <v>1.7</v>
       </c>
-      <c r="K64" s="1">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="L64" t="s">
-        <v>107</v>
-      </c>
-      <c r="M64">
+      <c r="L64" s="1">
+        <v>8.7193</v>
+      </c>
+      <c r="M64" t="s">
+        <v>108</v>
+      </c>
+      <c r="N64">
         <v>175972</v>
       </c>
-      <c r="N64" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="O64" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" s="3">
         <v>46226</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F65">
-        <v>4.24</v>
+        <v>4.241</v>
       </c>
       <c r="G65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H65">
+        <v>1.588</v>
+      </c>
+      <c r="I65" s="1">
         <v>1.67</v>
       </c>
-      <c r="I65" s="1">
-        <v>7.08</v>
-      </c>
       <c r="J65">
+        <v>7.08247</v>
+      </c>
+      <c r="K65" s="1">
         <v>1.7</v>
       </c>
-      <c r="K65" s="1">
-        <v>7.21</v>
-      </c>
-      <c r="L65" t="s">
-        <v>124</v>
-      </c>
-      <c r="M65">
+      <c r="L65" s="1">
+        <v>7.2097</v>
+      </c>
+      <c r="M65" t="s">
+        <v>125</v>
+      </c>
+      <c r="N65">
         <v>143777</v>
       </c>
-      <c r="N65" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="O65" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" s="3">
         <v>46226</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D66" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F66">
-        <v>9.09</v>
+        <v>9.087999999999999</v>
       </c>
       <c r="G66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H66">
+        <v>1.588</v>
+      </c>
+      <c r="I66" s="1">
         <v>1.67</v>
       </c>
-      <c r="I66" s="1">
-        <v>15.18</v>
-      </c>
       <c r="J66">
+        <v>15.17696</v>
+      </c>
+      <c r="K66" s="1">
         <v>1.7</v>
       </c>
-      <c r="K66" s="1">
-        <v>15.45</v>
-      </c>
-      <c r="L66" t="s">
-        <v>125</v>
-      </c>
-      <c r="M66">
+      <c r="L66" s="1">
+        <v>15.4496</v>
+      </c>
+      <c r="M66" t="s">
+        <v>126</v>
+      </c>
+      <c r="N66">
         <v>10403</v>
       </c>
-      <c r="N66" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="O66" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" s="3">
         <v>46226</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D67" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F67">
         <v>5</v>
       </c>
       <c r="G67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H67">
+        <v>1.588</v>
+      </c>
+      <c r="I67" s="1">
         <v>1.67</v>
       </c>
-      <c r="I67" s="1">
+      <c r="J67">
         <v>8.35</v>
       </c>
-      <c r="J67">
+      <c r="K67" s="1">
         <v>1.7</v>
       </c>
-      <c r="K67" s="1">
+      <c r="L67" s="1">
         <v>8.5</v>
       </c>
-      <c r="L67" t="s">
-        <v>102</v>
-      </c>
-      <c r="M67">
+      <c r="M67" t="s">
+        <v>103</v>
+      </c>
+      <c r="N67">
         <v>188817</v>
       </c>
-      <c r="N67" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+      <c r="O67" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" s="3">
         <v>46226</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D68" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E68" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F68">
         <v>8.6</v>
       </c>
       <c r="G68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H68">
+        <v>1.588</v>
+      </c>
+      <c r="I68" s="1">
         <v>1.67</v>
       </c>
-      <c r="I68" s="1">
-        <v>14.36</v>
-      </c>
       <c r="J68">
+        <v>14.362</v>
+      </c>
+      <c r="K68" s="1">
         <v>1.7</v>
       </c>
-      <c r="K68" s="1">
+      <c r="L68" s="1">
         <v>14.62</v>
       </c>
-      <c r="L68" t="s">
-        <v>126</v>
-      </c>
-      <c r="M68">
+      <c r="M68" t="s">
+        <v>127</v>
+      </c>
+      <c r="N68">
         <v>58258</v>
       </c>
-      <c r="N68" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+      <c r="O68" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" s="3">
         <v>46226</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D69" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E69" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F69">
         <v>8</v>
       </c>
       <c r="G69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H69">
+        <v>1.588</v>
+      </c>
+      <c r="I69" s="1">
         <v>1.67</v>
       </c>
-      <c r="I69" s="1">
+      <c r="J69">
         <v>13.36</v>
       </c>
-      <c r="J69">
+      <c r="K69" s="1">
         <v>1.7</v>
       </c>
-      <c r="K69" s="1">
+      <c r="L69" s="1">
         <v>13.6</v>
       </c>
-      <c r="L69" t="s">
-        <v>127</v>
-      </c>
-      <c r="M69">
+      <c r="M69" t="s">
+        <v>128</v>
+      </c>
+      <c r="N69">
         <v>74753</v>
       </c>
-      <c r="N69" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+      <c r="O69" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" s="3">
         <v>46227</v>
       </c>
       <c r="B70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F70">
         <v>24</v>
       </c>
       <c r="G70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H70">
+        <v>1.619</v>
+      </c>
+      <c r="I70" s="1">
         <v>1.69</v>
       </c>
-      <c r="I70" s="1">
+      <c r="J70">
         <v>40.56</v>
       </c>
-      <c r="J70">
+      <c r="K70" s="1">
         <v>1.72</v>
       </c>
-      <c r="K70" s="1">
+      <c r="L70" s="1">
         <v>41.28</v>
       </c>
-      <c r="L70" t="s">
-        <v>128</v>
-      </c>
-      <c r="M70">
+      <c r="M70" t="s">
+        <v>129</v>
+      </c>
+      <c r="N70">
         <v>78612</v>
       </c>
-      <c r="N70" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="O70" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" s="3">
         <v>46227</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D71" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E71" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F71">
-        <v>2.72</v>
+        <v>2.721</v>
       </c>
       <c r="G71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H71">
+        <v>1.619</v>
+      </c>
+      <c r="I71" s="1">
         <v>1.69</v>
       </c>
-      <c r="I71" s="1">
-        <v>4.6</v>
-      </c>
       <c r="J71">
+        <v>4.59849</v>
+      </c>
+      <c r="K71" s="1">
         <v>1.72</v>
       </c>
-      <c r="K71" s="1">
-        <v>4.68</v>
-      </c>
-      <c r="L71" t="s">
-        <v>129</v>
-      </c>
-      <c r="M71">
+      <c r="L71" s="1">
+        <v>4.68012</v>
+      </c>
+      <c r="M71" t="s">
+        <v>130</v>
+      </c>
+      <c r="N71">
         <v>188834</v>
       </c>
-      <c r="N71" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
+      <c r="O71" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="3">
         <v>46227</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D72" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E72" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F72">
-        <v>5.95</v>
+        <v>5.948</v>
       </c>
       <c r="G72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H72">
+        <v>1.619</v>
+      </c>
+      <c r="I72" s="1">
         <v>1.69</v>
       </c>
-      <c r="I72" s="1">
-        <v>10.06</v>
-      </c>
       <c r="J72">
+        <v>10.05212</v>
+      </c>
+      <c r="K72" s="1">
         <v>1.72</v>
       </c>
-      <c r="K72" s="1">
-        <v>10.23</v>
-      </c>
-      <c r="L72" t="s">
-        <v>97</v>
-      </c>
-      <c r="M72">
+      <c r="L72" s="1">
+        <v>10.23056</v>
+      </c>
+      <c r="M72" t="s">
+        <v>98</v>
+      </c>
+      <c r="N72">
         <v>44317</v>
       </c>
-      <c r="N72" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
+      <c r="O72" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" s="3">
         <v>46227</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E73" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F73">
         <v>6.89</v>
       </c>
       <c r="G73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H73">
+        <v>1.619</v>
+      </c>
+      <c r="I73" s="1">
         <v>1.69</v>
       </c>
-      <c r="I73" s="1">
-        <v>11.64</v>
-      </c>
       <c r="J73">
+        <v>11.6441</v>
+      </c>
+      <c r="K73" s="1">
         <v>1.72</v>
       </c>
-      <c r="K73" s="1">
-        <v>11.85</v>
-      </c>
-      <c r="L73" t="s">
-        <v>110</v>
-      </c>
-      <c r="M73">
+      <c r="L73" s="1">
+        <v>11.8508</v>
+      </c>
+      <c r="M73" t="s">
+        <v>111</v>
+      </c>
+      <c r="N73">
         <v>1433</v>
       </c>
-      <c r="N73" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14">
+      <c r="O73" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74" s="3">
         <v>46227</v>
       </c>
       <c r="B74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F74">
-        <v>6.65</v>
+        <v>6.651</v>
       </c>
       <c r="G74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H74">
+        <v>1.619</v>
+      </c>
+      <c r="I74" s="1">
         <v>1.69</v>
       </c>
-      <c r="I74" s="1">
-        <v>11.24</v>
-      </c>
       <c r="J74">
+        <v>11.24019</v>
+      </c>
+      <c r="K74" s="1">
         <v>1.72</v>
       </c>
-      <c r="K74" s="1">
-        <v>11.44</v>
-      </c>
-      <c r="L74" t="s">
-        <v>130</v>
-      </c>
-      <c r="M74">
+      <c r="L74" s="1">
+        <v>11.43972</v>
+      </c>
+      <c r="M74" t="s">
+        <v>131</v>
+      </c>
+      <c r="N74">
         <v>95464</v>
       </c>
-      <c r="N74" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14">
+      <c r="O74" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75" s="3">
         <v>46227</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F75">
         <v>3.11</v>
       </c>
       <c r="G75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H75">
+        <v>1.619</v>
+      </c>
+      <c r="I75" s="1">
         <v>1.69</v>
       </c>
-      <c r="I75" s="1">
-        <v>5.26</v>
-      </c>
       <c r="J75">
+        <v>5.2559</v>
+      </c>
+      <c r="K75" s="1">
         <v>1.72</v>
       </c>
-      <c r="K75" s="1">
-        <v>5.35</v>
-      </c>
-      <c r="L75" t="s">
-        <v>131</v>
-      </c>
-      <c r="M75">
+      <c r="L75" s="1">
+        <v>5.3492</v>
+      </c>
+      <c r="M75" t="s">
+        <v>132</v>
+      </c>
+      <c r="N75">
         <v>188076</v>
       </c>
-      <c r="N75" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14">
+      <c r="O75" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76" s="3">
         <v>46227</v>
       </c>
       <c r="B76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D76" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F76">
         <v>5</v>
       </c>
       <c r="G76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H76">
+        <v>1.619</v>
+      </c>
+      <c r="I76" s="1">
         <v>1.69</v>
       </c>
-      <c r="I76" s="1">
+      <c r="J76">
         <v>8.449999999999999</v>
       </c>
-      <c r="J76">
+      <c r="K76" s="1">
         <v>1.72</v>
       </c>
-      <c r="K76" s="1">
+      <c r="L76" s="1">
         <v>8.6</v>
       </c>
-      <c r="L76" t="s">
-        <v>132</v>
-      </c>
-      <c r="M76">
+      <c r="M76" t="s">
+        <v>133</v>
+      </c>
+      <c r="N76">
         <v>74799</v>
       </c>
-      <c r="N76" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14">
+      <c r="O76" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
       <c r="A77" s="3">
         <v>46227</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E77" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F77">
-        <v>100.04</v>
+        <v>100.041</v>
       </c>
       <c r="G77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H77">
+        <v>1.619</v>
+      </c>
+      <c r="I77" s="1">
         <v>1.69</v>
       </c>
-      <c r="I77" s="1">
-        <v>169.07</v>
-      </c>
       <c r="J77">
+        <v>169.06929</v>
+      </c>
+      <c r="K77" s="1">
         <v>1.72</v>
       </c>
-      <c r="K77" s="1">
-        <v>172.07</v>
-      </c>
-      <c r="L77" t="s">
-        <v>133</v>
-      </c>
-      <c r="M77">
+      <c r="L77" s="1">
+        <v>172.07052</v>
+      </c>
+      <c r="M77" t="s">
+        <v>134</v>
+      </c>
+      <c r="N77">
         <v>0</v>
       </c>
-      <c r="N77" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14">
+      <c r="O77" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" s="3">
         <v>46227</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D78" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E78" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F78">
-        <v>100.08</v>
+        <v>100.081</v>
       </c>
       <c r="G78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H78">
+        <v>1.619</v>
+      </c>
+      <c r="I78" s="1">
         <v>1.69</v>
       </c>
-      <c r="I78" s="1">
-        <v>169.14</v>
-      </c>
       <c r="J78">
+        <v>169.13689</v>
+      </c>
+      <c r="K78" s="1">
         <v>1.72</v>
       </c>
-      <c r="K78" s="1">
-        <v>172.14</v>
-      </c>
-      <c r="L78" t="s">
-        <v>134</v>
-      </c>
-      <c r="M78">
+      <c r="L78" s="1">
+        <v>172.13932</v>
+      </c>
+      <c r="M78" t="s">
+        <v>135</v>
+      </c>
+      <c r="N78">
         <v>0</v>
       </c>
-      <c r="N78" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
+      <c r="O78" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
       <c r="A79" s="3">
         <v>46227</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D79" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E79" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F79">
         <v>6</v>
       </c>
       <c r="G79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H79">
+        <v>1.619</v>
+      </c>
+      <c r="I79" s="1">
         <v>1.69</v>
       </c>
-      <c r="I79" s="1">
+      <c r="J79">
         <v>10.14</v>
       </c>
-      <c r="J79">
+      <c r="K79" s="1">
         <v>1.72</v>
       </c>
-      <c r="K79" s="1">
+      <c r="L79" s="1">
         <v>10.32</v>
       </c>
-      <c r="L79" t="s">
-        <v>94</v>
-      </c>
-      <c r="M79">
+      <c r="M79" t="s">
+        <v>95</v>
+      </c>
+      <c r="N79">
         <v>38765</v>
       </c>
-      <c r="N79" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14">
+      <c r="O79" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
       <c r="A80" s="3">
         <v>46227</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F80">
-        <v>200.02</v>
+        <v>200.019</v>
       </c>
       <c r="G80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H80">
+        <v>1.401</v>
+      </c>
+      <c r="I80" s="1">
         <v>1.51</v>
       </c>
-      <c r="I80" s="1">
-        <v>302.03</v>
-      </c>
       <c r="J80">
+        <v>302.02869</v>
+      </c>
+      <c r="K80" s="1">
         <v>1.54</v>
       </c>
-      <c r="K80" s="1">
-        <v>308.03</v>
-      </c>
-      <c r="L80" t="s">
-        <v>135</v>
-      </c>
-      <c r="M80">
+      <c r="L80" s="1">
+        <v>308.02926</v>
+      </c>
+      <c r="M80" t="s">
+        <v>136</v>
+      </c>
+      <c r="N80">
         <v>0</v>
       </c>
-      <c r="N80" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14">
+      <c r="O80" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
       <c r="A81" s="3">
         <v>46227</v>
       </c>
       <c r="B81" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E81" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F81">
-        <v>39.79</v>
+        <v>39.791</v>
       </c>
       <c r="G81" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H81">
+        <v>1.619</v>
+      </c>
+      <c r="I81" s="1">
         <v>1.69</v>
       </c>
-      <c r="I81" s="1">
-        <v>67.25</v>
-      </c>
       <c r="J81">
+        <v>67.24679</v>
+      </c>
+      <c r="K81" s="1">
         <v>1.72</v>
       </c>
-      <c r="K81" s="1">
-        <v>68.44</v>
-      </c>
-      <c r="L81" t="s">
-        <v>136</v>
-      </c>
-      <c r="M81">
+      <c r="L81" s="1">
+        <v>68.44052000000001</v>
+      </c>
+      <c r="M81" t="s">
+        <v>137</v>
+      </c>
+      <c r="N81">
         <v>2251</v>
       </c>
-      <c r="N81" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14">
+      <c r="O81" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
       <c r="A82" s="3">
         <v>46228</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D82" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E82" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F82">
-        <v>7.61</v>
+        <v>7.609</v>
       </c>
       <c r="G82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H82">
+        <v>1.619</v>
+      </c>
+      <c r="I82" s="1">
         <v>1.71</v>
       </c>
-      <c r="I82" s="1">
-        <v>13.01</v>
-      </c>
       <c r="J82">
+        <v>13.01139</v>
+      </c>
+      <c r="K82" s="1">
         <v>1.74</v>
       </c>
-      <c r="K82" s="1">
-        <v>13.24</v>
-      </c>
-      <c r="L82" t="s">
-        <v>137</v>
-      </c>
-      <c r="M82">
+      <c r="L82" s="1">
+        <v>13.23966</v>
+      </c>
+      <c r="M82" t="s">
+        <v>138</v>
+      </c>
+      <c r="N82">
         <v>14666</v>
       </c>
-      <c r="N82" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14">
+      <c r="O82" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
       <c r="A83" s="3">
         <v>46230</v>
       </c>
       <c r="B83" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D83" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E83" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F83">
-        <v>2.49</v>
+        <v>2.491</v>
       </c>
       <c r="G83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H83">
+        <v>1.619</v>
+      </c>
+      <c r="I83" s="1">
         <v>1.72</v>
       </c>
-      <c r="I83" s="1">
-        <v>4.28</v>
-      </c>
       <c r="J83">
+        <v>4.28452</v>
+      </c>
+      <c r="K83" s="1">
         <v>1.75</v>
       </c>
-      <c r="K83" s="1">
-        <v>4.36</v>
-      </c>
-      <c r="L83" t="s">
-        <v>115</v>
-      </c>
-      <c r="M83">
+      <c r="L83" s="1">
+        <v>4.35925</v>
+      </c>
+      <c r="M83" t="s">
+        <v>116</v>
+      </c>
+      <c r="N83">
         <v>44343</v>
       </c>
-      <c r="N83" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14">
+      <c r="O83" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
       <c r="A84" s="3">
         <v>46230</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E84" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F84">
-        <v>4.78</v>
+        <v>4.783</v>
       </c>
       <c r="G84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H84">
+        <v>1.619</v>
+      </c>
+      <c r="I84" s="1">
         <v>1.72</v>
       </c>
-      <c r="I84" s="1">
-        <v>8.220000000000001</v>
-      </c>
       <c r="J84">
+        <v>8.226760000000001</v>
+      </c>
+      <c r="K84" s="1">
         <v>1.75</v>
       </c>
-      <c r="K84" s="1">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="L84" t="s">
-        <v>122</v>
-      </c>
-      <c r="M84">
+      <c r="L84" s="1">
+        <v>8.37025</v>
+      </c>
+      <c r="M84" t="s">
+        <v>123</v>
+      </c>
+      <c r="N84">
         <v>188101</v>
       </c>
-      <c r="N84" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14">
+      <c r="O84" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
       <c r="A85" s="3">
         <v>46230</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F85">
-        <v>3.18</v>
+        <v>3.183</v>
       </c>
       <c r="G85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H85">
+        <v>1.619</v>
+      </c>
+      <c r="I85" s="1">
         <v>1.72</v>
       </c>
-      <c r="I85" s="1">
-        <v>5.47</v>
-      </c>
       <c r="J85">
+        <v>5.47476</v>
+      </c>
+      <c r="K85" s="1">
         <v>1.75</v>
       </c>
-      <c r="K85" s="1">
-        <v>5.56</v>
-      </c>
-      <c r="L85" t="s">
-        <v>108</v>
-      </c>
-      <c r="M85">
+      <c r="L85" s="1">
+        <v>5.57025</v>
+      </c>
+      <c r="M85" t="s">
+        <v>109</v>
+      </c>
+      <c r="N85">
         <v>143795</v>
       </c>
-      <c r="N85" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14">
+      <c r="O85" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
       <c r="A86" s="3">
         <v>46230</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D86" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E86" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F86">
-        <v>33.01</v>
+        <v>33.011</v>
       </c>
       <c r="G86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H86">
+        <v>1.619</v>
+      </c>
+      <c r="I86" s="1">
         <v>1.72</v>
       </c>
-      <c r="I86" s="1">
-        <v>56.78</v>
-      </c>
       <c r="J86">
+        <v>56.77892</v>
+      </c>
+      <c r="K86" s="1">
         <v>1.75</v>
       </c>
-      <c r="K86" s="1">
-        <v>57.77</v>
-      </c>
-      <c r="L86" t="s">
-        <v>118</v>
-      </c>
-      <c r="M86">
+      <c r="L86" s="1">
+        <v>57.76925</v>
+      </c>
+      <c r="M86" t="s">
+        <v>119</v>
+      </c>
+      <c r="N86">
         <v>78968</v>
       </c>
-      <c r="N86" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14">
+      <c r="O86" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
       <c r="A87" s="3">
         <v>46230</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D87" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E87" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F87">
         <v>3.4</v>
       </c>
       <c r="G87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H87">
+        <v>1.619</v>
+      </c>
+      <c r="I87" s="1">
         <v>1.72</v>
       </c>
-      <c r="I87" s="1">
-        <v>5.85</v>
-      </c>
       <c r="J87">
+        <v>5.848</v>
+      </c>
+      <c r="K87" s="1">
         <v>1.75</v>
       </c>
-      <c r="K87" s="1">
+      <c r="L87" s="1">
         <v>5.95</v>
       </c>
-      <c r="L87" t="s">
-        <v>71</v>
-      </c>
-      <c r="M87">
+      <c r="M87" t="s">
+        <v>72</v>
+      </c>
+      <c r="N87">
         <v>188868</v>
       </c>
-      <c r="N87" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14">
+      <c r="O87" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
       <c r="A88" s="3">
         <v>46230</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E88" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F88">
         <v>6.36</v>
       </c>
       <c r="G88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H88">
+        <v>1.619</v>
+      </c>
+      <c r="I88" s="1">
         <v>1.72</v>
       </c>
-      <c r="I88" s="1">
-        <v>10.94</v>
-      </c>
       <c r="J88">
+        <v>10.9392</v>
+      </c>
+      <c r="K88" s="1">
         <v>1.75</v>
       </c>
-      <c r="K88" s="1">
+      <c r="L88" s="1">
         <v>11.13</v>
       </c>
-      <c r="L88" t="s">
-        <v>138</v>
-      </c>
-      <c r="M88">
+      <c r="M88" t="s">
+        <v>139</v>
+      </c>
+      <c r="N88">
         <v>95504</v>
       </c>
-      <c r="N88" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14">
+      <c r="O88" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
       <c r="A89" s="3">
         <v>46230</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E89" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F89">
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H89">
+        <v>1.619</v>
+      </c>
+      <c r="I89" s="1">
         <v>1.72</v>
       </c>
-      <c r="I89" s="1">
+      <c r="J89">
         <v>17.2</v>
       </c>
-      <c r="J89">
+      <c r="K89" s="1">
         <v>1.75</v>
       </c>
-      <c r="K89" s="1">
+      <c r="L89" s="1">
         <v>17.5</v>
       </c>
-      <c r="L89" t="s">
-        <v>139</v>
-      </c>
-      <c r="M89">
+      <c r="M89" t="s">
+        <v>140</v>
+      </c>
+      <c r="N89">
         <v>74827</v>
       </c>
-      <c r="N89" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14">
+      <c r="O89" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
       <c r="A90" s="3">
         <v>46230</v>
       </c>
       <c r="B90" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D90" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E90" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F90">
-        <v>5.67</v>
+        <v>5.669</v>
       </c>
       <c r="G90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H90">
+        <v>1.619</v>
+      </c>
+      <c r="I90" s="1">
         <v>1.72</v>
       </c>
-      <c r="I90" s="1">
-        <v>9.75</v>
-      </c>
       <c r="J90">
+        <v>9.750679999999999</v>
+      </c>
+      <c r="K90" s="1">
         <v>1.75</v>
       </c>
-      <c r="K90" s="1">
-        <v>9.92</v>
-      </c>
-      <c r="L90" t="s">
-        <v>111</v>
-      </c>
-      <c r="M90">
+      <c r="L90" s="1">
+        <v>9.92075</v>
+      </c>
+      <c r="M90" t="s">
+        <v>112</v>
+      </c>
+      <c r="N90">
         <v>83917</v>
       </c>
-      <c r="N90" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14">
+      <c r="O90" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
       <c r="A91" s="3">
         <v>46230</v>
       </c>
       <c r="B91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E91" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F91">
         <v>5.72</v>
       </c>
       <c r="G91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H91">
+        <v>1.619</v>
+      </c>
+      <c r="I91" s="1">
         <v>1.72</v>
       </c>
-      <c r="I91" s="1">
-        <v>9.84</v>
-      </c>
       <c r="J91">
+        <v>9.8384</v>
+      </c>
+      <c r="K91" s="1">
         <v>1.75</v>
       </c>
-      <c r="K91" s="1">
+      <c r="L91" s="1">
         <v>10.01</v>
       </c>
-      <c r="L91" t="s">
-        <v>140</v>
-      </c>
-      <c r="M91">
+      <c r="M91" t="s">
+        <v>141</v>
+      </c>
+      <c r="N91">
         <v>1492</v>
       </c>
-      <c r="N91" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14">
+      <c r="O91" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
       <c r="A92" s="3">
         <v>46230</v>
       </c>
       <c r="B92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C92" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D92" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E92" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F92">
         <v>10</v>
       </c>
       <c r="G92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H92">
+        <v>1.619</v>
+      </c>
+      <c r="I92" s="1">
         <v>1.72</v>
       </c>
-      <c r="I92" s="1">
+      <c r="J92">
         <v>17.2</v>
       </c>
-      <c r="J92">
+      <c r="K92" s="1">
         <v>1.75</v>
       </c>
-      <c r="K92" s="1">
+      <c r="L92" s="1">
         <v>17.5</v>
       </c>
-      <c r="L92" t="s">
-        <v>141</v>
-      </c>
-      <c r="M92">
+      <c r="M92" t="s">
+        <v>142</v>
+      </c>
+      <c r="N92">
         <v>8267</v>
       </c>
-      <c r="N92" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14">
+      <c r="O92" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
       <c r="A93" s="3">
         <v>46230</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D93" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F93">
-        <v>28.61</v>
+        <v>28.609</v>
       </c>
       <c r="G93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93" s="1">
         <v>0.63</v>
       </c>
-      <c r="I93" s="1">
-        <v>18.02</v>
-      </c>
       <c r="J93">
+        <v>18.02367</v>
+      </c>
+      <c r="K93" s="1">
         <v>0.64</v>
       </c>
-      <c r="K93" s="1">
-        <v>18.31</v>
-      </c>
-      <c r="L93" t="s">
-        <v>142</v>
-      </c>
-      <c r="M93">
+      <c r="L93" s="1">
+        <v>18.30976</v>
+      </c>
+      <c r="M93" t="s">
+        <v>143</v>
+      </c>
+      <c r="N93">
         <v>181693</v>
       </c>
-      <c r="N93" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
+      <c r="O93" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
       <c r="A94" s="3">
         <v>46230</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C94" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D94" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E94" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F94">
-        <v>23.5</v>
+        <v>23.503</v>
       </c>
       <c r="G94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H94">
+        <v>1.619</v>
+      </c>
+      <c r="I94" s="1">
         <v>1.72</v>
       </c>
-      <c r="I94" s="1">
-        <v>40.42</v>
-      </c>
       <c r="J94">
+        <v>40.42516</v>
+      </c>
+      <c r="K94" s="1">
         <v>1.75</v>
       </c>
-      <c r="K94" s="1">
-        <v>41.12</v>
-      </c>
-      <c r="L94" t="s">
-        <v>143</v>
-      </c>
-      <c r="M94">
+      <c r="L94" s="1">
+        <v>41.13025</v>
+      </c>
+      <c r="M94" t="s">
+        <v>144</v>
+      </c>
+      <c r="N94">
         <v>68055</v>
       </c>
-      <c r="N94" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14">
+      <c r="O94" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
       <c r="A95" s="3">
         <v>46231</v>
       </c>
       <c r="B95" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D95" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E95" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F95">
-        <v>5.7</v>
+        <v>5.703</v>
       </c>
       <c r="G95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H95">
+        <v>1.653</v>
+      </c>
+      <c r="I95" s="1">
         <v>1.72</v>
       </c>
-      <c r="I95" s="1">
-        <v>9.800000000000001</v>
-      </c>
       <c r="J95">
+        <v>9.80916</v>
+      </c>
+      <c r="K95" s="1">
         <v>1.75</v>
       </c>
-      <c r="K95" s="1">
-        <v>9.98</v>
-      </c>
-      <c r="L95" t="s">
-        <v>144</v>
-      </c>
-      <c r="M95">
+      <c r="L95" s="1">
+        <v>9.98025</v>
+      </c>
+      <c r="M95" t="s">
+        <v>145</v>
+      </c>
+      <c r="N95">
         <v>44388</v>
       </c>
-      <c r="N95" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14">
+      <c r="O95" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
       <c r="A96" s="3">
         <v>46231</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D96" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E96" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F96">
-        <v>3.29</v>
+        <v>3.291</v>
       </c>
       <c r="G96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H96">
+        <v>1.653</v>
+      </c>
+      <c r="I96" s="1">
         <v>1.72</v>
       </c>
-      <c r="I96" s="1">
-        <v>5.66</v>
-      </c>
       <c r="J96">
+        <v>5.66052</v>
+      </c>
+      <c r="K96" s="1">
         <v>1.75</v>
       </c>
-      <c r="K96" s="1">
-        <v>5.76</v>
-      </c>
-      <c r="L96" t="s">
-        <v>71</v>
-      </c>
-      <c r="M96">
+      <c r="L96" s="1">
+        <v>5.75925</v>
+      </c>
+      <c r="M96" t="s">
+        <v>72</v>
+      </c>
+      <c r="N96">
         <v>188135</v>
       </c>
-      <c r="N96" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14">
+      <c r="O96" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
       <c r="A97" s="3">
         <v>46231</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D97" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E97" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F97">
-        <v>2.21</v>
+        <v>2.211</v>
       </c>
       <c r="G97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H97">
+        <v>1.653</v>
+      </c>
+      <c r="I97" s="1">
         <v>1.72</v>
       </c>
-      <c r="I97" s="1">
-        <v>3.8</v>
-      </c>
       <c r="J97">
+        <v>3.80292</v>
+      </c>
+      <c r="K97" s="1">
         <v>1.75</v>
       </c>
-      <c r="K97" s="1">
-        <v>3.87</v>
-      </c>
-      <c r="L97" t="s">
-        <v>145</v>
-      </c>
-      <c r="M97">
+      <c r="L97" s="1">
+        <v>3.86925</v>
+      </c>
+      <c r="M97" t="s">
+        <v>146</v>
+      </c>
+      <c r="N97">
         <v>188884</v>
       </c>
-      <c r="N97" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14">
+      <c r="O97" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
       <c r="A98" s="3">
         <v>46231</v>
       </c>
       <c r="B98" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D98" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E98" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F98">
         <v>7.48</v>
       </c>
       <c r="G98" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H98">
+        <v>1.653</v>
+      </c>
+      <c r="I98" s="1">
         <v>1.72</v>
       </c>
-      <c r="I98" s="1">
-        <v>12.87</v>
-      </c>
       <c r="J98">
+        <v>12.8656</v>
+      </c>
+      <c r="K98" s="1">
         <v>1.75</v>
       </c>
-      <c r="K98" s="1">
+      <c r="L98" s="1">
         <v>13.09</v>
       </c>
-      <c r="L98" t="s">
-        <v>95</v>
-      </c>
-      <c r="M98">
+      <c r="M98" t="s">
+        <v>96</v>
+      </c>
+      <c r="N98">
         <v>83974</v>
       </c>
-      <c r="N98" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14">
+      <c r="O98" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
       <c r="A99" s="3">
         <v>46231</v>
       </c>
       <c r="B99" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C99" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E99" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F99">
         <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H99">
+        <v>1.653</v>
+      </c>
+      <c r="I99" s="1">
         <v>1.72</v>
       </c>
-      <c r="I99" s="1">
+      <c r="J99">
         <v>34.4</v>
       </c>
-      <c r="J99">
+      <c r="K99" s="1">
         <v>1.75</v>
       </c>
-      <c r="K99" s="1">
+      <c r="L99" s="1">
         <v>35</v>
       </c>
-      <c r="L99" t="s">
-        <v>135</v>
-      </c>
-      <c r="M99">
+      <c r="M99" t="s">
+        <v>136</v>
+      </c>
+      <c r="N99">
         <v>78747</v>
       </c>
-      <c r="N99" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14">
+      <c r="O99" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
       <c r="A100" s="3">
         <v>46231</v>
       </c>
       <c r="B100" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E100" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F100">
-        <v>2.17</v>
+        <v>2.171</v>
       </c>
       <c r="G100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H100">
+        <v>1.653</v>
+      </c>
+      <c r="I100" s="1">
         <v>1.72</v>
       </c>
-      <c r="I100" s="1">
-        <v>3.73</v>
-      </c>
       <c r="J100">
+        <v>3.73412</v>
+      </c>
+      <c r="K100" s="1">
         <v>1.75</v>
       </c>
-      <c r="K100" s="1">
-        <v>3.8</v>
-      </c>
-      <c r="L100" t="s">
-        <v>73</v>
-      </c>
-      <c r="M100">
+      <c r="L100" s="1">
+        <v>3.79925</v>
+      </c>
+      <c r="M100" t="s">
+        <v>74</v>
+      </c>
+      <c r="N100">
         <v>143808</v>
       </c>
-      <c r="N100" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14">
+      <c r="O100" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
       <c r="A101" s="3">
         <v>46231</v>
       </c>
       <c r="B101" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C101" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D101" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E101" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F101">
-        <v>7.1</v>
+        <v>7.103</v>
       </c>
       <c r="G101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H101">
+        <v>1.653</v>
+      </c>
+      <c r="I101" s="1">
         <v>1.72</v>
       </c>
-      <c r="I101" s="1">
-        <v>12.21</v>
-      </c>
       <c r="J101">
+        <v>12.21716</v>
+      </c>
+      <c r="K101" s="1">
         <v>1.75</v>
       </c>
-      <c r="K101" s="1">
-        <v>12.42</v>
-      </c>
-      <c r="L101" t="s">
-        <v>90</v>
-      </c>
-      <c r="M101">
+      <c r="L101" s="1">
+        <v>12.43025</v>
+      </c>
+      <c r="M101" t="s">
+        <v>91</v>
+      </c>
+      <c r="N101">
         <v>58277</v>
       </c>
-      <c r="N101" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14">
+      <c r="O101" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
       <c r="A102" s="3">
         <v>46231</v>
       </c>
       <c r="B102" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D102" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E102" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F102">
-        <v>9.41</v>
+        <v>9.411</v>
       </c>
       <c r="G102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H102">
+        <v>1.653</v>
+      </c>
+      <c r="I102" s="1">
         <v>1.72</v>
       </c>
-      <c r="I102" s="1">
-        <v>16.19</v>
-      </c>
       <c r="J102">
+        <v>16.18692</v>
+      </c>
+      <c r="K102" s="1">
         <v>1.75</v>
       </c>
-      <c r="K102" s="1">
-        <v>16.47</v>
-      </c>
-      <c r="L102" t="s">
-        <v>146</v>
-      </c>
-      <c r="M102">
+      <c r="L102" s="1">
+        <v>16.46925</v>
+      </c>
+      <c r="M102" t="s">
+        <v>147</v>
+      </c>
+      <c r="N102">
         <v>1542</v>
       </c>
-      <c r="N102" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14">
+      <c r="O102" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
       <c r="A103" s="3">
         <v>46231</v>
       </c>
       <c r="B103" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D103" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E103" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F103">
         <v>5.32</v>
       </c>
       <c r="G103" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H103">
+        <v>1.653</v>
+      </c>
+      <c r="I103" s="1">
         <v>1.72</v>
       </c>
-      <c r="I103" s="1">
-        <v>9.15</v>
-      </c>
       <c r="J103">
+        <v>9.150399999999999</v>
+      </c>
+      <c r="K103" s="1">
         <v>1.75</v>
       </c>
-      <c r="K103" s="1">
+      <c r="L103" s="1">
         <v>9.31</v>
       </c>
-      <c r="L103" t="s">
-        <v>83</v>
-      </c>
-      <c r="M103">
+      <c r="M103" t="s">
+        <v>84</v>
+      </c>
+      <c r="N103">
         <v>95539</v>
       </c>
-      <c r="N103" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14">
+      <c r="O103" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
       <c r="A104" s="3">
         <v>46231</v>
       </c>
       <c r="B104" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D104" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E104" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F104">
         <v>11.08</v>
       </c>
       <c r="G104" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H104">
+        <v>1.653</v>
+      </c>
+      <c r="I104" s="1">
         <v>1.72</v>
       </c>
-      <c r="I104" s="1">
-        <v>19.06</v>
-      </c>
       <c r="J104">
+        <v>19.0576</v>
+      </c>
+      <c r="K104" s="1">
         <v>1.75</v>
       </c>
-      <c r="K104" s="1">
+      <c r="L104" s="1">
         <v>19.39</v>
       </c>
-      <c r="L104" t="s">
-        <v>147</v>
-      </c>
-      <c r="M104">
+      <c r="M104" t="s">
+        <v>148</v>
+      </c>
+      <c r="N104">
         <v>8281</v>
       </c>
-      <c r="N104" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14">
+      <c r="O104" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
       <c r="A105" s="3">
         <v>46231</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E105" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F105">
         <v>4</v>
       </c>
       <c r="G105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H105">
+        <v>1.653</v>
+      </c>
+      <c r="I105" s="1">
         <v>1.72</v>
       </c>
-      <c r="I105" s="1">
+      <c r="J105">
         <v>6.88</v>
       </c>
-      <c r="J105">
+      <c r="K105" s="1">
         <v>1.75</v>
       </c>
-      <c r="K105" s="1">
+      <c r="L105" s="1">
         <v>7</v>
       </c>
-      <c r="L105" t="s">
-        <v>148</v>
-      </c>
-      <c r="M105">
+      <c r="M105" t="s">
+        <v>149</v>
+      </c>
+      <c r="N105">
         <v>74863</v>
       </c>
-      <c r="N105" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14">
+      <c r="O105" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
       <c r="A106" s="3">
         <v>46232</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D106" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E106" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F106">
         <v>4</v>
       </c>
       <c r="G106" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H106">
+        <v>1.674</v>
+      </c>
+      <c r="I106" s="1">
         <v>1.72</v>
       </c>
-      <c r="I106" s="1">
+      <c r="J106">
         <v>6.88</v>
       </c>
-      <c r="J106">
+      <c r="K106" s="1">
         <v>1.75</v>
       </c>
-      <c r="K106" s="1">
+      <c r="L106" s="1">
         <v>7</v>
       </c>
-      <c r="L106" t="s">
-        <v>146</v>
-      </c>
-      <c r="M106">
+      <c r="M106" t="s">
+        <v>147</v>
+      </c>
+      <c r="N106">
         <v>44411</v>
       </c>
-      <c r="N106" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14">
+      <c r="O106" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
       <c r="A107" s="3">
         <v>46232</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C107" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D107" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E107" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F107">
         <v>28.56</v>
       </c>
       <c r="G107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H107">
+        <v>1.674</v>
+      </c>
+      <c r="I107" s="1">
         <v>1.72</v>
       </c>
-      <c r="I107" s="1">
-        <v>49.12</v>
-      </c>
       <c r="J107">
+        <v>49.1232</v>
+      </c>
+      <c r="K107" s="1">
         <v>1.75</v>
       </c>
-      <c r="K107" s="1">
+      <c r="L107" s="1">
         <v>49.98</v>
       </c>
-      <c r="L107" t="s">
-        <v>149</v>
-      </c>
-      <c r="M107">
+      <c r="M107" t="s">
+        <v>150</v>
+      </c>
+      <c r="N107">
         <v>340135</v>
       </c>
-      <c r="N107" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14">
+      <c r="O107" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
       <c r="A108" s="3">
         <v>46232</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C108" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D108" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E108" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F108">
         <v>25.2</v>
       </c>
       <c r="G108" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H108">
+        <v>1.674</v>
+      </c>
+      <c r="I108" s="1">
         <v>1.72</v>
       </c>
-      <c r="I108" s="1">
-        <v>43.34</v>
-      </c>
       <c r="J108">
+        <v>43.344</v>
+      </c>
+      <c r="K108" s="1">
         <v>1.75</v>
       </c>
-      <c r="K108" s="1">
+      <c r="L108" s="1">
         <v>44.1</v>
       </c>
-      <c r="L108" t="s">
-        <v>150</v>
-      </c>
-      <c r="M108">
+      <c r="M108" t="s">
+        <v>151</v>
+      </c>
+      <c r="N108">
         <v>340135</v>
       </c>
-      <c r="N108" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14">
+      <c r="O108" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
       <c r="A109" s="3">
         <v>46232</v>
       </c>
       <c r="B109" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D109" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E109" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F109">
-        <v>9.65</v>
+        <v>9.651</v>
       </c>
       <c r="G109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H109">
+        <v>1.674</v>
+      </c>
+      <c r="I109" s="1">
         <v>1.72</v>
       </c>
-      <c r="I109" s="1">
-        <v>16.6</v>
-      </c>
       <c r="J109">
+        <v>16.59972</v>
+      </c>
+      <c r="K109" s="1">
         <v>1.75</v>
       </c>
-      <c r="K109" s="1">
-        <v>16.89</v>
-      </c>
-      <c r="L109" t="s">
-        <v>101</v>
-      </c>
-      <c r="M109">
+      <c r="L109" s="1">
+        <v>16.88925</v>
+      </c>
+      <c r="M109" t="s">
+        <v>102</v>
+      </c>
+      <c r="N109">
         <v>1577</v>
       </c>
-      <c r="N109" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14">
+      <c r="O109" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
       <c r="A110" s="3">
         <v>46232</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D110" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E110" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F110">
-        <v>3.67</v>
+        <v>3.669</v>
       </c>
       <c r="G110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H110">
+        <v>1.674</v>
+      </c>
+      <c r="I110" s="1">
         <v>1.72</v>
       </c>
-      <c r="I110" s="1">
-        <v>6.31</v>
-      </c>
       <c r="J110">
+        <v>6.31068</v>
+      </c>
+      <c r="K110" s="1">
         <v>1.75</v>
       </c>
-      <c r="K110" s="1">
-        <v>6.42</v>
-      </c>
-      <c r="L110" t="s">
-        <v>151</v>
-      </c>
-      <c r="M110">
+      <c r="L110" s="1">
+        <v>6.42075</v>
+      </c>
+      <c r="M110" t="s">
+        <v>152</v>
+      </c>
+      <c r="N110">
         <v>188907</v>
       </c>
-      <c r="N110" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14">
+      <c r="O110" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
       <c r="A111" s="3">
         <v>46232</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C111" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D111" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E111" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F111">
         <v>11</v>
       </c>
       <c r="G111" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H111">
+        <v>1.674</v>
+      </c>
+      <c r="I111" s="1">
         <v>1.72</v>
       </c>
-      <c r="I111" s="1">
+      <c r="J111">
         <v>18.92</v>
       </c>
-      <c r="J111">
+      <c r="K111" s="1">
         <v>1.75</v>
       </c>
-      <c r="K111" s="1">
+      <c r="L111" s="1">
         <v>19.25</v>
       </c>
-      <c r="L111" t="s">
-        <v>152</v>
-      </c>
-      <c r="M111">
+      <c r="M111" t="s">
+        <v>153</v>
+      </c>
+      <c r="N111">
         <v>0</v>
       </c>
-      <c r="N111" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14">
+      <c r="O111" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
       <c r="A112" s="3">
         <v>46232</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E112" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F112">
         <v>5.8</v>
       </c>
       <c r="G112" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H112">
+        <v>1.674</v>
+      </c>
+      <c r="I112" s="1">
         <v>1.72</v>
       </c>
-      <c r="I112" s="1">
-        <v>9.98</v>
-      </c>
       <c r="J112">
+        <v>9.976000000000001</v>
+      </c>
+      <c r="K112" s="1">
         <v>1.75</v>
       </c>
-      <c r="K112" s="1">
+      <c r="L112" s="1">
         <v>10.15</v>
       </c>
-      <c r="L112" t="s">
-        <v>153</v>
-      </c>
-      <c r="M112">
+      <c r="M112" t="s">
+        <v>154</v>
+      </c>
+      <c r="N112">
         <v>74909</v>
       </c>
-      <c r="N112" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14">
+      <c r="O112" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
       <c r="A113" s="3">
         <v>46232</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C113" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E113" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F113">
         <v>34</v>
       </c>
       <c r="G113" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H113">
+        <v>1.674</v>
+      </c>
+      <c r="I113" s="1">
         <v>1.72</v>
       </c>
-      <c r="I113" s="1">
+      <c r="J113">
         <v>58.48</v>
       </c>
-      <c r="J113">
+      <c r="K113" s="1">
         <v>1.75</v>
       </c>
-      <c r="K113" s="1">
+      <c r="L113" s="1">
         <v>59.5</v>
       </c>
-      <c r="L113" t="s">
-        <v>127</v>
-      </c>
-      <c r="M113">
+      <c r="M113" t="s">
+        <v>128</v>
+      </c>
+      <c r="N113">
         <v>78834</v>
       </c>
-      <c r="N113" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
+      <c r="O113" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
       <c r="A114" s="3">
         <v>46232</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C114" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D114" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E114" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F114">
         <v>6.6</v>
       </c>
       <c r="G114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H114">
+        <v>1.674</v>
+      </c>
+      <c r="I114" s="1">
         <v>1.72</v>
       </c>
-      <c r="I114" s="1">
-        <v>11.35</v>
-      </c>
       <c r="J114">
+        <v>11.352</v>
+      </c>
+      <c r="K114" s="1">
         <v>1.75</v>
       </c>
-      <c r="K114" s="1">
+      <c r="L114" s="1">
         <v>11.55</v>
       </c>
-      <c r="L114" t="s">
-        <v>130</v>
-      </c>
-      <c r="M114">
+      <c r="M114" t="s">
+        <v>131</v>
+      </c>
+      <c r="N114">
         <v>84032</v>
       </c>
-      <c r="N114" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="115" spans="1:14">
+      <c r="O114" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
       <c r="A115" s="3">
         <v>46232</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C115" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D115" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E115" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F115">
         <v>10</v>
       </c>
       <c r="G115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H115">
+        <v>1.674</v>
+      </c>
+      <c r="I115" s="1">
         <v>1.72</v>
       </c>
-      <c r="I115" s="1">
+      <c r="J115">
         <v>17.2</v>
       </c>
-      <c r="J115">
+      <c r="K115" s="1">
         <v>1.75</v>
       </c>
-      <c r="K115" s="1">
+      <c r="L115" s="1">
         <v>17.5</v>
       </c>
-      <c r="L115" t="s">
-        <v>108</v>
-      </c>
-      <c r="M115">
+      <c r="M115" t="s">
+        <v>109</v>
+      </c>
+      <c r="N115">
         <v>8297</v>
       </c>
-      <c r="N115" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14">
+      <c r="O115" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
       <c r="A116" s="3">
         <v>46232</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D116" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E116" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F116">
-        <v>4.02</v>
+        <v>4.023</v>
       </c>
       <c r="G116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H116">
+        <v>1.674</v>
+      </c>
+      <c r="I116" s="1">
         <v>1.72</v>
       </c>
-      <c r="I116" s="1">
-        <v>6.91</v>
-      </c>
       <c r="J116">
+        <v>6.91956</v>
+      </c>
+      <c r="K116" s="1">
         <v>1.75</v>
       </c>
-      <c r="K116" s="1">
-        <v>7.03</v>
-      </c>
-      <c r="L116" t="s">
-        <v>154</v>
-      </c>
-      <c r="M116">
+      <c r="L116" s="1">
+        <v>7.04025</v>
+      </c>
+      <c r="M116" t="s">
+        <v>155</v>
+      </c>
+      <c r="N116">
         <v>58301</v>
       </c>
-      <c r="N116" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14">
+      <c r="O116" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
       <c r="A117" s="3">
         <v>46232</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D117" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E117" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F117">
-        <v>3.45</v>
+        <v>3.451</v>
       </c>
       <c r="G117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H117">
+        <v>1.674</v>
+      </c>
+      <c r="I117" s="1">
         <v>1.72</v>
       </c>
-      <c r="I117" s="1">
-        <v>5.93</v>
-      </c>
       <c r="J117">
+        <v>5.93572</v>
+      </c>
+      <c r="K117" s="1">
         <v>1.75</v>
       </c>
-      <c r="K117" s="1">
-        <v>6.04</v>
-      </c>
-      <c r="L117" t="s">
-        <v>95</v>
-      </c>
-      <c r="M117">
+      <c r="L117" s="1">
+        <v>6.03925</v>
+      </c>
+      <c r="M117" t="s">
+        <v>96</v>
+      </c>
+      <c r="N117">
         <v>95571</v>
       </c>
-      <c r="N117" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14">
+      <c r="O117" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
       <c r="A118" s="3">
         <v>46232</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C118" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D118" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E118" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F118">
         <v>18</v>
       </c>
       <c r="G118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H118">
+        <v>1.674</v>
+      </c>
+      <c r="I118" s="1">
         <v>1.72</v>
       </c>
-      <c r="I118" s="1">
+      <c r="J118">
         <v>30.96</v>
       </c>
-      <c r="J118">
+      <c r="K118" s="1">
         <v>1.75</v>
       </c>
-      <c r="K118" s="1">
+      <c r="L118" s="1">
         <v>31.5</v>
       </c>
-      <c r="L118" t="s">
-        <v>123</v>
-      </c>
-      <c r="M118">
+      <c r="M118" t="s">
+        <v>124</v>
+      </c>
+      <c r="N118">
         <v>68194</v>
       </c>
-      <c r="N118" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14">
+      <c r="O118" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
       <c r="A119" s="3">
         <v>46232</v>
       </c>
       <c r="B119" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C119" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D119" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E119" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F119">
-        <v>27.89</v>
+        <v>27.891</v>
       </c>
       <c r="G119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H119">
+        <v>1.674</v>
+      </c>
+      <c r="I119" s="1">
         <v>1.72</v>
       </c>
-      <c r="I119" s="1">
-        <v>47.97</v>
-      </c>
       <c r="J119">
+        <v>47.97252</v>
+      </c>
+      <c r="K119" s="1">
         <v>1.75</v>
       </c>
-      <c r="K119" s="1">
-        <v>48.81</v>
-      </c>
-      <c r="L119" t="s">
-        <v>155</v>
-      </c>
-      <c r="M119">
+      <c r="L119" s="1">
+        <v>48.80925</v>
+      </c>
+      <c r="M119" t="s">
+        <v>156</v>
+      </c>
+      <c r="N119">
         <v>2258</v>
       </c>
-      <c r="N119" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14">
+      <c r="O119" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
       <c r="A120" s="3">
         <v>46233</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C120" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D120" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E120" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F120">
         <v>6.79</v>
       </c>
       <c r="G120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H120">
+        <v>1.674</v>
+      </c>
+      <c r="I120" s="1">
         <v>1.73</v>
       </c>
-      <c r="I120" s="1">
-        <v>11.75</v>
-      </c>
       <c r="J120">
+        <v>11.7467</v>
+      </c>
+      <c r="K120" s="1">
         <v>1.76</v>
       </c>
-      <c r="K120" s="1">
-        <v>11.95</v>
-      </c>
-      <c r="L120" t="s">
-        <v>95</v>
-      </c>
-      <c r="M120">
+      <c r="L120" s="1">
+        <v>11.9504</v>
+      </c>
+      <c r="M120" t="s">
+        <v>96</v>
+      </c>
+      <c r="N120">
         <v>188177</v>
       </c>
-      <c r="N120" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="121" spans="1:14">
+      <c r="O120" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
       <c r="A121" s="3">
         <v>46233</v>
       </c>
       <c r="B121" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D121" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E121" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F121">
-        <v>7.84</v>
+        <v>7.841</v>
       </c>
       <c r="G121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H121">
+        <v>1.674</v>
+      </c>
+      <c r="I121" s="1">
         <v>1.73</v>
       </c>
-      <c r="I121" s="1">
-        <v>13.56</v>
-      </c>
       <c r="J121">
+        <v>13.56493</v>
+      </c>
+      <c r="K121" s="1">
         <v>1.76</v>
       </c>
-      <c r="K121" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="L121" t="s">
-        <v>131</v>
-      </c>
-      <c r="M121">
+      <c r="L121" s="1">
+        <v>13.80016</v>
+      </c>
+      <c r="M121" t="s">
+        <v>132</v>
+      </c>
+      <c r="N121">
         <v>84098</v>
       </c>
-      <c r="N121" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14">
+      <c r="O121" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
       <c r="A122" s="3">
         <v>46233</v>
       </c>
       <c r="B122" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C122" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D122" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E122" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F122">
-        <v>6.76</v>
+        <v>6.761</v>
       </c>
       <c r="G122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H122">
+        <v>1.674</v>
+      </c>
+      <c r="I122" s="1">
         <v>1.73</v>
       </c>
-      <c r="I122" s="1">
-        <v>11.69</v>
-      </c>
       <c r="J122">
+        <v>11.69653</v>
+      </c>
+      <c r="K122" s="1">
         <v>1.76</v>
       </c>
-      <c r="K122" s="1">
-        <v>11.9</v>
-      </c>
-      <c r="L122" t="s">
-        <v>135</v>
-      </c>
-      <c r="M122">
+      <c r="L122" s="1">
+        <v>11.89936</v>
+      </c>
+      <c r="M122" t="s">
+        <v>136</v>
+      </c>
+      <c r="N122">
         <v>44440</v>
       </c>
-      <c r="N122" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="123" spans="1:14">
+      <c r="O122" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
       <c r="A123" s="3">
         <v>46233</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C123" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D123" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E123" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F123">
         <v>11</v>
       </c>
       <c r="G123" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H123">
+        <v>1.674</v>
+      </c>
+      <c r="I123" s="1">
         <v>1.73</v>
       </c>
-      <c r="I123" s="1">
+      <c r="J123">
         <v>19.03</v>
       </c>
-      <c r="J123">
+      <c r="K123" s="1">
         <v>1.76</v>
       </c>
-      <c r="K123" s="1">
+      <c r="L123" s="1">
         <v>19.36</v>
       </c>
-      <c r="L123" t="s">
-        <v>78</v>
-      </c>
-      <c r="M123">
+      <c r="M123" t="s">
+        <v>79</v>
+      </c>
+      <c r="N123">
         <v>8321</v>
       </c>
-      <c r="N123" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14">
+      <c r="O123" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
       <c r="A124" s="3">
         <v>46233</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C124" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D124" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E124" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F124">
-        <v>66.73</v>
+        <v>66.727</v>
       </c>
       <c r="G124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H124">
+        <v>1.674</v>
+      </c>
+      <c r="I124" s="1">
         <v>1.73</v>
       </c>
-      <c r="I124" s="1">
-        <v>115.44</v>
-      </c>
       <c r="J124">
+        <v>115.43771</v>
+      </c>
+      <c r="K124" s="1">
         <v>1.76</v>
       </c>
-      <c r="K124" s="1">
-        <v>117.44</v>
-      </c>
-      <c r="L124" t="s">
-        <v>114</v>
-      </c>
-      <c r="M124">
+      <c r="L124" s="1">
+        <v>117.43952</v>
+      </c>
+      <c r="M124" t="s">
+        <v>115</v>
+      </c>
+      <c r="N124">
         <v>600</v>
       </c>
-      <c r="N124" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14">
+      <c r="O124" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
       <c r="A125" s="3">
         <v>46233</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C125" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D125" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E125" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F125">
         <v>8.75</v>
       </c>
       <c r="G125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H125">
+        <v>1.674</v>
+      </c>
+      <c r="I125" s="1">
         <v>1.73</v>
       </c>
-      <c r="I125" s="1">
-        <v>15.14</v>
-      </c>
       <c r="J125">
+        <v>15.1375</v>
+      </c>
+      <c r="K125" s="1">
         <v>1.76</v>
       </c>
-      <c r="K125" s="1">
+      <c r="L125" s="1">
         <v>15.4</v>
       </c>
-      <c r="L125" t="s">
-        <v>105</v>
-      </c>
-      <c r="M125">
+      <c r="M125" t="s">
+        <v>106</v>
+      </c>
+      <c r="N125">
         <v>1602</v>
       </c>
-      <c r="N125" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="126" spans="1:14">
+      <c r="O125" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
       <c r="A126" s="3">
         <v>46233</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C126" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E126" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F126">
-        <v>8.279999999999999</v>
+        <v>8.278</v>
       </c>
       <c r="G126" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H126">
+        <v>1.674</v>
+      </c>
+      <c r="I126" s="1">
         <v>1.73</v>
       </c>
-      <c r="I126" s="1">
-        <v>14.32</v>
-      </c>
       <c r="J126">
+        <v>14.32094</v>
+      </c>
+      <c r="K126" s="1">
         <v>1.76</v>
       </c>
-      <c r="K126" s="1">
-        <v>14.57</v>
-      </c>
-      <c r="L126" t="s">
-        <v>156</v>
-      </c>
-      <c r="M126">
+      <c r="L126" s="1">
+        <v>14.56928</v>
+      </c>
+      <c r="M126" t="s">
+        <v>157</v>
+      </c>
+      <c r="N126">
         <v>95625</v>
       </c>
-      <c r="N126" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14">
+      <c r="O126" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
       <c r="A127" s="3">
         <v>46233</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C127" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D127" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E127" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F127">
-        <v>3.55</v>
+        <v>3.551</v>
       </c>
       <c r="G127" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H127">
+        <v>1.674</v>
+      </c>
+      <c r="I127" s="1">
         <v>1.73</v>
       </c>
-      <c r="I127" s="1">
-        <v>6.14</v>
-      </c>
       <c r="J127">
+        <v>6.14323</v>
+      </c>
+      <c r="K127" s="1">
         <v>1.76</v>
       </c>
-      <c r="K127" s="1">
-        <v>6.25</v>
-      </c>
-      <c r="L127" t="s">
-        <v>157</v>
-      </c>
-      <c r="M127">
+      <c r="L127" s="1">
+        <v>6.24976</v>
+      </c>
+      <c r="M127" t="s">
+        <v>158</v>
+      </c>
+      <c r="N127">
         <v>188927</v>
       </c>
-      <c r="N127" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="128" spans="1:14">
+      <c r="O127" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
       <c r="A128" s="3">
         <v>46233</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C128" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D128" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E128" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F128">
-        <v>5.6</v>
+        <v>5.602</v>
       </c>
       <c r="G128" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H128">
+        <v>1.674</v>
+      </c>
+      <c r="I128" s="1">
         <v>1.73</v>
       </c>
-      <c r="I128" s="1">
-        <v>9.69</v>
-      </c>
       <c r="J128">
+        <v>9.691459999999999</v>
+      </c>
+      <c r="K128" s="1">
         <v>1.76</v>
       </c>
-      <c r="K128" s="1">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="L128" t="s">
-        <v>122</v>
-      </c>
-      <c r="M128">
+      <c r="L128" s="1">
+        <v>9.85952</v>
+      </c>
+      <c r="M128" t="s">
+        <v>123</v>
+      </c>
+      <c r="N128">
         <v>58348</v>
       </c>
-      <c r="N128" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="129" spans="1:14">
+      <c r="O128" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
       <c r="A129" s="3">
         <v>46233</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C129" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D129" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E129" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F129">
         <v>8.5</v>
       </c>
       <c r="G129" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H129">
+        <v>1.674</v>
+      </c>
+      <c r="I129" s="1">
         <v>1.73</v>
       </c>
-      <c r="I129" s="1">
-        <v>14.7</v>
-      </c>
       <c r="J129">
+        <v>14.705</v>
+      </c>
+      <c r="K129" s="1">
         <v>1.76</v>
       </c>
-      <c r="K129" s="1">
+      <c r="L129" s="1">
         <v>14.96</v>
       </c>
-      <c r="L129" t="s">
-        <v>158</v>
-      </c>
-      <c r="M129">
+      <c r="M129" t="s">
+        <v>159</v>
+      </c>
+      <c r="N129">
         <v>74961</v>
       </c>
-      <c r="N129" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14">
+      <c r="O129" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
       <c r="A130" s="3">
         <v>46233</v>
       </c>
       <c r="B130" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C130" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D130" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E130" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F130">
         <v>7.09</v>
       </c>
       <c r="G130" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H130">
+        <v>1.449</v>
+      </c>
+      <c r="I130" s="1">
         <v>1.52</v>
       </c>
-      <c r="I130" s="1">
-        <v>10.78</v>
-      </c>
       <c r="J130">
+        <v>10.7768</v>
+      </c>
+      <c r="K130" s="1">
         <v>1.55</v>
       </c>
-      <c r="K130" s="1">
-        <v>10.99</v>
-      </c>
-      <c r="L130" t="s">
-        <v>138</v>
-      </c>
-      <c r="M130">
+      <c r="L130" s="1">
+        <v>10.9895</v>
+      </c>
+      <c r="M130" t="s">
+        <v>139</v>
+      </c>
+      <c r="N130">
         <v>0</v>
       </c>
-      <c r="N130" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="131" spans="1:14">
+      <c r="O130" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
       <c r="A131" s="3">
         <v>46233</v>
       </c>
       <c r="B131" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C131" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E131" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F131">
-        <v>30.02</v>
+        <v>30.023</v>
       </c>
       <c r="G131" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H131">
+        <v>1.674</v>
+      </c>
+      <c r="I131" s="1">
         <v>1.73</v>
       </c>
-      <c r="I131" s="1">
-        <v>51.93</v>
-      </c>
       <c r="J131">
+        <v>51.93979</v>
+      </c>
+      <c r="K131" s="1">
         <v>1.76</v>
       </c>
-      <c r="K131" s="1">
-        <v>52.84</v>
-      </c>
-      <c r="L131" t="s">
-        <v>159</v>
-      </c>
-      <c r="M131">
+      <c r="L131" s="1">
+        <v>52.84048</v>
+      </c>
+      <c r="M131" t="s">
+        <v>160</v>
+      </c>
+      <c r="N131">
         <v>78915</v>
       </c>
-      <c r="N131" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14">
+      <c r="O131" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
       <c r="A132" s="3">
         <v>46233</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C132" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D132" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E132" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F132">
         <v>20</v>
       </c>
       <c r="G132" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H132">
+        <v>1.449</v>
+      </c>
+      <c r="I132" s="1">
         <v>1.52</v>
       </c>
-      <c r="I132" s="1">
+      <c r="J132">
         <v>30.4</v>
       </c>
-      <c r="J132">
+      <c r="K132" s="1">
         <v>1.55</v>
       </c>
-      <c r="K132" s="1">
+      <c r="L132" s="1">
         <v>31</v>
       </c>
-      <c r="L132" t="s">
-        <v>160</v>
-      </c>
-      <c r="M132">
+      <c r="M132" t="s">
+        <v>161</v>
+      </c>
+      <c r="N132">
         <v>181948</v>
       </c>
-      <c r="N132" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14">
+      <c r="O132" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
       <c r="A133" s="3">
         <v>46233</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C133" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D133" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E133" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F133">
-        <v>28.09</v>
+        <v>28.094</v>
       </c>
       <c r="G133" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133" s="1">
         <v>0.63</v>
       </c>
-      <c r="I133" s="1">
-        <v>17.7</v>
-      </c>
       <c r="J133">
+        <v>17.69922</v>
+      </c>
+      <c r="K133" s="1">
         <v>0.64</v>
       </c>
-      <c r="K133" s="1">
-        <v>17.98</v>
-      </c>
-      <c r="L133" t="s">
-        <v>160</v>
-      </c>
-      <c r="M133">
+      <c r="L133" s="1">
+        <v>17.98016</v>
+      </c>
+      <c r="M133" t="s">
+        <v>161</v>
+      </c>
+      <c r="N133">
         <v>181948</v>
       </c>
-      <c r="N133" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14">
+      <c r="O133" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
       <c r="A134" s="3">
         <v>46233</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C134" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D134" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E134" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F134">
-        <v>14.87</v>
+        <v>14.869</v>
       </c>
       <c r="G134" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H134">
+        <v>1.674</v>
+      </c>
+      <c r="I134" s="1">
         <v>1.73</v>
       </c>
-      <c r="I134" s="1">
-        <v>25.73</v>
-      </c>
       <c r="J134">
+        <v>25.72337</v>
+      </c>
+      <c r="K134" s="1">
         <v>1.76</v>
       </c>
-      <c r="K134" s="1">
-        <v>26.17</v>
-      </c>
-      <c r="L134" t="s">
-        <v>161</v>
-      </c>
-      <c r="M134">
+      <c r="L134" s="1">
+        <v>26.16944</v>
+      </c>
+      <c r="M134" t="s">
+        <v>162</v>
+      </c>
+      <c r="N134">
         <v>68282</v>
       </c>
-      <c r="N134" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14">
+      <c r="O134" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
       <c r="A135" s="3">
         <v>46234</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C135" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D135" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E135" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F135">
-        <v>2.6</v>
+        <v>2.599</v>
       </c>
       <c r="G135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H135">
+        <v>1.689</v>
+      </c>
+      <c r="I135" s="1">
         <v>1.74</v>
       </c>
-      <c r="I135" s="1">
-        <v>4.52</v>
-      </c>
       <c r="J135">
+        <v>4.52226</v>
+      </c>
+      <c r="K135" s="1">
         <v>1.77</v>
       </c>
-      <c r="K135" s="1">
-        <v>4.6</v>
-      </c>
-      <c r="L135" t="s">
-        <v>162</v>
-      </c>
-      <c r="M135">
+      <c r="L135" s="1">
+        <v>4.60023</v>
+      </c>
+      <c r="M135" t="s">
+        <v>163</v>
+      </c>
+      <c r="N135">
         <v>44473</v>
       </c>
-      <c r="N135" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14">
+      <c r="O135" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
       <c r="A136" s="3">
         <v>46234</v>
       </c>
       <c r="B136" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D136" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E136" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F136">
         <v>2</v>
       </c>
       <c r="G136" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H136">
+        <v>1.689</v>
+      </c>
+      <c r="I136" s="1">
         <v>1.74</v>
       </c>
-      <c r="I136" s="1">
+      <c r="J136">
         <v>3.48</v>
       </c>
-      <c r="J136">
+      <c r="K136" s="1">
         <v>1.77</v>
       </c>
-      <c r="K136" s="1">
+      <c r="L136" s="1">
         <v>3.54</v>
       </c>
-      <c r="L136" t="s">
-        <v>163</v>
-      </c>
-      <c r="M136">
+      <c r="M136" t="s">
+        <v>164</v>
+      </c>
+      <c r="N136">
         <v>621</v>
       </c>
-      <c r="N136" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14">
+      <c r="O136" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
       <c r="A137" s="3">
         <v>46234</v>
       </c>
       <c r="B137" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C137" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D137" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E137" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F137">
-        <v>7.16</v>
+        <v>7.158</v>
       </c>
       <c r="G137" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H137">
+        <v>1.689</v>
+      </c>
+      <c r="I137" s="1">
         <v>1.74</v>
       </c>
-      <c r="I137" s="1">
-        <v>12.46</v>
-      </c>
       <c r="J137">
+        <v>12.45492</v>
+      </c>
+      <c r="K137" s="1">
         <v>1.77</v>
       </c>
-      <c r="K137" s="1">
-        <v>12.67</v>
-      </c>
-      <c r="L137" t="s">
-        <v>164</v>
-      </c>
-      <c r="M137">
+      <c r="L137" s="1">
+        <v>12.66966</v>
+      </c>
+      <c r="M137" t="s">
+        <v>165</v>
+      </c>
+      <c r="N137">
         <v>84152</v>
       </c>
-      <c r="N137" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14">
+      <c r="O137" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
       <c r="A138" s="3">
         <v>46234</v>
       </c>
       <c r="B138" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C138" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D138" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E138" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F138">
-        <v>12.92</v>
+        <v>12.921</v>
       </c>
       <c r="G138" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H138">
+        <v>1.689</v>
+      </c>
+      <c r="I138" s="1">
         <v>1.74</v>
       </c>
-      <c r="I138" s="1">
-        <v>22.48</v>
-      </c>
       <c r="J138">
+        <v>22.48254</v>
+      </c>
+      <c r="K138" s="1">
         <v>1.77</v>
       </c>
-      <c r="K138" s="1">
-        <v>22.87</v>
-      </c>
-      <c r="L138" t="s">
-        <v>165</v>
-      </c>
-      <c r="M138">
+      <c r="L138" s="1">
+        <v>22.87017</v>
+      </c>
+      <c r="M138" t="s">
+        <v>166</v>
+      </c>
+      <c r="N138">
         <v>103572</v>
       </c>
-      <c r="N138" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14">
+      <c r="O138" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
       <c r="A139" s="3">
         <v>46234</v>
       </c>
       <c r="B139" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C139" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D139" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E139" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F139">
-        <v>2.63</v>
+        <v>2.633</v>
       </c>
       <c r="G139" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H139">
+        <v>1.689</v>
+      </c>
+      <c r="I139" s="1">
         <v>1.74</v>
       </c>
-      <c r="I139" s="1">
-        <v>4.58</v>
-      </c>
       <c r="J139">
+        <v>4.58142</v>
+      </c>
+      <c r="K139" s="1">
         <v>1.77</v>
       </c>
-      <c r="K139" s="1">
-        <v>4.66</v>
-      </c>
-      <c r="L139" t="s">
-        <v>117</v>
-      </c>
-      <c r="M139">
+      <c r="L139" s="1">
+        <v>4.66041</v>
+      </c>
+      <c r="M139" t="s">
+        <v>118</v>
+      </c>
+      <c r="N139">
         <v>188205</v>
       </c>
-      <c r="N139" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="140" spans="1:14">
+      <c r="O139" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
       <c r="A140" s="3">
         <v>46234</v>
       </c>
       <c r="B140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C140" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D140" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E140" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F140">
         <v>4.87</v>
       </c>
       <c r="G140" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H140">
+        <v>1.689</v>
+      </c>
+      <c r="I140" s="1">
         <v>1.74</v>
       </c>
-      <c r="I140" s="1">
-        <v>8.470000000000001</v>
-      </c>
       <c r="J140">
+        <v>8.473800000000001</v>
+      </c>
+      <c r="K140" s="1">
         <v>1.77</v>
       </c>
-      <c r="K140" s="1">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="L140" t="s">
-        <v>81</v>
-      </c>
-      <c r="M140">
+      <c r="L140" s="1">
+        <v>8.619899999999999</v>
+      </c>
+      <c r="M140" t="s">
+        <v>82</v>
+      </c>
+      <c r="N140">
         <v>188960</v>
       </c>
-      <c r="N140" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14">
+      <c r="O140" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
       <c r="A141" s="3">
         <v>46234</v>
       </c>
       <c r="B141" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C141" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D141" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E141" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F141">
-        <v>6.67</v>
+        <v>6.672</v>
       </c>
       <c r="G141" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H141">
+        <v>1.689</v>
+      </c>
+      <c r="I141" s="1">
         <v>1.74</v>
       </c>
-      <c r="I141" s="1">
-        <v>11.61</v>
-      </c>
       <c r="J141">
+        <v>11.60928</v>
+      </c>
+      <c r="K141" s="1">
         <v>1.77</v>
       </c>
-      <c r="K141" s="1">
-        <v>11.81</v>
-      </c>
-      <c r="L141" t="s">
-        <v>72</v>
-      </c>
-      <c r="M141">
+      <c r="L141" s="1">
+        <v>11.80944</v>
+      </c>
+      <c r="M141" t="s">
+        <v>73</v>
+      </c>
+      <c r="N141">
         <v>1000619</v>
       </c>
-      <c r="N141" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14">
+      <c r="O141" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
       <c r="A142" s="3">
         <v>46234</v>
       </c>
       <c r="B142" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C142" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E142" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F142">
         <v>32</v>
       </c>
       <c r="G142" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H142">
+        <v>1.689</v>
+      </c>
+      <c r="I142" s="1">
         <v>1.74</v>
       </c>
-      <c r="I142" s="1">
+      <c r="J142">
         <v>55.68</v>
       </c>
-      <c r="J142">
+      <c r="K142" s="1">
         <v>1.77</v>
       </c>
-      <c r="K142" s="1">
+      <c r="L142" s="1">
         <v>56.64</v>
       </c>
-      <c r="L142" t="s">
-        <v>130</v>
-      </c>
-      <c r="M142">
+      <c r="M142" t="s">
+        <v>131</v>
+      </c>
+      <c r="N142">
         <v>79000</v>
       </c>
-      <c r="N142" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14">
+      <c r="O142" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
       <c r="A143" s="3">
         <v>46234</v>
       </c>
       <c r="B143" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C143" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E143" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F143">
-        <v>7.1</v>
+        <v>7.102</v>
       </c>
       <c r="G143" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H143">
+        <v>1.689</v>
+      </c>
+      <c r="I143" s="1">
         <v>1.74</v>
       </c>
-      <c r="I143" s="1">
-        <v>12.35</v>
-      </c>
       <c r="J143">
+        <v>12.35748</v>
+      </c>
+      <c r="K143" s="1">
         <v>1.77</v>
       </c>
-      <c r="K143" s="1">
-        <v>12.57</v>
-      </c>
-      <c r="L143" t="s">
-        <v>71</v>
-      </c>
-      <c r="M143">
+      <c r="L143" s="1">
+        <v>12.57054</v>
+      </c>
+      <c r="M143" t="s">
+        <v>72</v>
+      </c>
+      <c r="N143">
         <v>58408</v>
       </c>
-      <c r="N143" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14">
+      <c r="O143" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
       <c r="A144" s="3">
         <v>46234</v>
       </c>
       <c r="B144" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C144" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D144" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E144" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F144">
         <v>10</v>
       </c>
       <c r="G144" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H144">
+        <v>1.689</v>
+      </c>
+      <c r="I144" s="1">
         <v>1.74</v>
       </c>
-      <c r="I144" s="1">
+      <c r="J144">
         <v>17.4</v>
       </c>
-      <c r="J144">
+      <c r="K144" s="1">
         <v>1.77</v>
       </c>
-      <c r="K144" s="1">
+      <c r="L144" s="1">
         <v>17.7</v>
       </c>
-      <c r="L144" t="s">
-        <v>107</v>
-      </c>
-      <c r="M144">
+      <c r="M144" t="s">
+        <v>108</v>
+      </c>
+      <c r="N144">
         <v>8335</v>
       </c>
-      <c r="N144" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14">
+      <c r="O144" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
       <c r="A145" s="3">
         <v>46234</v>
       </c>
       <c r="B145" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C145" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D145" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E145" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F145">
         <v>4.26</v>
       </c>
       <c r="G145" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H145">
+        <v>1.689</v>
+      </c>
+      <c r="I145" s="1">
         <v>1.74</v>
       </c>
-      <c r="I145" s="1">
-        <v>7.41</v>
-      </c>
       <c r="J145">
+        <v>7.4124</v>
+      </c>
+      <c r="K145" s="1">
         <v>1.77</v>
       </c>
-      <c r="K145" s="1">
-        <v>7.54</v>
-      </c>
-      <c r="L145" t="s">
-        <v>166</v>
-      </c>
-      <c r="M145">
+      <c r="L145" s="1">
+        <v>7.5402</v>
+      </c>
+      <c r="M145" t="s">
+        <v>167</v>
+      </c>
+      <c r="N145">
         <v>95655</v>
       </c>
-      <c r="N145" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14">
+      <c r="O145" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
       <c r="A146" s="3">
         <v>46234</v>
       </c>
       <c r="B146" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C146" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D146" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E146" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F146">
-        <v>4.5</v>
+        <v>4.503</v>
       </c>
       <c r="G146" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H146">
+        <v>1.689</v>
+      </c>
+      <c r="I146" s="1">
         <v>1.74</v>
       </c>
-      <c r="I146" s="1">
-        <v>7.83</v>
-      </c>
       <c r="J146">
+        <v>7.83522</v>
+      </c>
+      <c r="K146" s="1">
         <v>1.77</v>
       </c>
-      <c r="K146" s="1">
-        <v>7.96</v>
-      </c>
-      <c r="L146" t="s">
-        <v>90</v>
-      </c>
-      <c r="M146">
+      <c r="L146" s="1">
+        <v>7.97031</v>
+      </c>
+      <c r="M146" t="s">
+        <v>91</v>
+      </c>
+      <c r="N146">
         <v>74898</v>
       </c>
-      <c r="N146" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14">
+      <c r="O146" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
       <c r="A147" s="3">
         <v>46234</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C147" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D147" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E147" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F147">
         <v>9</v>
       </c>
       <c r="G147" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H147">
+        <v>1.689</v>
+      </c>
+      <c r="I147" s="1">
         <v>1.74</v>
       </c>
-      <c r="I147" s="1">
+      <c r="J147">
         <v>15.66</v>
       </c>
-      <c r="J147">
+      <c r="K147" s="1">
         <v>1.77</v>
       </c>
-      <c r="K147" s="1">
+      <c r="L147" s="1">
         <v>15.93</v>
       </c>
-      <c r="L147" t="s">
-        <v>167</v>
-      </c>
-      <c r="M147">
+      <c r="M147" t="s">
+        <v>168</v>
+      </c>
+      <c r="N147">
         <v>68337</v>
       </c>
-      <c r="N147" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14">
+      <c r="O147" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
       <c r="A150" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -7869,58 +8313,58 @@
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:15">
       <c r="A151" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
       <c r="A152" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B152" s="7">
-        <v>1602.99</v>
+        <v>1603.052</v>
       </c>
       <c r="C152" s="7">
         <v>140</v>
       </c>
       <c r="D152" s="8">
-        <v>1.681171</v>
+        <v>1.681172</v>
       </c>
       <c r="E152" s="7">
-        <v>2694.9</v>
+        <v>2695.01</v>
       </c>
       <c r="F152" s="7">
-        <v>2743.02</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14">
+        <v>2743.1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
       <c r="A153" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B153" s="7">
-        <v>227.11</v>
+        <v>227.109</v>
       </c>
       <c r="C153" s="7">
         <v>3</v>
       </c>
       <c r="D153" s="8">
-        <v>1.511206</v>
+        <v>1.511193</v>
       </c>
       <c r="E153" s="7">
         <v>343.21</v>
@@ -7929,18 +8373,18 @@
         <v>350.02</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:15">
       <c r="A154" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B154" s="7">
-        <v>83.56</v>
+        <v>83.562</v>
       </c>
       <c r="C154" s="7">
         <v>3</v>
       </c>
       <c r="D154" s="8">
-        <v>0.629966</v>
+        <v>0.63</v>
       </c>
       <c r="E154" s="7">
         <v>52.64</v>
@@ -7949,22 +8393,22 @@
         <v>53.48</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:15">
       <c r="A155" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B155" s="10">
-        <v>1913.66</v>
+        <v>1913.723</v>
       </c>
       <c r="C155" s="10">
         <v>146</v>
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="10">
-        <v>3090.75</v>
+        <v>3090.86</v>
       </c>
       <c r="F155" s="10">
-        <v>3146.52</v>
+        <v>3146.6</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="319">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -981,9 +978,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1077,10 +1074,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1375,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O155"/>
+  <dimension ref="A1:N155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1388,13 +1385,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1437,6875 +1434,6434 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F2">
         <v>33.081</v>
       </c>
       <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2">
+        <v>1.58</v>
+      </c>
+      <c r="I2" s="1">
+        <v>52.268</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>53.26</v>
+      </c>
+      <c r="L2" t="s">
         <v>71</v>
       </c>
-      <c r="H2">
-        <v>1.499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J2">
-        <v>52.26798</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L2" s="1">
-        <v>53.26041</v>
-      </c>
-      <c r="M2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>78167</v>
       </c>
-      <c r="O2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F3">
         <v>9.167999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I3" s="1">
-        <v>1.58</v>
+        <v>14.485</v>
       </c>
       <c r="J3">
-        <v>14.48544</v>
+        <v>1.61</v>
       </c>
       <c r="K3" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L3" s="1">
-        <v>14.76048</v>
-      </c>
-      <c r="M3" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3">
+        <v>14.76</v>
+      </c>
+      <c r="L3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3">
         <v>95281</v>
       </c>
-      <c r="O3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4">
         <v>9.031000000000001</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H4">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I4" s="1">
-        <v>1.58</v>
+        <v>14.269</v>
       </c>
       <c r="J4">
-        <v>14.26898</v>
+        <v>1.61</v>
       </c>
       <c r="K4" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L4" s="1">
-        <v>14.53991</v>
-      </c>
-      <c r="M4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N4">
+        <v>14.54</v>
+      </c>
+      <c r="L4" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4">
         <v>175883</v>
       </c>
-      <c r="O4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46219</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F5">
         <v>5.851</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I5" s="1">
-        <v>1.58</v>
+        <v>9.244999999999999</v>
       </c>
       <c r="J5">
-        <v>9.244579999999999</v>
+        <v>1.61</v>
       </c>
       <c r="K5" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L5" s="1">
-        <v>9.420109999999999</v>
-      </c>
-      <c r="M5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N5">
+        <v>9.42</v>
+      </c>
+      <c r="L5" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5">
         <v>83832</v>
       </c>
-      <c r="O5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46219</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F6">
         <v>3.36</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H6">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I6" s="1">
-        <v>1.58</v>
+        <v>5.309</v>
       </c>
       <c r="J6">
-        <v>5.3088</v>
+        <v>1.61</v>
       </c>
       <c r="K6" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L6" s="1">
-        <v>5.4096</v>
-      </c>
-      <c r="M6" t="s">
-        <v>76</v>
-      </c>
-      <c r="N6">
+        <v>5.41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6">
         <v>188731</v>
       </c>
-      <c r="O6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46219</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F7">
         <v>2.752</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H7">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I7" s="1">
-        <v>1.58</v>
+        <v>4.348</v>
       </c>
       <c r="J7">
-        <v>4.34816</v>
+        <v>1.61</v>
       </c>
       <c r="K7" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L7" s="1">
-        <v>4.43072</v>
-      </c>
-      <c r="M7" t="s">
-        <v>77</v>
-      </c>
-      <c r="N7">
+        <v>4.431</v>
+      </c>
+      <c r="L7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7">
         <v>143654</v>
       </c>
-      <c r="O7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46219</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8">
         <v>8.571</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H8">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I8" s="1">
-        <v>1.58</v>
+        <v>13.542</v>
       </c>
       <c r="J8">
-        <v>13.54218</v>
+        <v>1.61</v>
       </c>
       <c r="K8" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L8" s="1">
-        <v>13.79931</v>
-      </c>
-      <c r="M8" t="s">
-        <v>78</v>
-      </c>
-      <c r="N8">
+        <v>13.799</v>
+      </c>
+      <c r="L8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8">
         <v>38716</v>
       </c>
-      <c r="O8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46219</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H9">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I9" s="1">
-        <v>1.58</v>
+        <v>17.38</v>
       </c>
       <c r="J9">
-        <v>17.38</v>
+        <v>1.61</v>
       </c>
       <c r="K9" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L9" s="1">
         <v>17.71</v>
       </c>
-      <c r="M9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>78</v>
+      </c>
+      <c r="M9">
         <v>8186</v>
       </c>
-      <c r="O9" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46219</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <v>6.702</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H10">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I10" s="1">
-        <v>1.58</v>
+        <v>10.589</v>
       </c>
       <c r="J10">
-        <v>10.58916</v>
+        <v>1.61</v>
       </c>
       <c r="K10" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L10" s="1">
-        <v>10.79022</v>
-      </c>
-      <c r="M10" t="s">
-        <v>80</v>
-      </c>
-      <c r="N10">
+        <v>10.79</v>
+      </c>
+      <c r="L10" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10">
         <v>58110</v>
       </c>
-      <c r="O10" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46219</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F11">
         <v>4.112</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I11" s="1">
-        <v>1.58</v>
+        <v>6.497</v>
       </c>
       <c r="J11">
-        <v>6.49696</v>
+        <v>1.61</v>
       </c>
       <c r="K11" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L11" s="1">
-        <v>6.62032</v>
-      </c>
-      <c r="M11" t="s">
-        <v>81</v>
-      </c>
-      <c r="N11">
+        <v>6.62</v>
+      </c>
+      <c r="L11" t="s">
+        <v>80</v>
+      </c>
+      <c r="M11">
         <v>44138</v>
       </c>
-      <c r="O11" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46219</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12">
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H12">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I12" s="1">
-        <v>1.58</v>
+        <v>9.48</v>
       </c>
       <c r="J12">
-        <v>9.48</v>
+        <v>1.61</v>
       </c>
       <c r="K12" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L12" s="1">
         <v>9.66</v>
       </c>
-      <c r="M12" t="s">
-        <v>81</v>
-      </c>
-      <c r="N12">
+      <c r="L12" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12">
         <v>1170</v>
       </c>
-      <c r="O12" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46219</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F13">
         <v>4.503</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H13">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I13" s="1">
-        <v>1.58</v>
+        <v>7.115</v>
       </c>
       <c r="J13">
-        <v>7.11474</v>
+        <v>1.61</v>
       </c>
       <c r="K13" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L13" s="1">
-        <v>7.24983</v>
-      </c>
-      <c r="M13" t="s">
-        <v>82</v>
-      </c>
-      <c r="N13">
+        <v>7.25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>81</v>
+      </c>
+      <c r="M13">
         <v>74495</v>
       </c>
-      <c r="O13" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46219</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F14">
         <v>17.012</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H14">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I14" s="1">
-        <v>1.58</v>
+        <v>26.879</v>
       </c>
       <c r="J14">
-        <v>26.87896</v>
+        <v>1.61</v>
       </c>
       <c r="K14" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L14" s="1">
-        <v>27.38932</v>
-      </c>
-      <c r="M14" t="s">
-        <v>83</v>
-      </c>
-      <c r="N14">
+        <v>27.389</v>
+      </c>
+      <c r="L14" t="s">
+        <v>82</v>
+      </c>
+      <c r="M14">
         <v>67651</v>
       </c>
-      <c r="O14" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46220</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15">
         <v>2.871</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H15">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I15" s="1">
-        <v>1.6</v>
+        <v>4.594</v>
       </c>
       <c r="J15">
-        <v>4.5936</v>
+        <v>1.63</v>
       </c>
       <c r="K15" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L15" s="1">
-        <v>4.67973</v>
-      </c>
-      <c r="M15" t="s">
-        <v>84</v>
-      </c>
-      <c r="N15">
+        <v>4.68</v>
+      </c>
+      <c r="L15" t="s">
+        <v>83</v>
+      </c>
+      <c r="M15">
         <v>187950</v>
       </c>
-      <c r="O15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46220</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16">
         <v>5.933</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H16">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I16" s="1">
-        <v>1.6</v>
+        <v>9.493</v>
       </c>
       <c r="J16">
-        <v>9.492800000000001</v>
+        <v>1.63</v>
       </c>
       <c r="K16" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L16" s="1">
-        <v>9.67079</v>
-      </c>
-      <c r="M16" t="s">
-        <v>85</v>
-      </c>
-      <c r="N16">
+        <v>9.670999999999999</v>
+      </c>
+      <c r="L16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M16">
         <v>1192</v>
       </c>
-      <c r="O16" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46220</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17">
         <v>5.061</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H17">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I17" s="1">
-        <v>1.6</v>
+        <v>8.098000000000001</v>
       </c>
       <c r="J17">
-        <v>8.0976</v>
+        <v>1.63</v>
       </c>
       <c r="K17" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L17" s="1">
-        <v>8.24943</v>
-      </c>
-      <c r="M17" t="s">
-        <v>86</v>
-      </c>
-      <c r="N17">
+        <v>8.249000000000001</v>
+      </c>
+      <c r="L17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M17">
         <v>83871</v>
       </c>
-      <c r="O17" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46220</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18">
         <v>2.503</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H18">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I18" s="1">
-        <v>1.6</v>
+        <v>4.005</v>
       </c>
       <c r="J18">
-        <v>4.0048</v>
+        <v>1.63</v>
       </c>
       <c r="K18" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L18" s="1">
-        <v>4.07989</v>
-      </c>
-      <c r="M18" t="s">
-        <v>87</v>
-      </c>
-      <c r="N18">
+        <v>4.08</v>
+      </c>
+      <c r="L18" t="s">
+        <v>86</v>
+      </c>
+      <c r="M18">
         <v>188745</v>
       </c>
-      <c r="O18" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46220</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F19">
         <v>1.503</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H19">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="1">
-        <v>1.6</v>
+        <v>2.405</v>
       </c>
       <c r="J19">
-        <v>2.4048</v>
+        <v>1.63</v>
       </c>
       <c r="K19" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L19" s="1">
-        <v>2.44989</v>
-      </c>
-      <c r="M19" t="s">
-        <v>88</v>
-      </c>
-      <c r="N19">
+        <v>2.45</v>
+      </c>
+      <c r="L19" t="s">
+        <v>87</v>
+      </c>
+      <c r="M19">
         <v>38742</v>
       </c>
-      <c r="O19" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46220</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F20">
         <v>6.828</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H20">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I20" s="1">
-        <v>1.6</v>
+        <v>10.925</v>
       </c>
       <c r="J20">
-        <v>10.9248</v>
+        <v>1.63</v>
       </c>
       <c r="K20" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L20" s="1">
-        <v>11.12964</v>
-      </c>
-      <c r="M20" t="s">
-        <v>89</v>
-      </c>
-      <c r="N20">
+        <v>11.13</v>
+      </c>
+      <c r="L20" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20">
         <v>44174</v>
       </c>
-      <c r="O20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46220</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F21">
         <v>4.84</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H21">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I21" s="1">
-        <v>1.6</v>
+        <v>7.744</v>
       </c>
       <c r="J21">
-        <v>7.744</v>
+        <v>1.63</v>
       </c>
       <c r="K21" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L21" s="1">
-        <v>7.8892</v>
-      </c>
-      <c r="M21" t="s">
-        <v>90</v>
-      </c>
-      <c r="N21">
+        <v>7.889</v>
+      </c>
+      <c r="L21" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21">
         <v>143686</v>
       </c>
-      <c r="O21" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46220</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F22">
         <v>10.012</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H22">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I22" s="1">
-        <v>1.6</v>
+        <v>16.019</v>
       </c>
       <c r="J22">
-        <v>16.0192</v>
+        <v>1.63</v>
       </c>
       <c r="K22" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L22" s="1">
-        <v>16.31956</v>
-      </c>
-      <c r="M22" t="s">
-        <v>91</v>
-      </c>
-      <c r="N22">
+        <v>16.32</v>
+      </c>
+      <c r="L22" t="s">
+        <v>90</v>
+      </c>
+      <c r="M22">
         <v>8202</v>
       </c>
-      <c r="O22" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="N22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46220</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F23">
         <v>39</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H23">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I23" s="1">
-        <v>1.6</v>
+        <v>62.4</v>
       </c>
       <c r="J23">
-        <v>62.4</v>
+        <v>1.63</v>
       </c>
       <c r="K23" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L23" s="1">
         <v>63.57</v>
       </c>
-      <c r="M23" t="s">
-        <v>92</v>
-      </c>
-      <c r="N23">
+      <c r="L23" t="s">
+        <v>91</v>
+      </c>
+      <c r="M23">
         <v>78268</v>
       </c>
-      <c r="O23" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46220</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F24">
         <v>7.748</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H24">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I24" s="1">
-        <v>1.6</v>
+        <v>12.397</v>
       </c>
       <c r="J24">
-        <v>12.3968</v>
+        <v>1.63</v>
       </c>
       <c r="K24" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L24" s="1">
-        <v>12.62924</v>
-      </c>
-      <c r="M24" t="s">
-        <v>90</v>
-      </c>
-      <c r="N24">
+        <v>12.629</v>
+      </c>
+      <c r="L24" t="s">
+        <v>89</v>
+      </c>
+      <c r="M24">
         <v>95351</v>
       </c>
-      <c r="O24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46220</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H25">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I25" s="1">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>8</v>
+        <v>1.63</v>
       </c>
       <c r="K25" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L25" s="1">
         <v>8.15</v>
       </c>
-      <c r="M25" t="s">
-        <v>73</v>
-      </c>
-      <c r="N25">
+      <c r="L25" t="s">
+        <v>72</v>
+      </c>
+      <c r="M25">
         <v>74529</v>
       </c>
-      <c r="O25" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46220</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F26">
         <v>37.368</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H26">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="1">
-        <v>1.6</v>
+        <v>59.789</v>
       </c>
       <c r="J26">
-        <v>59.7888</v>
+        <v>1.63</v>
       </c>
       <c r="K26" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L26" s="1">
-        <v>60.90984</v>
-      </c>
-      <c r="M26" t="s">
-        <v>93</v>
-      </c>
-      <c r="N26">
+        <v>60.91</v>
+      </c>
+      <c r="L26" t="s">
+        <v>92</v>
+      </c>
+      <c r="M26">
         <v>2236</v>
       </c>
-      <c r="O26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46221</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F27">
         <v>3.618</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H27">
-        <v>1.528</v>
+        <v>1.62</v>
       </c>
       <c r="I27" s="1">
-        <v>1.62</v>
+        <v>5.861</v>
       </c>
       <c r="J27">
-        <v>5.86116</v>
+        <v>1.65</v>
       </c>
       <c r="K27" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="L27" s="1">
-        <v>5.9697</v>
-      </c>
-      <c r="M27" t="s">
-        <v>94</v>
-      </c>
-      <c r="N27">
+        <v>5.97</v>
+      </c>
+      <c r="L27" t="s">
+        <v>93</v>
+      </c>
+      <c r="M27">
         <v>58121</v>
       </c>
-      <c r="O27" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="N27" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46221</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F28">
         <v>7.012</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H28">
-        <v>1.528</v>
+        <v>1.62</v>
       </c>
       <c r="I28" s="1">
-        <v>1.62</v>
+        <v>11.359</v>
       </c>
       <c r="J28">
-        <v>11.35944</v>
+        <v>1.65</v>
       </c>
       <c r="K28" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="L28" s="1">
-        <v>11.5698</v>
-      </c>
-      <c r="M28" t="s">
-        <v>95</v>
-      </c>
-      <c r="N28">
+        <v>11.57</v>
+      </c>
+      <c r="L28" t="s">
+        <v>94</v>
+      </c>
+      <c r="M28">
         <v>1224</v>
       </c>
-      <c r="O28" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="N28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46223</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F29">
         <v>2.512</v>
       </c>
       <c r="G29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H29">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I29" s="1">
-        <v>1.65</v>
+        <v>4.145</v>
       </c>
       <c r="J29">
-        <v>4.1448</v>
+        <v>1.68</v>
       </c>
       <c r="K29" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L29" s="1">
-        <v>4.22016</v>
-      </c>
-      <c r="M29" t="s">
-        <v>96</v>
-      </c>
-      <c r="N29">
+        <v>4.22</v>
+      </c>
+      <c r="L29" t="s">
+        <v>95</v>
+      </c>
+      <c r="M29">
         <v>187971</v>
       </c>
-      <c r="O29" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="N29" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46223</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F30">
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H30">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I30" s="1">
-        <v>1.65</v>
+        <v>33</v>
       </c>
       <c r="J30">
-        <v>33</v>
+        <v>1.68</v>
       </c>
       <c r="K30" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L30" s="1">
         <v>33.6</v>
       </c>
-      <c r="M30" t="s">
-        <v>97</v>
-      </c>
-      <c r="N30">
+      <c r="L30" t="s">
+        <v>96</v>
+      </c>
+      <c r="M30">
         <v>78316</v>
       </c>
-      <c r="O30" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="N30" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46223</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F31">
         <v>2.982</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H31">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I31" s="1">
-        <v>1.65</v>
+        <v>4.92</v>
       </c>
       <c r="J31">
-        <v>4.9203</v>
+        <v>1.68</v>
       </c>
       <c r="K31" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L31" s="1">
-        <v>5.00976</v>
-      </c>
-      <c r="M31" t="s">
-        <v>98</v>
-      </c>
-      <c r="N31">
+        <v>5.01</v>
+      </c>
+      <c r="L31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M31">
         <v>143704</v>
       </c>
-      <c r="O31" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="N31" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46223</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F32">
         <v>13.952</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H32">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I32" s="1">
-        <v>1.65</v>
+        <v>23.021</v>
       </c>
       <c r="J32">
-        <v>23.0208</v>
+        <v>1.68</v>
       </c>
       <c r="K32" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L32" s="1">
-        <v>23.43936</v>
-      </c>
-      <c r="M32" t="s">
-        <v>99</v>
-      </c>
-      <c r="N32">
+        <v>23.439</v>
+      </c>
+      <c r="L32" t="s">
+        <v>98</v>
+      </c>
+      <c r="M32">
         <v>67743</v>
       </c>
-      <c r="O32" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46223</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F33">
         <v>5.601</v>
       </c>
       <c r="G33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H33">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I33" s="1">
-        <v>1.65</v>
+        <v>9.242000000000001</v>
       </c>
       <c r="J33">
-        <v>9.24165</v>
+        <v>1.68</v>
       </c>
       <c r="K33" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L33" s="1">
-        <v>9.40968</v>
-      </c>
-      <c r="M33" t="s">
-        <v>100</v>
-      </c>
-      <c r="N33">
+        <v>9.41</v>
+      </c>
+      <c r="L33" t="s">
+        <v>99</v>
+      </c>
+      <c r="M33">
         <v>44204</v>
       </c>
-      <c r="O33" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>46223</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F34">
         <v>2.47</v>
       </c>
       <c r="G34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H34">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I34" s="1">
-        <v>1.65</v>
+        <v>4.076</v>
       </c>
       <c r="J34">
-        <v>4.0755</v>
+        <v>1.68</v>
       </c>
       <c r="K34" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L34" s="1">
-        <v>4.1496</v>
-      </c>
-      <c r="M34" t="s">
-        <v>101</v>
-      </c>
-      <c r="N34">
+        <v>4.15</v>
+      </c>
+      <c r="L34" t="s">
+        <v>100</v>
+      </c>
+      <c r="M34">
         <v>188762</v>
       </c>
-      <c r="O34" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="N34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>46223</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F35">
         <v>6.702</v>
       </c>
       <c r="G35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H35">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I35" s="1">
-        <v>1.65</v>
+        <v>11.058</v>
       </c>
       <c r="J35">
-        <v>11.0583</v>
+        <v>1.68</v>
       </c>
       <c r="K35" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L35" s="1">
-        <v>11.25936</v>
-      </c>
-      <c r="M35" t="s">
-        <v>102</v>
-      </c>
-      <c r="N35">
+        <v>11.259</v>
+      </c>
+      <c r="L35" t="s">
+        <v>101</v>
+      </c>
+      <c r="M35">
         <v>95389</v>
       </c>
-      <c r="O35" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="N35" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>46223</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F36">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H36">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I36" s="1">
-        <v>1.65</v>
+        <v>18.15</v>
       </c>
       <c r="J36">
-        <v>18.15</v>
+        <v>1.68</v>
       </c>
       <c r="K36" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L36" s="1">
         <v>18.48</v>
       </c>
-      <c r="M36" t="s">
-        <v>103</v>
-      </c>
-      <c r="N36">
+      <c r="L36" t="s">
+        <v>102</v>
+      </c>
+      <c r="M36">
         <v>8218</v>
       </c>
-      <c r="O36" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="N36" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>46223</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F37">
         <v>6.661</v>
       </c>
       <c r="G37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H37">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I37" s="1">
-        <v>1.65</v>
+        <v>10.991</v>
       </c>
       <c r="J37">
-        <v>10.99065</v>
+        <v>1.68</v>
       </c>
       <c r="K37" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L37" s="1">
-        <v>11.19048</v>
-      </c>
-      <c r="M37" t="s">
-        <v>96</v>
-      </c>
-      <c r="N37">
+        <v>11.19</v>
+      </c>
+      <c r="L37" t="s">
+        <v>95</v>
+      </c>
+      <c r="M37">
         <v>1243</v>
       </c>
-      <c r="O37" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>46223</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F38">
         <v>3.5</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H38">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I38" s="1">
-        <v>1.65</v>
+        <v>5.775</v>
       </c>
       <c r="J38">
-        <v>5.775</v>
+        <v>1.68</v>
       </c>
       <c r="K38" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L38" s="1">
         <v>5.88</v>
       </c>
-      <c r="M38" t="s">
-        <v>104</v>
-      </c>
-      <c r="N38">
+      <c r="L38" t="s">
+        <v>103</v>
+      </c>
+      <c r="M38">
         <v>74577</v>
       </c>
-      <c r="O38" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="3">
         <v>46223</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F39">
         <v>26.859</v>
       </c>
       <c r="G39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I39" s="1">
-        <v>0.63</v>
+        <v>16.921</v>
       </c>
       <c r="J39">
-        <v>16.92117</v>
+        <v>0.64</v>
       </c>
       <c r="K39" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L39" s="1">
-        <v>17.18976</v>
-      </c>
-      <c r="M39" t="s">
-        <v>105</v>
-      </c>
-      <c r="N39">
+        <v>17.19</v>
+      </c>
+      <c r="L39" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39">
         <v>181437</v>
       </c>
-      <c r="O39" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="N39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="3">
         <v>46224</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F40">
         <v>11.881</v>
       </c>
       <c r="G40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H40">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I40" s="1">
-        <v>1.65</v>
+        <v>19.604</v>
       </c>
       <c r="J40">
-        <v>19.60365</v>
+        <v>1.68</v>
       </c>
       <c r="K40" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L40" s="1">
-        <v>19.96008</v>
-      </c>
-      <c r="M40" t="s">
-        <v>106</v>
-      </c>
-      <c r="N40">
+        <v>19.96</v>
+      </c>
+      <c r="L40" t="s">
+        <v>105</v>
+      </c>
+      <c r="M40">
         <v>1332</v>
       </c>
-      <c r="O40" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="N40" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="3">
         <v>46224</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F41">
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H41">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I41" s="1">
-        <v>1.65</v>
+        <v>18.15</v>
       </c>
       <c r="J41">
-        <v>18.15</v>
+        <v>1.68</v>
       </c>
       <c r="K41" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L41" s="1">
         <v>18.48</v>
       </c>
-      <c r="M41" t="s">
-        <v>79</v>
-      </c>
-      <c r="N41">
+      <c r="L41" t="s">
+        <v>78</v>
+      </c>
+      <c r="M41">
         <v>8241</v>
       </c>
-      <c r="O41" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="N41" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="3">
         <v>46224</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F42">
         <v>3.958</v>
       </c>
       <c r="G42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H42">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I42" s="1">
-        <v>1.65</v>
+        <v>6.531</v>
       </c>
       <c r="J42">
-        <v>6.5307</v>
+        <v>1.68</v>
       </c>
       <c r="K42" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L42" s="1">
-        <v>6.64944</v>
-      </c>
-      <c r="M42" t="s">
-        <v>107</v>
-      </c>
-      <c r="N42">
+        <v>6.649</v>
+      </c>
+      <c r="L42" t="s">
+        <v>106</v>
+      </c>
+      <c r="M42">
         <v>143730</v>
       </c>
-      <c r="O42" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="N42" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="3">
         <v>46224</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F43">
         <v>3.857</v>
       </c>
       <c r="G43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H43">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I43" s="1">
-        <v>1.65</v>
+        <v>6.364</v>
       </c>
       <c r="J43">
-        <v>6.36405</v>
+        <v>1.68</v>
       </c>
       <c r="K43" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L43" s="1">
-        <v>6.47976</v>
-      </c>
-      <c r="M43" t="s">
-        <v>108</v>
-      </c>
-      <c r="N43">
+        <v>6.48</v>
+      </c>
+      <c r="L43" t="s">
+        <v>107</v>
+      </c>
+      <c r="M43">
         <v>188792</v>
       </c>
-      <c r="O43" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="3">
         <v>46224</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F44">
         <v>4.899</v>
       </c>
       <c r="G44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H44">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I44" s="1">
-        <v>1.65</v>
+        <v>8.083</v>
       </c>
       <c r="J44">
-        <v>8.083349999999999</v>
+        <v>1.68</v>
       </c>
       <c r="K44" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L44" s="1">
-        <v>8.230320000000001</v>
-      </c>
-      <c r="M44" t="s">
-        <v>109</v>
-      </c>
-      <c r="N44">
+        <v>8.23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>108</v>
+      </c>
+      <c r="M44">
         <v>58157</v>
       </c>
-      <c r="O44" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="N44" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="3">
         <v>46224</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45">
         <v>7</v>
       </c>
       <c r="G45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H45">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I45" s="1">
-        <v>1.65</v>
+        <v>11.55</v>
       </c>
       <c r="J45">
-        <v>11.55</v>
+        <v>1.68</v>
       </c>
       <c r="K45" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L45" s="1">
         <v>11.76</v>
       </c>
-      <c r="M45" t="s">
-        <v>110</v>
-      </c>
-      <c r="N45">
+      <c r="L45" t="s">
+        <v>109</v>
+      </c>
+      <c r="M45">
         <v>175931</v>
       </c>
-      <c r="O45" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="N45" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="3">
         <v>46224</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F46">
         <v>3.929</v>
       </c>
       <c r="G46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H46">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I46" s="1">
-        <v>1.65</v>
+        <v>6.483</v>
       </c>
       <c r="J46">
-        <v>6.48285</v>
+        <v>1.68</v>
       </c>
       <c r="K46" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L46" s="1">
-        <v>6.60072</v>
-      </c>
-      <c r="M46" t="s">
-        <v>97</v>
-      </c>
-      <c r="N46">
+        <v>6.601</v>
+      </c>
+      <c r="L46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M46">
         <v>44228</v>
       </c>
-      <c r="O46" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="3">
         <v>46224</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F47">
         <v>2.393</v>
       </c>
       <c r="G47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H47">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I47" s="1">
-        <v>1.65</v>
+        <v>3.948</v>
       </c>
       <c r="J47">
-        <v>3.94845</v>
+        <v>1.68</v>
       </c>
       <c r="K47" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L47" s="1">
-        <v>4.02024</v>
-      </c>
-      <c r="M47" t="s">
-        <v>111</v>
-      </c>
-      <c r="N47">
+        <v>4.02</v>
+      </c>
+      <c r="L47" t="s">
+        <v>110</v>
+      </c>
+      <c r="M47">
         <v>187996</v>
       </c>
-      <c r="O47" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="3">
         <v>46224</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F48">
         <v>34</v>
       </c>
       <c r="G48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H48">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I48" s="1">
-        <v>1.65</v>
+        <v>56.1</v>
       </c>
       <c r="J48">
-        <v>56.1</v>
+        <v>1.68</v>
       </c>
       <c r="K48" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L48" s="1">
         <v>57.12</v>
       </c>
-      <c r="M48" t="s">
-        <v>112</v>
-      </c>
-      <c r="N48">
+      <c r="L48" t="s">
+        <v>111</v>
+      </c>
+      <c r="M48">
         <v>78404</v>
       </c>
-      <c r="O48" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="N48" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="3">
         <v>46224</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F49">
         <v>3.512</v>
       </c>
       <c r="G49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H49">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I49" s="1">
-        <v>1.65</v>
+        <v>5.795</v>
       </c>
       <c r="J49">
-        <v>5.7948</v>
+        <v>1.68</v>
       </c>
       <c r="K49" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L49" s="1">
-        <v>5.90016</v>
-      </c>
-      <c r="M49" t="s">
-        <v>113</v>
-      </c>
-      <c r="N49">
+        <v>5.9</v>
+      </c>
+      <c r="L49" t="s">
+        <v>112</v>
+      </c>
+      <c r="M49">
         <v>74615</v>
       </c>
-      <c r="O49" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="N49" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="3">
         <v>46224</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F50">
         <v>4.94</v>
       </c>
       <c r="G50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H50">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I50" s="1">
-        <v>1.65</v>
+        <v>8.151</v>
       </c>
       <c r="J50">
-        <v>8.151</v>
+        <v>1.68</v>
       </c>
       <c r="K50" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L50" s="1">
-        <v>8.299200000000001</v>
-      </c>
-      <c r="M50" t="s">
-        <v>114</v>
-      </c>
-      <c r="N50">
+        <v>8.298999999999999</v>
+      </c>
+      <c r="L50" t="s">
+        <v>113</v>
+      </c>
+      <c r="M50">
         <v>95427</v>
       </c>
-      <c r="O50" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="N50" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="3">
         <v>46224</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F51">
         <v>33.28</v>
       </c>
       <c r="G51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H51">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I51" s="1">
-        <v>1.65</v>
+        <v>54.912</v>
       </c>
       <c r="J51">
-        <v>54.912</v>
+        <v>1.68</v>
       </c>
       <c r="K51" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L51" s="1">
-        <v>55.9104</v>
-      </c>
-      <c r="M51" t="s">
-        <v>115</v>
-      </c>
-      <c r="N51">
+        <v>55.91</v>
+      </c>
+      <c r="L51" t="s">
+        <v>114</v>
+      </c>
+      <c r="M51">
         <v>2243</v>
       </c>
-      <c r="O51" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="N51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="3">
         <v>46225</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F52">
         <v>3.698</v>
       </c>
       <c r="G52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H52">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I52" s="1">
-        <v>1.66</v>
+        <v>6.139</v>
       </c>
       <c r="J52">
-        <v>6.13868</v>
+        <v>1.69</v>
       </c>
       <c r="K52" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L52" s="1">
-        <v>6.24962</v>
-      </c>
-      <c r="M52" t="s">
-        <v>108</v>
-      </c>
-      <c r="N52">
+        <v>6.25</v>
+      </c>
+      <c r="L52" t="s">
+        <v>107</v>
+      </c>
+      <c r="M52">
         <v>188027</v>
       </c>
-      <c r="O52" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="N52" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="3">
         <v>46225</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F53">
         <v>5.609</v>
       </c>
       <c r="G53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H53">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I53" s="1">
-        <v>1.66</v>
+        <v>9.311</v>
       </c>
       <c r="J53">
-        <v>9.31094</v>
+        <v>1.69</v>
       </c>
       <c r="K53" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L53" s="1">
-        <v>9.47921</v>
-      </c>
-      <c r="M53" t="s">
-        <v>108</v>
-      </c>
-      <c r="N53">
+        <v>9.478999999999999</v>
+      </c>
+      <c r="L53" t="s">
+        <v>107</v>
+      </c>
+      <c r="M53">
         <v>44270</v>
       </c>
-      <c r="O53" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="N53" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="3">
         <v>46225</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F54">
         <v>9.750999999999999</v>
       </c>
       <c r="G54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H54">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I54" s="1">
-        <v>1.66</v>
+        <v>16.187</v>
       </c>
       <c r="J54">
-        <v>16.18666</v>
+        <v>1.69</v>
       </c>
       <c r="K54" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L54" s="1">
-        <v>16.47919</v>
-      </c>
-      <c r="M54" t="s">
-        <v>116</v>
-      </c>
-      <c r="N54">
+        <v>16.479</v>
+      </c>
+      <c r="L54" t="s">
+        <v>115</v>
+      </c>
+      <c r="M54">
         <v>1351</v>
       </c>
-      <c r="O54" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="N54" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="3">
         <v>46225</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F55">
         <v>3.45</v>
       </c>
       <c r="G55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H55">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I55" s="1">
-        <v>1.66</v>
+        <v>5.727</v>
       </c>
       <c r="J55">
-        <v>5.727</v>
+        <v>1.69</v>
       </c>
       <c r="K55" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L55" s="1">
-        <v>5.8305</v>
-      </c>
-      <c r="M55" t="s">
-        <v>117</v>
-      </c>
-      <c r="N55">
+        <v>5.83</v>
+      </c>
+      <c r="L55" t="s">
+        <v>116</v>
+      </c>
+      <c r="M55">
         <v>143753</v>
       </c>
-      <c r="O55" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="N55" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" s="3">
         <v>46225</v>
       </c>
       <c r="B56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F56">
         <v>24.012</v>
       </c>
       <c r="G56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H56">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I56" s="1">
-        <v>1.66</v>
+        <v>39.86</v>
       </c>
       <c r="J56">
-        <v>39.85992</v>
+        <v>1.69</v>
       </c>
       <c r="K56" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L56" s="1">
-        <v>40.58028</v>
-      </c>
-      <c r="M56" t="s">
-        <v>118</v>
-      </c>
-      <c r="N56">
+        <v>40.58</v>
+      </c>
+      <c r="L56" t="s">
+        <v>117</v>
+      </c>
+      <c r="M56">
         <v>78470</v>
       </c>
-      <c r="O56" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="N56" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" s="3">
         <v>46225</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F57">
         <v>17.751</v>
       </c>
       <c r="G57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H57">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I57" s="1">
-        <v>1.66</v>
+        <v>29.467</v>
       </c>
       <c r="J57">
-        <v>29.46666</v>
+        <v>1.69</v>
       </c>
       <c r="K57" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L57" s="1">
-        <v>29.99919</v>
-      </c>
-      <c r="M57" t="s">
-        <v>84</v>
-      </c>
-      <c r="N57">
+        <v>29.999</v>
+      </c>
+      <c r="L57" t="s">
+        <v>83</v>
+      </c>
+      <c r="M57">
         <v>74692</v>
       </c>
-      <c r="O57" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="N57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" s="3">
         <v>46225</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F58">
         <v>10</v>
       </c>
       <c r="G58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H58">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I58" s="1">
-        <v>1.66</v>
+        <v>16.6</v>
       </c>
       <c r="J58">
-        <v>16.6</v>
+        <v>1.69</v>
       </c>
       <c r="K58" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L58" s="1">
         <v>16.9</v>
       </c>
-      <c r="M58" t="s">
-        <v>119</v>
-      </c>
-      <c r="N58">
+      <c r="L58" t="s">
+        <v>118</v>
+      </c>
+      <c r="M58">
         <v>8254</v>
       </c>
-      <c r="O58" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="N58" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" s="3">
         <v>46225</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F59">
         <v>5.698</v>
       </c>
       <c r="G59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H59">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I59" s="1">
-        <v>1.66</v>
+        <v>9.459</v>
       </c>
       <c r="J59">
-        <v>9.458679999999999</v>
+        <v>1.69</v>
       </c>
       <c r="K59" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L59" s="1">
-        <v>9.629619999999999</v>
-      </c>
-      <c r="M59" t="s">
-        <v>120</v>
-      </c>
-      <c r="N59">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="L59" t="s">
+        <v>119</v>
+      </c>
+      <c r="M59">
         <v>58194</v>
       </c>
-      <c r="O59" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="N59" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" s="3">
         <v>46225</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F60">
         <v>16.651</v>
       </c>
       <c r="G60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H60">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I60" s="1">
-        <v>1.66</v>
+        <v>27.641</v>
       </c>
       <c r="J60">
-        <v>27.64066</v>
+        <v>1.69</v>
       </c>
       <c r="K60" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L60" s="1">
-        <v>28.14019</v>
-      </c>
-      <c r="M60" t="s">
-        <v>121</v>
-      </c>
-      <c r="N60">
+        <v>28.14</v>
+      </c>
+      <c r="L60" t="s">
+        <v>120</v>
+      </c>
+      <c r="M60">
         <v>67874</v>
       </c>
-      <c r="O60" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="N60" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="3">
         <v>46226</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F61">
         <v>1.418</v>
       </c>
       <c r="G61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H61">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I61" s="1">
-        <v>1.67</v>
+        <v>2.368</v>
       </c>
       <c r="J61">
-        <v>2.36806</v>
+        <v>1.7</v>
       </c>
       <c r="K61" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L61" s="1">
-        <v>2.4106</v>
-      </c>
-      <c r="M61" t="s">
-        <v>122</v>
-      </c>
-      <c r="N61">
+        <v>2.411</v>
+      </c>
+      <c r="L61" t="s">
+        <v>121</v>
+      </c>
+      <c r="M61">
         <v>44285</v>
       </c>
-      <c r="O61" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="N61" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" s="3">
         <v>46226</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F62">
         <v>2.482</v>
       </c>
       <c r="G62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H62">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I62" s="1">
-        <v>1.67</v>
+        <v>4.145</v>
       </c>
       <c r="J62">
-        <v>4.14494</v>
+        <v>1.7</v>
       </c>
       <c r="K62" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L62" s="1">
-        <v>4.2194</v>
-      </c>
-      <c r="M62" t="s">
-        <v>123</v>
-      </c>
-      <c r="N62">
+        <v>4.219</v>
+      </c>
+      <c r="L62" t="s">
+        <v>122</v>
+      </c>
+      <c r="M62">
         <v>188047</v>
       </c>
-      <c r="O62" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+      <c r="N62" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" s="3">
         <v>46226</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F63">
         <v>32.018</v>
       </c>
       <c r="G63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H63">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I63" s="1">
-        <v>1.67</v>
+        <v>53.47</v>
       </c>
       <c r="J63">
-        <v>53.47006</v>
+        <v>1.7</v>
       </c>
       <c r="K63" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L63" s="1">
-        <v>54.4306</v>
-      </c>
-      <c r="M63" t="s">
-        <v>124</v>
-      </c>
-      <c r="N63">
+        <v>54.431</v>
+      </c>
+      <c r="L63" t="s">
+        <v>123</v>
+      </c>
+      <c r="M63">
         <v>78551</v>
       </c>
-      <c r="O63" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="N63" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" s="3">
         <v>46226</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F64">
         <v>5.129</v>
       </c>
       <c r="G64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H64">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I64" s="1">
-        <v>1.67</v>
+        <v>8.565</v>
       </c>
       <c r="J64">
-        <v>8.565429999999999</v>
+        <v>1.7</v>
       </c>
       <c r="K64" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L64" s="1">
-        <v>8.7193</v>
-      </c>
-      <c r="M64" t="s">
-        <v>108</v>
-      </c>
-      <c r="N64">
+        <v>8.718999999999999</v>
+      </c>
+      <c r="L64" t="s">
+        <v>107</v>
+      </c>
+      <c r="M64">
         <v>175972</v>
       </c>
-      <c r="O64" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
+      <c r="N64" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" s="3">
         <v>46226</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F65">
         <v>4.241</v>
       </c>
       <c r="G65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H65">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I65" s="1">
-        <v>1.67</v>
+        <v>7.082</v>
       </c>
       <c r="J65">
-        <v>7.08247</v>
+        <v>1.7</v>
       </c>
       <c r="K65" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L65" s="1">
-        <v>7.2097</v>
-      </c>
-      <c r="M65" t="s">
-        <v>125</v>
-      </c>
-      <c r="N65">
+        <v>7.21</v>
+      </c>
+      <c r="L65" t="s">
+        <v>124</v>
+      </c>
+      <c r="M65">
         <v>143777</v>
       </c>
-      <c r="O65" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15">
+      <c r="N65" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" s="3">
         <v>46226</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D66" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F66">
         <v>9.087999999999999</v>
       </c>
       <c r="G66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H66">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I66" s="1">
-        <v>1.67</v>
+        <v>15.177</v>
       </c>
       <c r="J66">
-        <v>15.17696</v>
+        <v>1.7</v>
       </c>
       <c r="K66" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L66" s="1">
-        <v>15.4496</v>
-      </c>
-      <c r="M66" t="s">
-        <v>126</v>
-      </c>
-      <c r="N66">
+        <v>15.45</v>
+      </c>
+      <c r="L66" t="s">
+        <v>125</v>
+      </c>
+      <c r="M66">
         <v>10403</v>
       </c>
-      <c r="O66" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
+      <c r="N66" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" s="3">
         <v>46226</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D67" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F67">
         <v>5</v>
       </c>
       <c r="G67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H67">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I67" s="1">
-        <v>1.67</v>
+        <v>8.35</v>
       </c>
       <c r="J67">
-        <v>8.35</v>
+        <v>1.7</v>
       </c>
       <c r="K67" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L67" s="1">
         <v>8.5</v>
       </c>
-      <c r="M67" t="s">
-        <v>103</v>
-      </c>
-      <c r="N67">
+      <c r="L67" t="s">
+        <v>102</v>
+      </c>
+      <c r="M67">
         <v>188817</v>
       </c>
-      <c r="O67" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
+      <c r="N67" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" s="3">
         <v>46226</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F68">
         <v>8.6</v>
       </c>
       <c r="G68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H68">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I68" s="1">
-        <v>1.67</v>
+        <v>14.362</v>
       </c>
       <c r="J68">
-        <v>14.362</v>
+        <v>1.7</v>
       </c>
       <c r="K68" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L68" s="1">
         <v>14.62</v>
       </c>
-      <c r="M68" t="s">
-        <v>127</v>
-      </c>
-      <c r="N68">
+      <c r="L68" t="s">
+        <v>126</v>
+      </c>
+      <c r="M68">
         <v>58258</v>
       </c>
-      <c r="O68" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
+      <c r="N68" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" s="3">
         <v>46226</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F69">
         <v>8</v>
       </c>
       <c r="G69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H69">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I69" s="1">
-        <v>1.67</v>
+        <v>13.36</v>
       </c>
       <c r="J69">
-        <v>13.36</v>
+        <v>1.7</v>
       </c>
       <c r="K69" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L69" s="1">
         <v>13.6</v>
       </c>
-      <c r="M69" t="s">
-        <v>128</v>
-      </c>
-      <c r="N69">
+      <c r="L69" t="s">
+        <v>127</v>
+      </c>
+      <c r="M69">
         <v>74753</v>
       </c>
-      <c r="O69" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
+      <c r="N69" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" s="3">
         <v>46227</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F70">
         <v>24</v>
       </c>
       <c r="G70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H70">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I70" s="1">
-        <v>1.69</v>
+        <v>40.56</v>
       </c>
       <c r="J70">
-        <v>40.56</v>
+        <v>1.72</v>
       </c>
       <c r="K70" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L70" s="1">
         <v>41.28</v>
       </c>
-      <c r="M70" t="s">
-        <v>129</v>
-      </c>
-      <c r="N70">
+      <c r="L70" t="s">
+        <v>128</v>
+      </c>
+      <c r="M70">
         <v>78612</v>
       </c>
-      <c r="O70" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
+      <c r="N70" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" s="3">
         <v>46227</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F71">
         <v>2.721</v>
       </c>
       <c r="G71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H71">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I71" s="1">
-        <v>1.69</v>
+        <v>4.598</v>
       </c>
       <c r="J71">
-        <v>4.59849</v>
+        <v>1.72</v>
       </c>
       <c r="K71" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L71" s="1">
-        <v>4.68012</v>
-      </c>
-      <c r="M71" t="s">
-        <v>130</v>
-      </c>
-      <c r="N71">
+        <v>4.68</v>
+      </c>
+      <c r="L71" t="s">
+        <v>129</v>
+      </c>
+      <c r="M71">
         <v>188834</v>
       </c>
-      <c r="O71" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15">
+      <c r="N71" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" s="3">
         <v>46227</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F72">
         <v>5.948</v>
       </c>
       <c r="G72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H72">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I72" s="1">
-        <v>1.69</v>
+        <v>10.052</v>
       </c>
       <c r="J72">
-        <v>10.05212</v>
+        <v>1.72</v>
       </c>
       <c r="K72" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L72" s="1">
-        <v>10.23056</v>
-      </c>
-      <c r="M72" t="s">
-        <v>98</v>
-      </c>
-      <c r="N72">
+        <v>10.231</v>
+      </c>
+      <c r="L72" t="s">
+        <v>97</v>
+      </c>
+      <c r="M72">
         <v>44317</v>
       </c>
-      <c r="O72" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15">
+      <c r="N72" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" s="3">
         <v>46227</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C73" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F73">
         <v>6.89</v>
       </c>
       <c r="G73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H73">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I73" s="1">
-        <v>1.69</v>
+        <v>11.644</v>
       </c>
       <c r="J73">
-        <v>11.6441</v>
+        <v>1.72</v>
       </c>
       <c r="K73" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L73" s="1">
-        <v>11.8508</v>
-      </c>
-      <c r="M73" t="s">
-        <v>111</v>
-      </c>
-      <c r="N73">
+        <v>11.851</v>
+      </c>
+      <c r="L73" t="s">
+        <v>110</v>
+      </c>
+      <c r="M73">
         <v>1433</v>
       </c>
-      <c r="O73" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
+      <c r="N73" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" s="3">
         <v>46227</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F74">
         <v>6.651</v>
       </c>
       <c r="G74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H74">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I74" s="1">
-        <v>1.69</v>
+        <v>11.24</v>
       </c>
       <c r="J74">
-        <v>11.24019</v>
+        <v>1.72</v>
       </c>
       <c r="K74" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L74" s="1">
-        <v>11.43972</v>
-      </c>
-      <c r="M74" t="s">
-        <v>131</v>
-      </c>
-      <c r="N74">
+        <v>11.44</v>
+      </c>
+      <c r="L74" t="s">
+        <v>130</v>
+      </c>
+      <c r="M74">
         <v>95464</v>
       </c>
-      <c r="O74" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
+      <c r="N74" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" s="3">
         <v>46227</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F75">
         <v>3.11</v>
       </c>
       <c r="G75" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H75">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I75" s="1">
-        <v>1.69</v>
+        <v>5.256</v>
       </c>
       <c r="J75">
-        <v>5.2559</v>
+        <v>1.72</v>
       </c>
       <c r="K75" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L75" s="1">
-        <v>5.3492</v>
-      </c>
-      <c r="M75" t="s">
-        <v>132</v>
-      </c>
-      <c r="N75">
+        <v>5.349</v>
+      </c>
+      <c r="L75" t="s">
+        <v>131</v>
+      </c>
+      <c r="M75">
         <v>188076</v>
       </c>
-      <c r="O75" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
+      <c r="N75" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76" s="3">
         <v>46227</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D76" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F76">
         <v>5</v>
       </c>
       <c r="G76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H76">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I76" s="1">
-        <v>1.69</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J76">
-        <v>8.449999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="K76" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L76" s="1">
         <v>8.6</v>
       </c>
-      <c r="M76" t="s">
-        <v>133</v>
-      </c>
-      <c r="N76">
+      <c r="L76" t="s">
+        <v>132</v>
+      </c>
+      <c r="M76">
         <v>74799</v>
       </c>
-      <c r="O76" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
+      <c r="N76" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77" s="3">
         <v>46227</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D77" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F77">
         <v>100.041</v>
       </c>
       <c r="G77" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H77">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I77" s="1">
-        <v>1.69</v>
+        <v>169.069</v>
       </c>
       <c r="J77">
-        <v>169.06929</v>
+        <v>1.72</v>
       </c>
       <c r="K77" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L77" s="1">
-        <v>172.07052</v>
-      </c>
-      <c r="M77" t="s">
-        <v>134</v>
-      </c>
-      <c r="N77">
+        <v>172.071</v>
+      </c>
+      <c r="L77" t="s">
+        <v>133</v>
+      </c>
+      <c r="M77">
         <v>0</v>
       </c>
-      <c r="O77" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
+      <c r="N77" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78" s="3">
         <v>46227</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C78" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D78" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F78">
         <v>100.081</v>
       </c>
       <c r="G78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H78">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I78" s="1">
-        <v>1.69</v>
+        <v>169.137</v>
       </c>
       <c r="J78">
-        <v>169.13689</v>
+        <v>1.72</v>
       </c>
       <c r="K78" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L78" s="1">
-        <v>172.13932</v>
-      </c>
-      <c r="M78" t="s">
-        <v>135</v>
-      </c>
-      <c r="N78">
+        <v>172.139</v>
+      </c>
+      <c r="L78" t="s">
+        <v>134</v>
+      </c>
+      <c r="M78">
         <v>0</v>
       </c>
-      <c r="O78" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15">
+      <c r="N78" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79" s="3">
         <v>46227</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F79">
         <v>6</v>
       </c>
       <c r="G79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H79">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I79" s="1">
-        <v>1.69</v>
+        <v>10.14</v>
       </c>
       <c r="J79">
-        <v>10.14</v>
+        <v>1.72</v>
       </c>
       <c r="K79" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L79" s="1">
         <v>10.32</v>
       </c>
-      <c r="M79" t="s">
-        <v>95</v>
-      </c>
-      <c r="N79">
+      <c r="L79" t="s">
+        <v>94</v>
+      </c>
+      <c r="M79">
         <v>38765</v>
       </c>
-      <c r="O79" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15">
+      <c r="N79" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80" s="3">
         <v>46227</v>
       </c>
       <c r="B80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C80" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E80" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F80">
         <v>200.019</v>
       </c>
       <c r="G80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H80">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I80" s="1">
-        <v>1.51</v>
+        <v>302.029</v>
       </c>
       <c r="J80">
-        <v>302.02869</v>
+        <v>1.54</v>
       </c>
       <c r="K80" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L80" s="1">
-        <v>308.02926</v>
-      </c>
-      <c r="M80" t="s">
-        <v>136</v>
-      </c>
-      <c r="N80">
+        <v>308.029</v>
+      </c>
+      <c r="L80" t="s">
+        <v>135</v>
+      </c>
+      <c r="M80">
         <v>0</v>
       </c>
-      <c r="O80" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15">
+      <c r="N80" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" s="3">
         <v>46227</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D81" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F81">
         <v>39.791</v>
       </c>
       <c r="G81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H81">
-        <v>1.619</v>
+        <v>1.69</v>
       </c>
       <c r="I81" s="1">
-        <v>1.69</v>
+        <v>67.247</v>
       </c>
       <c r="J81">
-        <v>67.24679</v>
+        <v>1.72</v>
       </c>
       <c r="K81" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L81" s="1">
-        <v>68.44052000000001</v>
-      </c>
-      <c r="M81" t="s">
-        <v>137</v>
-      </c>
-      <c r="N81">
+        <v>68.441</v>
+      </c>
+      <c r="L81" t="s">
+        <v>136</v>
+      </c>
+      <c r="M81">
         <v>2251</v>
       </c>
-      <c r="O81" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15">
+      <c r="N81" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82" s="3">
         <v>46228</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D82" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F82">
         <v>7.609</v>
       </c>
       <c r="G82" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H82">
-        <v>1.619</v>
+        <v>1.71</v>
       </c>
       <c r="I82" s="1">
-        <v>1.71</v>
+        <v>13.011</v>
       </c>
       <c r="J82">
-        <v>13.01139</v>
+        <v>1.74</v>
       </c>
       <c r="K82" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L82" s="1">
-        <v>13.23966</v>
-      </c>
-      <c r="M82" t="s">
-        <v>138</v>
-      </c>
-      <c r="N82">
+        <v>13.24</v>
+      </c>
+      <c r="L82" t="s">
+        <v>137</v>
+      </c>
+      <c r="M82">
         <v>14666</v>
       </c>
-      <c r="O82" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15">
+      <c r="N82" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83" s="3">
         <v>46230</v>
       </c>
       <c r="B83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D83" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E83" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F83">
         <v>2.491</v>
       </c>
       <c r="G83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H83">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I83" s="1">
-        <v>1.72</v>
+        <v>4.285</v>
       </c>
       <c r="J83">
-        <v>4.28452</v>
+        <v>1.75</v>
       </c>
       <c r="K83" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L83" s="1">
-        <v>4.35925</v>
-      </c>
-      <c r="M83" t="s">
-        <v>116</v>
-      </c>
-      <c r="N83">
+        <v>4.359</v>
+      </c>
+      <c r="L83" t="s">
+        <v>115</v>
+      </c>
+      <c r="M83">
         <v>44343</v>
       </c>
-      <c r="O83" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15">
+      <c r="N83" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84" s="3">
         <v>46230</v>
       </c>
       <c r="B84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E84" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F84">
         <v>4.783</v>
       </c>
       <c r="G84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H84">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I84" s="1">
-        <v>1.72</v>
+        <v>8.227</v>
       </c>
       <c r="J84">
-        <v>8.226760000000001</v>
+        <v>1.75</v>
       </c>
       <c r="K84" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L84" s="1">
-        <v>8.37025</v>
-      </c>
-      <c r="M84" t="s">
-        <v>123</v>
-      </c>
-      <c r="N84">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L84" t="s">
+        <v>122</v>
+      </c>
+      <c r="M84">
         <v>188101</v>
       </c>
-      <c r="O84" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15">
+      <c r="N84" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85" s="3">
         <v>46230</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E85" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F85">
         <v>3.183</v>
       </c>
       <c r="G85" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H85">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I85" s="1">
-        <v>1.72</v>
+        <v>5.475</v>
       </c>
       <c r="J85">
-        <v>5.47476</v>
+        <v>1.75</v>
       </c>
       <c r="K85" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L85" s="1">
-        <v>5.57025</v>
-      </c>
-      <c r="M85" t="s">
-        <v>109</v>
-      </c>
-      <c r="N85">
+        <v>5.57</v>
+      </c>
+      <c r="L85" t="s">
+        <v>108</v>
+      </c>
+      <c r="M85">
         <v>143795</v>
       </c>
-      <c r="O85" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15">
+      <c r="N85" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86" s="3">
         <v>46230</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F86">
         <v>33.011</v>
       </c>
       <c r="G86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H86">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I86" s="1">
-        <v>1.72</v>
+        <v>56.779</v>
       </c>
       <c r="J86">
-        <v>56.77892</v>
+        <v>1.75</v>
       </c>
       <c r="K86" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L86" s="1">
-        <v>57.76925</v>
-      </c>
-      <c r="M86" t="s">
-        <v>119</v>
-      </c>
-      <c r="N86">
+        <v>57.769</v>
+      </c>
+      <c r="L86" t="s">
+        <v>118</v>
+      </c>
+      <c r="M86">
         <v>78968</v>
       </c>
-      <c r="O86" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15">
+      <c r="N86" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87" s="3">
         <v>46230</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E87" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F87">
         <v>3.4</v>
       </c>
       <c r="G87" t="s">
+        <v>70</v>
+      </c>
+      <c r="H87">
+        <v>1.72</v>
+      </c>
+      <c r="I87" s="1">
+        <v>5.848</v>
+      </c>
+      <c r="J87">
+        <v>1.75</v>
+      </c>
+      <c r="K87" s="1">
+        <v>5.95</v>
+      </c>
+      <c r="L87" t="s">
         <v>71</v>
       </c>
-      <c r="H87">
-        <v>1.619</v>
-      </c>
-      <c r="I87" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="J87">
-        <v>5.848</v>
-      </c>
-      <c r="K87" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L87" s="1">
-        <v>5.95</v>
-      </c>
-      <c r="M87" t="s">
-        <v>72</v>
-      </c>
-      <c r="N87">
+      <c r="M87">
         <v>188868</v>
       </c>
-      <c r="O87" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15">
+      <c r="N87" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88" s="3">
         <v>46230</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E88" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F88">
         <v>6.36</v>
       </c>
       <c r="G88" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H88">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I88" s="1">
-        <v>1.72</v>
+        <v>10.939</v>
       </c>
       <c r="J88">
-        <v>10.9392</v>
+        <v>1.75</v>
       </c>
       <c r="K88" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L88" s="1">
         <v>11.13</v>
       </c>
-      <c r="M88" t="s">
-        <v>139</v>
-      </c>
-      <c r="N88">
+      <c r="L88" t="s">
+        <v>138</v>
+      </c>
+      <c r="M88">
         <v>95504</v>
       </c>
-      <c r="O88" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15">
+      <c r="N88" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89" s="3">
         <v>46230</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D89" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E89" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F89">
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H89">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I89" s="1">
-        <v>1.72</v>
+        <v>17.2</v>
       </c>
       <c r="J89">
-        <v>17.2</v>
+        <v>1.75</v>
       </c>
       <c r="K89" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L89" s="1">
         <v>17.5</v>
       </c>
-      <c r="M89" t="s">
-        <v>140</v>
-      </c>
-      <c r="N89">
+      <c r="L89" t="s">
+        <v>139</v>
+      </c>
+      <c r="M89">
         <v>74827</v>
       </c>
-      <c r="O89" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15">
+      <c r="N89" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90" s="3">
         <v>46230</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C90" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D90" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E90" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F90">
         <v>5.669</v>
       </c>
       <c r="G90" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H90">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I90" s="1">
-        <v>1.72</v>
+        <v>9.750999999999999</v>
       </c>
       <c r="J90">
-        <v>9.750679999999999</v>
+        <v>1.75</v>
       </c>
       <c r="K90" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L90" s="1">
-        <v>9.92075</v>
-      </c>
-      <c r="M90" t="s">
-        <v>112</v>
-      </c>
-      <c r="N90">
+        <v>9.920999999999999</v>
+      </c>
+      <c r="L90" t="s">
+        <v>111</v>
+      </c>
+      <c r="M90">
         <v>83917</v>
       </c>
-      <c r="O90" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15">
+      <c r="N90" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91" s="3">
         <v>46230</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E91" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F91">
         <v>5.72</v>
       </c>
       <c r="G91" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H91">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I91" s="1">
-        <v>1.72</v>
+        <v>9.837999999999999</v>
       </c>
       <c r="J91">
-        <v>9.8384</v>
+        <v>1.75</v>
       </c>
       <c r="K91" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L91" s="1">
         <v>10.01</v>
       </c>
-      <c r="M91" t="s">
-        <v>141</v>
-      </c>
-      <c r="N91">
+      <c r="L91" t="s">
+        <v>140</v>
+      </c>
+      <c r="M91">
         <v>1492</v>
       </c>
-      <c r="O91" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15">
+      <c r="N91" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92" s="3">
         <v>46230</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D92" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E92" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F92">
         <v>10</v>
       </c>
       <c r="G92" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H92">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I92" s="1">
-        <v>1.72</v>
+        <v>17.2</v>
       </c>
       <c r="J92">
-        <v>17.2</v>
+        <v>1.75</v>
       </c>
       <c r="K92" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L92" s="1">
         <v>17.5</v>
       </c>
-      <c r="M92" t="s">
-        <v>142</v>
-      </c>
-      <c r="N92">
+      <c r="L92" t="s">
+        <v>141</v>
+      </c>
+      <c r="M92">
         <v>8267</v>
       </c>
-      <c r="O92" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15">
+      <c r="N92" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93" s="3">
         <v>46230</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F93">
         <v>28.609</v>
       </c>
       <c r="G93" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I93" s="1">
-        <v>0.63</v>
+        <v>18.024</v>
       </c>
       <c r="J93">
-        <v>18.02367</v>
+        <v>0.64</v>
       </c>
       <c r="K93" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L93" s="1">
-        <v>18.30976</v>
-      </c>
-      <c r="M93" t="s">
-        <v>143</v>
-      </c>
-      <c r="N93">
+        <v>18.31</v>
+      </c>
+      <c r="L93" t="s">
+        <v>142</v>
+      </c>
+      <c r="M93">
         <v>181693</v>
       </c>
-      <c r="O93" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15">
+      <c r="N93" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94" s="3">
         <v>46230</v>
       </c>
       <c r="B94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E94" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F94">
         <v>23.503</v>
       </c>
       <c r="G94" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H94">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I94" s="1">
-        <v>1.72</v>
+        <v>40.425</v>
       </c>
       <c r="J94">
-        <v>40.42516</v>
+        <v>1.75</v>
       </c>
       <c r="K94" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L94" s="1">
-        <v>41.13025</v>
-      </c>
-      <c r="M94" t="s">
-        <v>144</v>
-      </c>
-      <c r="N94">
+        <v>41.13</v>
+      </c>
+      <c r="L94" t="s">
+        <v>143</v>
+      </c>
+      <c r="M94">
         <v>68055</v>
       </c>
-      <c r="O94" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15">
+      <c r="N94" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95" s="3">
         <v>46231</v>
       </c>
       <c r="B95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D95" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E95" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F95">
         <v>5.703</v>
       </c>
       <c r="G95" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H95">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I95" s="1">
-        <v>1.72</v>
+        <v>9.808999999999999</v>
       </c>
       <c r="J95">
-        <v>9.80916</v>
+        <v>1.75</v>
       </c>
       <c r="K95" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L95" s="1">
-        <v>9.98025</v>
-      </c>
-      <c r="M95" t="s">
-        <v>145</v>
-      </c>
-      <c r="N95">
+        <v>9.98</v>
+      </c>
+      <c r="L95" t="s">
+        <v>144</v>
+      </c>
+      <c r="M95">
         <v>44388</v>
       </c>
-      <c r="O95" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15">
+      <c r="N95" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96" s="3">
         <v>46231</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D96" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E96" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F96">
         <v>3.291</v>
       </c>
       <c r="G96" t="s">
+        <v>70</v>
+      </c>
+      <c r="H96">
+        <v>1.72</v>
+      </c>
+      <c r="I96" s="1">
+        <v>5.661</v>
+      </c>
+      <c r="J96">
+        <v>1.75</v>
+      </c>
+      <c r="K96" s="1">
+        <v>5.759</v>
+      </c>
+      <c r="L96" t="s">
         <v>71</v>
       </c>
-      <c r="H96">
-        <v>1.653</v>
-      </c>
-      <c r="I96" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="J96">
-        <v>5.66052</v>
-      </c>
-      <c r="K96" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L96" s="1">
-        <v>5.75925</v>
-      </c>
-      <c r="M96" t="s">
-        <v>72</v>
-      </c>
-      <c r="N96">
+      <c r="M96">
         <v>188135</v>
       </c>
-      <c r="O96" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15">
+      <c r="N96" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97" s="3">
         <v>46231</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D97" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E97" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F97">
         <v>2.211</v>
       </c>
       <c r="G97" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H97">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I97" s="1">
-        <v>1.72</v>
+        <v>3.803</v>
       </c>
       <c r="J97">
-        <v>3.80292</v>
+        <v>1.75</v>
       </c>
       <c r="K97" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L97" s="1">
-        <v>3.86925</v>
-      </c>
-      <c r="M97" t="s">
-        <v>146</v>
-      </c>
-      <c r="N97">
+        <v>3.869</v>
+      </c>
+      <c r="L97" t="s">
+        <v>145</v>
+      </c>
+      <c r="M97">
         <v>188884</v>
       </c>
-      <c r="O97" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15">
+      <c r="N97" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98" s="3">
         <v>46231</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D98" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E98" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F98">
         <v>7.48</v>
       </c>
       <c r="G98" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H98">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I98" s="1">
-        <v>1.72</v>
+        <v>12.866</v>
       </c>
       <c r="J98">
-        <v>12.8656</v>
+        <v>1.75</v>
       </c>
       <c r="K98" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L98" s="1">
         <v>13.09</v>
       </c>
-      <c r="M98" t="s">
-        <v>96</v>
-      </c>
-      <c r="N98">
+      <c r="L98" t="s">
+        <v>95</v>
+      </c>
+      <c r="M98">
         <v>83974</v>
       </c>
-      <c r="O98" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15">
+      <c r="N98" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99" s="3">
         <v>46231</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E99" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F99">
         <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H99">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I99" s="1">
-        <v>1.72</v>
+        <v>34.4</v>
       </c>
       <c r="J99">
-        <v>34.4</v>
+        <v>1.75</v>
       </c>
       <c r="K99" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L99" s="1">
         <v>35</v>
       </c>
-      <c r="M99" t="s">
-        <v>136</v>
-      </c>
-      <c r="N99">
+      <c r="L99" t="s">
+        <v>135</v>
+      </c>
+      <c r="M99">
         <v>78747</v>
       </c>
-      <c r="O99" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15">
+      <c r="N99" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100" s="3">
         <v>46231</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D100" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E100" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F100">
         <v>2.171</v>
       </c>
       <c r="G100" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H100">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I100" s="1">
-        <v>1.72</v>
+        <v>3.734</v>
       </c>
       <c r="J100">
-        <v>3.73412</v>
+        <v>1.75</v>
       </c>
       <c r="K100" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L100" s="1">
-        <v>3.79925</v>
-      </c>
-      <c r="M100" t="s">
-        <v>74</v>
-      </c>
-      <c r="N100">
+        <v>3.799</v>
+      </c>
+      <c r="L100" t="s">
+        <v>73</v>
+      </c>
+      <c r="M100">
         <v>143808</v>
       </c>
-      <c r="O100" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15">
+      <c r="N100" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
       <c r="A101" s="3">
         <v>46231</v>
       </c>
       <c r="B101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E101" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F101">
         <v>7.103</v>
       </c>
       <c r="G101" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H101">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I101" s="1">
-        <v>1.72</v>
+        <v>12.217</v>
       </c>
       <c r="J101">
-        <v>12.21716</v>
+        <v>1.75</v>
       </c>
       <c r="K101" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L101" s="1">
-        <v>12.43025</v>
-      </c>
-      <c r="M101" t="s">
-        <v>91</v>
-      </c>
-      <c r="N101">
+        <v>12.43</v>
+      </c>
+      <c r="L101" t="s">
+        <v>90</v>
+      </c>
+      <c r="M101">
         <v>58277</v>
       </c>
-      <c r="O101" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15">
+      <c r="N101" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102" s="3">
         <v>46231</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D102" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E102" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F102">
         <v>9.411</v>
       </c>
       <c r="G102" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H102">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I102" s="1">
-        <v>1.72</v>
+        <v>16.187</v>
       </c>
       <c r="J102">
-        <v>16.18692</v>
+        <v>1.75</v>
       </c>
       <c r="K102" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L102" s="1">
-        <v>16.46925</v>
-      </c>
-      <c r="M102" t="s">
-        <v>147</v>
-      </c>
-      <c r="N102">
+        <v>16.469</v>
+      </c>
+      <c r="L102" t="s">
+        <v>146</v>
+      </c>
+      <c r="M102">
         <v>1542</v>
       </c>
-      <c r="O102" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15">
+      <c r="N102" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103" s="3">
         <v>46231</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D103" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E103" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F103">
         <v>5.32</v>
       </c>
       <c r="G103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H103">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I103" s="1">
-        <v>1.72</v>
+        <v>9.15</v>
       </c>
       <c r="J103">
-        <v>9.150399999999999</v>
+        <v>1.75</v>
       </c>
       <c r="K103" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L103" s="1">
         <v>9.31</v>
       </c>
-      <c r="M103" t="s">
-        <v>84</v>
-      </c>
-      <c r="N103">
+      <c r="L103" t="s">
+        <v>83</v>
+      </c>
+      <c r="M103">
         <v>95539</v>
       </c>
-      <c r="O103" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15">
+      <c r="N103" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104" s="3">
         <v>46231</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D104" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E104" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F104">
         <v>11.08</v>
       </c>
       <c r="G104" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H104">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I104" s="1">
-        <v>1.72</v>
+        <v>19.058</v>
       </c>
       <c r="J104">
-        <v>19.0576</v>
+        <v>1.75</v>
       </c>
       <c r="K104" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L104" s="1">
         <v>19.39</v>
       </c>
-      <c r="M104" t="s">
-        <v>148</v>
-      </c>
-      <c r="N104">
+      <c r="L104" t="s">
+        <v>147</v>
+      </c>
+      <c r="M104">
         <v>8281</v>
       </c>
-      <c r="O104" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15">
+      <c r="N104" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105" s="3">
         <v>46231</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D105" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E105" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F105">
         <v>4</v>
       </c>
       <c r="G105" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H105">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I105" s="1">
-        <v>1.72</v>
+        <v>6.88</v>
       </c>
       <c r="J105">
-        <v>6.88</v>
+        <v>1.75</v>
       </c>
       <c r="K105" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L105" s="1">
         <v>7</v>
       </c>
-      <c r="M105" t="s">
-        <v>149</v>
-      </c>
-      <c r="N105">
+      <c r="L105" t="s">
+        <v>148</v>
+      </c>
+      <c r="M105">
         <v>74863</v>
       </c>
-      <c r="O105" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15">
+      <c r="N105" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
       <c r="A106" s="3">
         <v>46232</v>
       </c>
       <c r="B106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D106" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E106" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F106">
         <v>4</v>
       </c>
       <c r="G106" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H106">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I106" s="1">
-        <v>1.72</v>
+        <v>6.88</v>
       </c>
       <c r="J106">
-        <v>6.88</v>
+        <v>1.75</v>
       </c>
       <c r="K106" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L106" s="1">
         <v>7</v>
       </c>
-      <c r="M106" t="s">
-        <v>147</v>
-      </c>
-      <c r="N106">
+      <c r="L106" t="s">
+        <v>146</v>
+      </c>
+      <c r="M106">
         <v>44411</v>
       </c>
-      <c r="O106" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15">
+      <c r="N106" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107" s="3">
         <v>46232</v>
       </c>
       <c r="B107" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C107" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D107" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E107" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F107">
         <v>28.56</v>
       </c>
       <c r="G107" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H107">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I107" s="1">
-        <v>1.72</v>
+        <v>49.123</v>
       </c>
       <c r="J107">
-        <v>49.1232</v>
+        <v>1.75</v>
       </c>
       <c r="K107" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L107" s="1">
         <v>49.98</v>
       </c>
-      <c r="M107" t="s">
-        <v>150</v>
-      </c>
-      <c r="N107">
+      <c r="L107" t="s">
+        <v>149</v>
+      </c>
+      <c r="M107">
         <v>340135</v>
       </c>
-      <c r="O107" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15">
+      <c r="N107" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
       <c r="A108" s="3">
         <v>46232</v>
       </c>
       <c r="B108" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E108" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F108">
         <v>25.2</v>
       </c>
       <c r="G108" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H108">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I108" s="1">
-        <v>1.72</v>
+        <v>43.344</v>
       </c>
       <c r="J108">
-        <v>43.344</v>
+        <v>1.75</v>
       </c>
       <c r="K108" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L108" s="1">
         <v>44.1</v>
       </c>
-      <c r="M108" t="s">
-        <v>151</v>
-      </c>
-      <c r="N108">
+      <c r="L108" t="s">
+        <v>150</v>
+      </c>
+      <c r="M108">
         <v>340135</v>
       </c>
-      <c r="O108" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15">
+      <c r="N108" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
       <c r="A109" s="3">
         <v>46232</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D109" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E109" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F109">
         <v>9.651</v>
       </c>
       <c r="G109" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H109">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I109" s="1">
-        <v>1.72</v>
+        <v>16.6</v>
       </c>
       <c r="J109">
-        <v>16.59972</v>
+        <v>1.75</v>
       </c>
       <c r="K109" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L109" s="1">
-        <v>16.88925</v>
-      </c>
-      <c r="M109" t="s">
-        <v>102</v>
-      </c>
-      <c r="N109">
+        <v>16.889</v>
+      </c>
+      <c r="L109" t="s">
+        <v>101</v>
+      </c>
+      <c r="M109">
         <v>1577</v>
       </c>
-      <c r="O109" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15">
+      <c r="N109" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
       <c r="A110" s="3">
         <v>46232</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D110" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E110" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F110">
         <v>3.669</v>
       </c>
       <c r="G110" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H110">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I110" s="1">
-        <v>1.72</v>
+        <v>6.311</v>
       </c>
       <c r="J110">
-        <v>6.31068</v>
+        <v>1.75</v>
       </c>
       <c r="K110" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L110" s="1">
-        <v>6.42075</v>
-      </c>
-      <c r="M110" t="s">
-        <v>152</v>
-      </c>
-      <c r="N110">
+        <v>6.421</v>
+      </c>
+      <c r="L110" t="s">
+        <v>151</v>
+      </c>
+      <c r="M110">
         <v>188907</v>
       </c>
-      <c r="O110" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15">
+      <c r="N110" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111" s="3">
         <v>46232</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E111" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F111">
         <v>11</v>
       </c>
       <c r="G111" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H111">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I111" s="1">
-        <v>1.72</v>
+        <v>18.92</v>
       </c>
       <c r="J111">
-        <v>18.92</v>
+        <v>1.75</v>
       </c>
       <c r="K111" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L111" s="1">
         <v>19.25</v>
       </c>
-      <c r="M111" t="s">
-        <v>153</v>
-      </c>
-      <c r="N111">
+      <c r="L111" t="s">
+        <v>152</v>
+      </c>
+      <c r="M111">
         <v>0</v>
       </c>
-      <c r="O111" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15">
+      <c r="N111" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
       <c r="A112" s="3">
         <v>46232</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D112" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E112" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F112">
         <v>5.8</v>
       </c>
       <c r="G112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H112">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I112" s="1">
-        <v>1.72</v>
+        <v>9.976000000000001</v>
       </c>
       <c r="J112">
-        <v>9.976000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="K112" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L112" s="1">
         <v>10.15</v>
       </c>
-      <c r="M112" t="s">
-        <v>154</v>
-      </c>
-      <c r="N112">
+      <c r="L112" t="s">
+        <v>153</v>
+      </c>
+      <c r="M112">
         <v>74909</v>
       </c>
-      <c r="O112" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15">
+      <c r="N112" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
       <c r="A113" s="3">
         <v>46232</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E113" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F113">
         <v>34</v>
       </c>
       <c r="G113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H113">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I113" s="1">
-        <v>1.72</v>
+        <v>58.48</v>
       </c>
       <c r="J113">
-        <v>58.48</v>
+        <v>1.75</v>
       </c>
       <c r="K113" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L113" s="1">
         <v>59.5</v>
       </c>
-      <c r="M113" t="s">
-        <v>128</v>
-      </c>
-      <c r="N113">
+      <c r="L113" t="s">
+        <v>127</v>
+      </c>
+      <c r="M113">
         <v>78834</v>
       </c>
-      <c r="O113" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15">
+      <c r="N113" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14">
       <c r="A114" s="3">
         <v>46232</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C114" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E114" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F114">
         <v>6.6</v>
       </c>
       <c r="G114" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H114">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I114" s="1">
-        <v>1.72</v>
+        <v>11.352</v>
       </c>
       <c r="J114">
-        <v>11.352</v>
+        <v>1.75</v>
       </c>
       <c r="K114" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L114" s="1">
         <v>11.55</v>
       </c>
-      <c r="M114" t="s">
-        <v>131</v>
-      </c>
-      <c r="N114">
+      <c r="L114" t="s">
+        <v>130</v>
+      </c>
+      <c r="M114">
         <v>84032</v>
       </c>
-      <c r="O114" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15">
+      <c r="N114" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115" s="3">
         <v>46232</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D115" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E115" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F115">
         <v>10</v>
       </c>
       <c r="G115" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H115">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I115" s="1">
-        <v>1.72</v>
+        <v>17.2</v>
       </c>
       <c r="J115">
-        <v>17.2</v>
+        <v>1.75</v>
       </c>
       <c r="K115" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L115" s="1">
         <v>17.5</v>
       </c>
-      <c r="M115" t="s">
-        <v>109</v>
-      </c>
-      <c r="N115">
+      <c r="L115" t="s">
+        <v>108</v>
+      </c>
+      <c r="M115">
         <v>8297</v>
       </c>
-      <c r="O115" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15">
+      <c r="N115" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
       <c r="A116" s="3">
         <v>46232</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D116" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E116" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F116">
         <v>4.023</v>
       </c>
       <c r="G116" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H116">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I116" s="1">
-        <v>1.72</v>
+        <v>6.92</v>
       </c>
       <c r="J116">
-        <v>6.91956</v>
+        <v>1.75</v>
       </c>
       <c r="K116" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L116" s="1">
-        <v>7.04025</v>
-      </c>
-      <c r="M116" t="s">
-        <v>155</v>
-      </c>
-      <c r="N116">
+        <v>7.04</v>
+      </c>
+      <c r="L116" t="s">
+        <v>154</v>
+      </c>
+      <c r="M116">
         <v>58301</v>
       </c>
-      <c r="O116" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15">
+      <c r="N116" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117" s="3">
         <v>46232</v>
       </c>
       <c r="B117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C117" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E117" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F117">
         <v>3.451</v>
       </c>
       <c r="G117" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H117">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I117" s="1">
-        <v>1.72</v>
+        <v>5.936</v>
       </c>
       <c r="J117">
-        <v>5.93572</v>
+        <v>1.75</v>
       </c>
       <c r="K117" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L117" s="1">
-        <v>6.03925</v>
-      </c>
-      <c r="M117" t="s">
-        <v>96</v>
-      </c>
-      <c r="N117">
+        <v>6.039</v>
+      </c>
+      <c r="L117" t="s">
+        <v>95</v>
+      </c>
+      <c r="M117">
         <v>95571</v>
       </c>
-      <c r="O117" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15">
+      <c r="N117" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
       <c r="A118" s="3">
         <v>46232</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C118" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E118" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F118">
         <v>18</v>
       </c>
       <c r="G118" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H118">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I118" s="1">
-        <v>1.72</v>
+        <v>30.96</v>
       </c>
       <c r="J118">
-        <v>30.96</v>
+        <v>1.75</v>
       </c>
       <c r="K118" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L118" s="1">
         <v>31.5</v>
       </c>
-      <c r="M118" t="s">
-        <v>124</v>
-      </c>
-      <c r="N118">
+      <c r="L118" t="s">
+        <v>123</v>
+      </c>
+      <c r="M118">
         <v>68194</v>
       </c>
-      <c r="O118" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15">
+      <c r="N118" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
       <c r="A119" s="3">
         <v>46232</v>
       </c>
       <c r="B119" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D119" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E119" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F119">
         <v>27.891</v>
       </c>
       <c r="G119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H119">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I119" s="1">
-        <v>1.72</v>
+        <v>47.973</v>
       </c>
       <c r="J119">
-        <v>47.97252</v>
+        <v>1.75</v>
       </c>
       <c r="K119" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L119" s="1">
-        <v>48.80925</v>
-      </c>
-      <c r="M119" t="s">
-        <v>156</v>
-      </c>
-      <c r="N119">
+        <v>48.809</v>
+      </c>
+      <c r="L119" t="s">
+        <v>155</v>
+      </c>
+      <c r="M119">
         <v>2258</v>
       </c>
-      <c r="O119" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15">
+      <c r="N119" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14">
       <c r="A120" s="3">
         <v>46233</v>
       </c>
       <c r="B120" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D120" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E120" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F120">
         <v>6.79</v>
       </c>
       <c r="G120" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H120">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I120" s="1">
-        <v>1.73</v>
+        <v>11.747</v>
       </c>
       <c r="J120">
-        <v>11.7467</v>
+        <v>1.76</v>
       </c>
       <c r="K120" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L120" s="1">
-        <v>11.9504</v>
-      </c>
-      <c r="M120" t="s">
-        <v>96</v>
-      </c>
-      <c r="N120">
+        <v>11.95</v>
+      </c>
+      <c r="L120" t="s">
+        <v>95</v>
+      </c>
+      <c r="M120">
         <v>188177</v>
       </c>
-      <c r="O120" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15">
+      <c r="N120" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
       <c r="A121" s="3">
         <v>46233</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D121" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E121" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F121">
         <v>7.841</v>
       </c>
       <c r="G121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H121">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I121" s="1">
-        <v>1.73</v>
+        <v>13.565</v>
       </c>
       <c r="J121">
-        <v>13.56493</v>
+        <v>1.76</v>
       </c>
       <c r="K121" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L121" s="1">
-        <v>13.80016</v>
-      </c>
-      <c r="M121" t="s">
-        <v>132</v>
-      </c>
-      <c r="N121">
+        <v>13.8</v>
+      </c>
+      <c r="L121" t="s">
+        <v>131</v>
+      </c>
+      <c r="M121">
         <v>84098</v>
       </c>
-      <c r="O121" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15">
+      <c r="N121" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
       <c r="A122" s="3">
         <v>46233</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C122" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D122" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E122" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F122">
         <v>6.761</v>
       </c>
       <c r="G122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H122">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I122" s="1">
-        <v>1.73</v>
+        <v>11.697</v>
       </c>
       <c r="J122">
-        <v>11.69653</v>
+        <v>1.76</v>
       </c>
       <c r="K122" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L122" s="1">
-        <v>11.89936</v>
-      </c>
-      <c r="M122" t="s">
-        <v>136</v>
-      </c>
-      <c r="N122">
+        <v>11.899</v>
+      </c>
+      <c r="L122" t="s">
+        <v>135</v>
+      </c>
+      <c r="M122">
         <v>44440</v>
       </c>
-      <c r="O122" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15">
+      <c r="N122" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14">
       <c r="A123" s="3">
         <v>46233</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C123" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D123" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E123" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F123">
         <v>11</v>
       </c>
       <c r="G123" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H123">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I123" s="1">
-        <v>1.73</v>
+        <v>19.03</v>
       </c>
       <c r="J123">
-        <v>19.03</v>
+        <v>1.76</v>
       </c>
       <c r="K123" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L123" s="1">
         <v>19.36</v>
       </c>
-      <c r="M123" t="s">
-        <v>79</v>
-      </c>
-      <c r="N123">
+      <c r="L123" t="s">
+        <v>78</v>
+      </c>
+      <c r="M123">
         <v>8321</v>
       </c>
-      <c r="O123" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15">
+      <c r="N123" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
       <c r="A124" s="3">
         <v>46233</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C124" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D124" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E124" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F124">
         <v>66.727</v>
       </c>
       <c r="G124" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H124">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I124" s="1">
-        <v>1.73</v>
+        <v>115.438</v>
       </c>
       <c r="J124">
-        <v>115.43771</v>
+        <v>1.76</v>
       </c>
       <c r="K124" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L124" s="1">
-        <v>117.43952</v>
-      </c>
-      <c r="M124" t="s">
-        <v>115</v>
-      </c>
-      <c r="N124">
+        <v>117.44</v>
+      </c>
+      <c r="L124" t="s">
+        <v>114</v>
+      </c>
+      <c r="M124">
         <v>600</v>
       </c>
-      <c r="O124" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15">
+      <c r="N124" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
       <c r="A125" s="3">
         <v>46233</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D125" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E125" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F125">
         <v>8.75</v>
       </c>
       <c r="G125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H125">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I125" s="1">
-        <v>1.73</v>
+        <v>15.138</v>
       </c>
       <c r="J125">
-        <v>15.1375</v>
+        <v>1.76</v>
       </c>
       <c r="K125" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L125" s="1">
         <v>15.4</v>
       </c>
-      <c r="M125" t="s">
-        <v>106</v>
-      </c>
-      <c r="N125">
+      <c r="L125" t="s">
+        <v>105</v>
+      </c>
+      <c r="M125">
         <v>1602</v>
       </c>
-      <c r="O125" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15">
+      <c r="N125" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14">
       <c r="A126" s="3">
         <v>46233</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C126" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E126" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F126">
         <v>8.278</v>
       </c>
       <c r="G126" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H126">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I126" s="1">
-        <v>1.73</v>
+        <v>14.321</v>
       </c>
       <c r="J126">
-        <v>14.32094</v>
+        <v>1.76</v>
       </c>
       <c r="K126" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L126" s="1">
-        <v>14.56928</v>
-      </c>
-      <c r="M126" t="s">
-        <v>157</v>
-      </c>
-      <c r="N126">
+        <v>14.569</v>
+      </c>
+      <c r="L126" t="s">
+        <v>156</v>
+      </c>
+      <c r="M126">
         <v>95625</v>
       </c>
-      <c r="O126" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15">
+      <c r="N126" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
       <c r="A127" s="3">
         <v>46233</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D127" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E127" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F127">
         <v>3.551</v>
       </c>
       <c r="G127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H127">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I127" s="1">
-        <v>1.73</v>
+        <v>6.143</v>
       </c>
       <c r="J127">
-        <v>6.14323</v>
+        <v>1.76</v>
       </c>
       <c r="K127" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L127" s="1">
-        <v>6.24976</v>
-      </c>
-      <c r="M127" t="s">
-        <v>158</v>
-      </c>
-      <c r="N127">
+        <v>6.25</v>
+      </c>
+      <c r="L127" t="s">
+        <v>157</v>
+      </c>
+      <c r="M127">
         <v>188927</v>
       </c>
-      <c r="O127" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15">
+      <c r="N127" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
       <c r="A128" s="3">
         <v>46233</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C128" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D128" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E128" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F128">
         <v>5.602</v>
       </c>
       <c r="G128" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H128">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I128" s="1">
-        <v>1.73</v>
+        <v>9.691000000000001</v>
       </c>
       <c r="J128">
-        <v>9.691459999999999</v>
+        <v>1.76</v>
       </c>
       <c r="K128" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L128" s="1">
-        <v>9.85952</v>
-      </c>
-      <c r="M128" t="s">
-        <v>123</v>
-      </c>
-      <c r="N128">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L128" t="s">
+        <v>122</v>
+      </c>
+      <c r="M128">
         <v>58348</v>
       </c>
-      <c r="O128" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15">
+      <c r="N128" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
       <c r="A129" s="3">
         <v>46233</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D129" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E129" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F129">
         <v>8.5</v>
       </c>
       <c r="G129" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H129">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I129" s="1">
-        <v>1.73</v>
+        <v>14.705</v>
       </c>
       <c r="J129">
-        <v>14.705</v>
+        <v>1.76</v>
       </c>
       <c r="K129" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L129" s="1">
         <v>14.96</v>
       </c>
-      <c r="M129" t="s">
-        <v>159</v>
-      </c>
-      <c r="N129">
+      <c r="L129" t="s">
+        <v>158</v>
+      </c>
+      <c r="M129">
         <v>74961</v>
       </c>
-      <c r="O129" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15">
+      <c r="N129" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130" s="3">
         <v>46233</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C130" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D130" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E130" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F130">
         <v>7.09</v>
       </c>
       <c r="G130" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H130">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I130" s="1">
-        <v>1.52</v>
+        <v>10.777</v>
       </c>
       <c r="J130">
-        <v>10.7768</v>
+        <v>1.55</v>
       </c>
       <c r="K130" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L130" s="1">
-        <v>10.9895</v>
-      </c>
-      <c r="M130" t="s">
-        <v>139</v>
-      </c>
-      <c r="N130">
+        <v>10.99</v>
+      </c>
+      <c r="L130" t="s">
+        <v>138</v>
+      </c>
+      <c r="M130">
         <v>0</v>
       </c>
-      <c r="O130" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15">
+      <c r="N130" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131" s="3">
         <v>46233</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D131" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E131" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F131">
         <v>30.023</v>
       </c>
       <c r="G131" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H131">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I131" s="1">
-        <v>1.73</v>
+        <v>51.94</v>
       </c>
       <c r="J131">
-        <v>51.93979</v>
+        <v>1.76</v>
       </c>
       <c r="K131" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L131" s="1">
-        <v>52.84048</v>
-      </c>
-      <c r="M131" t="s">
-        <v>160</v>
-      </c>
-      <c r="N131">
+        <v>52.84</v>
+      </c>
+      <c r="L131" t="s">
+        <v>159</v>
+      </c>
+      <c r="M131">
         <v>78915</v>
       </c>
-      <c r="O131" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15">
+      <c r="N131" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132" s="3">
         <v>46233</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D132" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E132" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F132">
         <v>20</v>
       </c>
       <c r="G132" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H132">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I132" s="1">
-        <v>1.52</v>
+        <v>30.4</v>
       </c>
       <c r="J132">
-        <v>30.4</v>
+        <v>1.55</v>
       </c>
       <c r="K132" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L132" s="1">
         <v>31</v>
       </c>
-      <c r="M132" t="s">
-        <v>161</v>
-      </c>
-      <c r="N132">
+      <c r="L132" t="s">
+        <v>160</v>
+      </c>
+      <c r="M132">
         <v>181948</v>
       </c>
-      <c r="O132" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15">
+      <c r="N132" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14">
       <c r="A133" s="3">
         <v>46233</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D133" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E133" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F133">
         <v>28.094</v>
       </c>
       <c r="G133" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H133">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I133" s="1">
-        <v>0.63</v>
+        <v>17.699</v>
       </c>
       <c r="J133">
-        <v>17.69922</v>
+        <v>0.64</v>
       </c>
       <c r="K133" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L133" s="1">
-        <v>17.98016</v>
-      </c>
-      <c r="M133" t="s">
-        <v>161</v>
-      </c>
-      <c r="N133">
+        <v>17.98</v>
+      </c>
+      <c r="L133" t="s">
+        <v>160</v>
+      </c>
+      <c r="M133">
         <v>181948</v>
       </c>
-      <c r="O133" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15">
+      <c r="N133" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14">
       <c r="A134" s="3">
         <v>46233</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C134" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D134" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E134" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F134">
         <v>14.869</v>
       </c>
       <c r="G134" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H134">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I134" s="1">
-        <v>1.73</v>
+        <v>25.723</v>
       </c>
       <c r="J134">
-        <v>25.72337</v>
+        <v>1.76</v>
       </c>
       <c r="K134" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L134" s="1">
-        <v>26.16944</v>
-      </c>
-      <c r="M134" t="s">
-        <v>162</v>
-      </c>
-      <c r="N134">
+        <v>26.169</v>
+      </c>
+      <c r="L134" t="s">
+        <v>161</v>
+      </c>
+      <c r="M134">
         <v>68282</v>
       </c>
-      <c r="O134" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15">
+      <c r="N134" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14">
       <c r="A135" s="3">
         <v>46234</v>
       </c>
       <c r="B135" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C135" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D135" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E135" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F135">
         <v>2.599</v>
       </c>
       <c r="G135" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H135">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I135" s="1">
-        <v>1.74</v>
+        <v>4.522</v>
       </c>
       <c r="J135">
-        <v>4.52226</v>
+        <v>1.77</v>
       </c>
       <c r="K135" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L135" s="1">
-        <v>4.60023</v>
-      </c>
-      <c r="M135" t="s">
-        <v>163</v>
-      </c>
-      <c r="N135">
+        <v>4.6</v>
+      </c>
+      <c r="L135" t="s">
+        <v>162</v>
+      </c>
+      <c r="M135">
         <v>44473</v>
       </c>
-      <c r="O135" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15">
+      <c r="N135" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14">
       <c r="A136" s="3">
         <v>46234</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D136" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E136" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F136">
         <v>2</v>
       </c>
       <c r="G136" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H136">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I136" s="1">
-        <v>1.74</v>
+        <v>3.48</v>
       </c>
       <c r="J136">
-        <v>3.48</v>
+        <v>1.77</v>
       </c>
       <c r="K136" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L136" s="1">
         <v>3.54</v>
       </c>
-      <c r="M136" t="s">
-        <v>164</v>
-      </c>
-      <c r="N136">
+      <c r="L136" t="s">
+        <v>163</v>
+      </c>
+      <c r="M136">
         <v>621</v>
       </c>
-      <c r="O136" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15">
+      <c r="N136" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14">
       <c r="A137" s="3">
         <v>46234</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D137" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E137" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F137">
         <v>7.158</v>
       </c>
       <c r="G137" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H137">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I137" s="1">
-        <v>1.74</v>
+        <v>12.455</v>
       </c>
       <c r="J137">
-        <v>12.45492</v>
+        <v>1.77</v>
       </c>
       <c r="K137" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L137" s="1">
-        <v>12.66966</v>
-      </c>
-      <c r="M137" t="s">
-        <v>165</v>
-      </c>
-      <c r="N137">
+        <v>12.67</v>
+      </c>
+      <c r="L137" t="s">
+        <v>164</v>
+      </c>
+      <c r="M137">
         <v>84152</v>
       </c>
-      <c r="O137" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15">
+      <c r="N137" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14">
       <c r="A138" s="3">
         <v>46234</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C138" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D138" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E138" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F138">
         <v>12.921</v>
       </c>
       <c r="G138" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H138">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I138" s="1">
-        <v>1.74</v>
+        <v>22.483</v>
       </c>
       <c r="J138">
-        <v>22.48254</v>
+        <v>1.77</v>
       </c>
       <c r="K138" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L138" s="1">
-        <v>22.87017</v>
-      </c>
-      <c r="M138" t="s">
-        <v>166</v>
-      </c>
-      <c r="N138">
+        <v>22.87</v>
+      </c>
+      <c r="L138" t="s">
+        <v>165</v>
+      </c>
+      <c r="M138">
         <v>103572</v>
       </c>
-      <c r="O138" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15">
+      <c r="N138" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139" s="3">
         <v>46234</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C139" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D139" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E139" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F139">
         <v>2.633</v>
       </c>
       <c r="G139" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H139">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I139" s="1">
-        <v>1.74</v>
+        <v>4.581</v>
       </c>
       <c r="J139">
-        <v>4.58142</v>
+        <v>1.77</v>
       </c>
       <c r="K139" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L139" s="1">
-        <v>4.66041</v>
-      </c>
-      <c r="M139" t="s">
-        <v>118</v>
-      </c>
-      <c r="N139">
+        <v>4.66</v>
+      </c>
+      <c r="L139" t="s">
+        <v>117</v>
+      </c>
+      <c r="M139">
         <v>188205</v>
       </c>
-      <c r="O139" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15">
+      <c r="N139" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14">
       <c r="A140" s="3">
         <v>46234</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C140" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D140" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E140" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F140">
         <v>4.87</v>
       </c>
       <c r="G140" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H140">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I140" s="1">
-        <v>1.74</v>
+        <v>8.474</v>
       </c>
       <c r="J140">
-        <v>8.473800000000001</v>
+        <v>1.77</v>
       </c>
       <c r="K140" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L140" s="1">
-        <v>8.619899999999999</v>
-      </c>
-      <c r="M140" t="s">
-        <v>82</v>
-      </c>
-      <c r="N140">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="L140" t="s">
+        <v>81</v>
+      </c>
+      <c r="M140">
         <v>188960</v>
       </c>
-      <c r="O140" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15">
+      <c r="N140" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141" s="3">
         <v>46234</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C141" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D141" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E141" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F141">
         <v>6.672</v>
       </c>
       <c r="G141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H141">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I141" s="1">
-        <v>1.74</v>
+        <v>11.609</v>
       </c>
       <c r="J141">
-        <v>11.60928</v>
+        <v>1.77</v>
       </c>
       <c r="K141" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L141" s="1">
-        <v>11.80944</v>
-      </c>
-      <c r="M141" t="s">
-        <v>73</v>
-      </c>
-      <c r="N141">
+        <v>11.809</v>
+      </c>
+      <c r="L141" t="s">
+        <v>72</v>
+      </c>
+      <c r="M141">
         <v>1000619</v>
       </c>
-      <c r="O141" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15">
+      <c r="N141" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14">
       <c r="A142" s="3">
         <v>46234</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C142" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D142" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E142" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F142">
         <v>32</v>
       </c>
       <c r="G142" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H142">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I142" s="1">
-        <v>1.74</v>
+        <v>55.68</v>
       </c>
       <c r="J142">
-        <v>55.68</v>
+        <v>1.77</v>
       </c>
       <c r="K142" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L142" s="1">
         <v>56.64</v>
       </c>
-      <c r="M142" t="s">
-        <v>131</v>
-      </c>
-      <c r="N142">
+      <c r="L142" t="s">
+        <v>130</v>
+      </c>
+      <c r="M142">
         <v>79000</v>
       </c>
-      <c r="O142" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15">
+      <c r="N142" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14">
       <c r="A143" s="3">
         <v>46234</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D143" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E143" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F143">
         <v>7.102</v>
       </c>
       <c r="G143" t="s">
+        <v>70</v>
+      </c>
+      <c r="H143">
+        <v>1.74</v>
+      </c>
+      <c r="I143" s="1">
+        <v>12.357</v>
+      </c>
+      <c r="J143">
+        <v>1.77</v>
+      </c>
+      <c r="K143" s="1">
+        <v>12.571</v>
+      </c>
+      <c r="L143" t="s">
         <v>71</v>
       </c>
-      <c r="H143">
-        <v>1.689</v>
-      </c>
-      <c r="I143" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="J143">
-        <v>12.35748</v>
-      </c>
-      <c r="K143" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L143" s="1">
-        <v>12.57054</v>
-      </c>
-      <c r="M143" t="s">
-        <v>72</v>
-      </c>
-      <c r="N143">
+      <c r="M143">
         <v>58408</v>
       </c>
-      <c r="O143" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15">
+      <c r="N143" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14">
       <c r="A144" s="3">
         <v>46234</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C144" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D144" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E144" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F144">
         <v>10</v>
       </c>
       <c r="G144" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H144">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I144" s="1">
-        <v>1.74</v>
+        <v>17.4</v>
       </c>
       <c r="J144">
-        <v>17.4</v>
+        <v>1.77</v>
       </c>
       <c r="K144" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L144" s="1">
         <v>17.7</v>
       </c>
-      <c r="M144" t="s">
-        <v>108</v>
-      </c>
-      <c r="N144">
+      <c r="L144" t="s">
+        <v>107</v>
+      </c>
+      <c r="M144">
         <v>8335</v>
       </c>
-      <c r="O144" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15">
+      <c r="N144" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14">
       <c r="A145" s="3">
         <v>46234</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C145" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D145" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E145" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F145">
         <v>4.26</v>
       </c>
       <c r="G145" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H145">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I145" s="1">
-        <v>1.74</v>
+        <v>7.412</v>
       </c>
       <c r="J145">
-        <v>7.4124</v>
+        <v>1.77</v>
       </c>
       <c r="K145" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L145" s="1">
-        <v>7.5402</v>
-      </c>
-      <c r="M145" t="s">
-        <v>167</v>
-      </c>
-      <c r="N145">
+        <v>7.54</v>
+      </c>
+      <c r="L145" t="s">
+        <v>166</v>
+      </c>
+      <c r="M145">
         <v>95655</v>
       </c>
-      <c r="O145" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15">
+      <c r="N145" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14">
       <c r="A146" s="3">
         <v>46234</v>
       </c>
       <c r="B146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C146" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D146" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E146" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F146">
         <v>4.503</v>
       </c>
       <c r="G146" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H146">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I146" s="1">
-        <v>1.74</v>
+        <v>7.835</v>
       </c>
       <c r="J146">
-        <v>7.83522</v>
+        <v>1.77</v>
       </c>
       <c r="K146" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L146" s="1">
-        <v>7.97031</v>
-      </c>
-      <c r="M146" t="s">
-        <v>91</v>
-      </c>
-      <c r="N146">
+        <v>7.97</v>
+      </c>
+      <c r="L146" t="s">
+        <v>90</v>
+      </c>
+      <c r="M146">
         <v>74898</v>
       </c>
-      <c r="O146" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15">
+      <c r="N146" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14">
       <c r="A147" s="3">
         <v>46234</v>
       </c>
       <c r="B147" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C147" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E147" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F147">
         <v>9</v>
       </c>
       <c r="G147" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H147">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I147" s="1">
-        <v>1.74</v>
+        <v>15.66</v>
       </c>
       <c r="J147">
-        <v>15.66</v>
+        <v>1.77</v>
       </c>
       <c r="K147" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L147" s="1">
         <v>15.93</v>
       </c>
-      <c r="M147" t="s">
-        <v>168</v>
-      </c>
-      <c r="N147">
+      <c r="L147" t="s">
+        <v>167</v>
+      </c>
+      <c r="M147">
         <v>68337</v>
       </c>
-      <c r="O147" t="s">
+      <c r="N147" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14">
+      <c r="A150" s="4" t="s">
         <v>313</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15">
-      <c r="A150" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -8313,89 +7869,89 @@
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
     </row>
-    <row r="151" spans="1:15">
+    <row r="151" spans="1:14">
       <c r="A151" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="C151" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="C151" s="5" t="s">
+      <c r="D151" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D151" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="E151" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14">
       <c r="A152" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B152" s="7">
         <v>1603.052</v>
       </c>
-      <c r="C152" s="7">
+      <c r="C152" s="8">
         <v>140</v>
       </c>
       <c r="D152" s="8">
-        <v>1.681172</v>
-      </c>
-      <c r="E152" s="7">
-        <v>2695.01</v>
-      </c>
-      <c r="F152" s="7">
-        <v>2743.1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15">
+        <v>1.681</v>
+      </c>
+      <c r="E152" s="8">
+        <v>2695.011</v>
+      </c>
+      <c r="F152" s="8">
+        <v>2743.093</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14">
       <c r="A153" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B153" s="7">
         <v>227.109</v>
       </c>
-      <c r="C153" s="7">
+      <c r="C153" s="8">
         <v>3</v>
       </c>
       <c r="D153" s="8">
-        <v>1.511193</v>
-      </c>
-      <c r="E153" s="7">
-        <v>343.21</v>
-      </c>
-      <c r="F153" s="7">
-        <v>350.02</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15">
+        <v>1.511</v>
+      </c>
+      <c r="E153" s="8">
+        <v>343.206</v>
+      </c>
+      <c r="F153" s="8">
+        <v>350.019</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14">
       <c r="A154" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B154" s="7">
         <v>83.562</v>
       </c>
-      <c r="C154" s="7">
+      <c r="C154" s="8">
         <v>3</v>
       </c>
       <c r="D154" s="8">
         <v>0.63</v>
       </c>
-      <c r="E154" s="7">
-        <v>52.64</v>
-      </c>
-      <c r="F154" s="7">
+      <c r="E154" s="8">
+        <v>52.644</v>
+      </c>
+      <c r="F154" s="8">
         <v>53.48</v>
       </c>
     </row>
-    <row r="155" spans="1:15">
+    <row r="155" spans="1:14">
       <c r="A155" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B155" s="10">
         <v>1913.723</v>
@@ -8405,10 +7961,10 @@
       </c>
       <c r="D155" s="8"/>
       <c r="E155" s="10">
-        <v>3090.86</v>
+        <v>3090.861</v>
       </c>
       <c r="F155" s="10">
-        <v>3146.6</v>
+        <v>3146.592</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ/ОП УПРАВЛЕНИЕ НА ПРОЕКТИ И ОЗЕЛЕНЯВАНЕ.xlsx
@@ -1371,10 +1371,10 @@
         <v>68</v>
       </c>
       <c r="H2" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I2" s="1">
-        <v>10.108</v>
+        <v>10.797</v>
       </c>
       <c r="J2" s="1">
         <v>1.8</v>
@@ -1415,10 +1415,10 @@
         <v>68</v>
       </c>
       <c r="H3" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I3" s="1">
-        <v>8.086</v>
+        <v>8.638</v>
       </c>
       <c r="J3" s="1">
         <v>1.8</v>
@@ -1459,10 +1459,10 @@
         <v>68</v>
       </c>
       <c r="H4" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I4" s="1">
-        <v>7.987</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="J4" s="1">
         <v>1.8</v>
@@ -1503,10 +1503,10 @@
         <v>68</v>
       </c>
       <c r="H5" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I5" s="1">
-        <v>5.899</v>
+        <v>6.301</v>
       </c>
       <c r="J5" s="1">
         <v>1.8</v>
@@ -1547,10 +1547,10 @@
         <v>68</v>
       </c>
       <c r="H6" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I6" s="1">
-        <v>9.577</v>
+        <v>10.231</v>
       </c>
       <c r="J6" s="1">
         <v>1.8</v>
@@ -1591,10 +1591,10 @@
         <v>68</v>
       </c>
       <c r="H7" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I7" s="1">
-        <v>19.884</v>
+        <v>21.24</v>
       </c>
       <c r="J7" s="1">
         <v>1.8</v>
@@ -1635,10 +1635,10 @@
         <v>68</v>
       </c>
       <c r="H8" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I8" s="1">
-        <v>4.258</v>
+        <v>4.549</v>
       </c>
       <c r="J8" s="1">
         <v>1.8</v>
@@ -1679,10 +1679,10 @@
         <v>68</v>
       </c>
       <c r="H9" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I9" s="1">
-        <v>7.142</v>
+        <v>7.629</v>
       </c>
       <c r="J9" s="1">
         <v>1.8</v>
@@ -1723,10 +1723,10 @@
         <v>68</v>
       </c>
       <c r="H10" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I10" s="1">
-        <v>33.14</v>
+        <v>35.4</v>
       </c>
       <c r="J10" s="1">
         <v>1.8</v>
@@ -1767,10 +1767,10 @@
         <v>68</v>
       </c>
       <c r="H11" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I11" s="1">
-        <v>6.628</v>
+        <v>7.08</v>
       </c>
       <c r="J11" s="1">
         <v>1.8</v>
@@ -1811,10 +1811,10 @@
         <v>68</v>
       </c>
       <c r="H12" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I12" s="1">
-        <v>22.32</v>
+        <v>23.842</v>
       </c>
       <c r="J12" s="1">
         <v>1.8</v>
@@ -1855,10 +1855,10 @@
         <v>68</v>
       </c>
       <c r="H13" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I13" s="1">
-        <v>26.727</v>
+        <v>28.55</v>
       </c>
       <c r="J13" s="1">
         <v>1.8</v>
@@ -1899,10 +1899,10 @@
         <v>68</v>
       </c>
       <c r="H14" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I14" s="1">
-        <v>4.26</v>
+        <v>4.496</v>
       </c>
       <c r="J14" s="1">
         <v>1.8</v>
@@ -1943,10 +1943,10 @@
         <v>68</v>
       </c>
       <c r="H15" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I15" s="1">
-        <v>16.77</v>
+        <v>17.7</v>
       </c>
       <c r="J15" s="1">
         <v>1.8</v>
@@ -1987,10 +1987,10 @@
         <v>68</v>
       </c>
       <c r="H16" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I16" s="1">
-        <v>11.739</v>
+        <v>12.39</v>
       </c>
       <c r="J16" s="1">
         <v>1.8</v>
@@ -2031,10 +2031,10 @@
         <v>68</v>
       </c>
       <c r="H17" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I17" s="1">
-        <v>46.319</v>
+        <v>48.887</v>
       </c>
       <c r="J17" s="1">
         <v>1.8</v>
@@ -2075,10 +2075,10 @@
         <v>68</v>
       </c>
       <c r="H18" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I18" s="1">
-        <v>19.94</v>
+        <v>21.045</v>
       </c>
       <c r="J18" s="1">
         <v>1.8</v>
@@ -2119,10 +2119,10 @@
         <v>68</v>
       </c>
       <c r="H19" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I19" s="1">
-        <v>19.638</v>
+        <v>20.727</v>
       </c>
       <c r="J19" s="1">
         <v>1.8</v>
@@ -2163,10 +2163,10 @@
         <v>68</v>
       </c>
       <c r="H20" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I20" s="1">
-        <v>11.991</v>
+        <v>12.656</v>
       </c>
       <c r="J20" s="1">
         <v>1.8</v>
@@ -2207,10 +2207,10 @@
         <v>68</v>
       </c>
       <c r="H21" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I21" s="1">
-        <v>3.773</v>
+        <v>3.982</v>
       </c>
       <c r="J21" s="1">
         <v>1.8</v>
@@ -2251,10 +2251,10 @@
         <v>68</v>
       </c>
       <c r="H22" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I22" s="1">
-        <v>16.518</v>
+        <v>17.434</v>
       </c>
       <c r="J22" s="1">
         <v>1.8</v>
@@ -2295,10 +2295,10 @@
         <v>68</v>
       </c>
       <c r="H23" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I23" s="1">
-        <v>5.35</v>
+        <v>5.646</v>
       </c>
       <c r="J23" s="1">
         <v>1.8</v>
@@ -2339,10 +2339,10 @@
         <v>68</v>
       </c>
       <c r="H24" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I24" s="1">
-        <v>18.481</v>
+        <v>19.505</v>
       </c>
       <c r="J24" s="1">
         <v>1.8</v>
@@ -2383,10 +2383,10 @@
         <v>68</v>
       </c>
       <c r="H25" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I25" s="1">
-        <v>5.065</v>
+        <v>5.345</v>
       </c>
       <c r="J25" s="1">
         <v>1.8</v>
@@ -2427,10 +2427,10 @@
         <v>68</v>
       </c>
       <c r="H26" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I26" s="1">
-        <v>30.462</v>
+        <v>20</v>
       </c>
       <c r="J26" s="1">
         <v>0.66</v>
@@ -2471,10 +2471,10 @@
         <v>68</v>
       </c>
       <c r="H27" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I27" s="1">
-        <v>5.651</v>
+        <v>6.032</v>
       </c>
       <c r="J27" s="1">
         <v>1.82</v>
@@ -2515,10 +2515,10 @@
         <v>68</v>
       </c>
       <c r="H28" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I28" s="1">
-        <v>5.031</v>
+        <v>5.37</v>
       </c>
       <c r="J28" s="1">
         <v>1.82</v>
@@ -2559,10 +2559,10 @@
         <v>68</v>
       </c>
       <c r="H29" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I29" s="1">
-        <v>16.77</v>
+        <v>17.9</v>
       </c>
       <c r="J29" s="1">
         <v>1.82</v>
@@ -2603,10 +2603,10 @@
         <v>68</v>
       </c>
       <c r="H30" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I30" s="1">
-        <v>6.339</v>
+        <v>6.766</v>
       </c>
       <c r="J30" s="1">
         <v>1.82</v>
@@ -2647,10 +2647,10 @@
         <v>68</v>
       </c>
       <c r="H31" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I31" s="1">
-        <v>9.19</v>
+        <v>9.808999999999999</v>
       </c>
       <c r="J31" s="1">
         <v>1.82</v>
@@ -2691,10 +2691,10 @@
         <v>68</v>
       </c>
       <c r="H32" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I32" s="1">
-        <v>8.955</v>
+        <v>9.558999999999999</v>
       </c>
       <c r="J32" s="1">
         <v>1.82</v>
@@ -2735,10 +2735,10 @@
         <v>68</v>
       </c>
       <c r="H33" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I33" s="1">
-        <v>4.125</v>
+        <v>4.403</v>
       </c>
       <c r="J33" s="1">
         <v>1.82</v>
@@ -2779,10 +2779,10 @@
         <v>68</v>
       </c>
       <c r="H34" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I34" s="1">
-        <v>40.533</v>
+        <v>43.264</v>
       </c>
       <c r="J34" s="1">
         <v>1.82</v>
@@ -2823,10 +2823,10 @@
         <v>68</v>
       </c>
       <c r="H35" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I35" s="1">
-        <v>5.87</v>
+        <v>6.265</v>
       </c>
       <c r="J35" s="1">
         <v>1.82</v>
@@ -2867,10 +2867,10 @@
         <v>68</v>
       </c>
       <c r="H36" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I36" s="1">
-        <v>6.037</v>
+        <v>6.444</v>
       </c>
       <c r="J36" s="1">
         <v>1.82</v>
@@ -2911,10 +2911,10 @@
         <v>68</v>
       </c>
       <c r="H37" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I37" s="1">
-        <v>36.894</v>
+        <v>39.38</v>
       </c>
       <c r="J37" s="1">
         <v>1.82</v>
@@ -2955,10 +2955,10 @@
         <v>68</v>
       </c>
       <c r="H38" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I38" s="1">
-        <v>285.814</v>
+        <v>306.015</v>
       </c>
       <c r="J38" s="1">
         <v>1.56</v>
@@ -2999,10 +2999,10 @@
         <v>68</v>
       </c>
       <c r="H39" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I39" s="1">
-        <v>167.7</v>
+        <v>177</v>
       </c>
       <c r="J39" s="1">
         <v>1.8</v>
@@ -3043,10 +3043,10 @@
         <v>68</v>
       </c>
       <c r="H40" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I40" s="1">
-        <v>167.817</v>
+        <v>177.124</v>
       </c>
       <c r="J40" s="1">
         <v>1.8</v>
@@ -3087,10 +3087,10 @@
         <v>68</v>
       </c>
       <c r="H41" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I41" s="1">
-        <v>8.401999999999999</v>
+        <v>8.968</v>
       </c>
       <c r="J41" s="1">
         <v>1.82</v>
@@ -3131,10 +3131,10 @@
         <v>68</v>
       </c>
       <c r="H42" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I42" s="1">
-        <v>4.594</v>
+        <v>4.923</v>
       </c>
       <c r="J42" s="1">
         <v>1.84</v>
@@ -3175,10 +3175,10 @@
         <v>68</v>
       </c>
       <c r="H43" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I43" s="1">
-        <v>3.699</v>
+        <v>3.964</v>
       </c>
       <c r="J43" s="1">
         <v>1.84</v>
@@ -3219,10 +3219,10 @@
         <v>68</v>
       </c>
       <c r="H44" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I44" s="1">
-        <v>21.974</v>
+        <v>23.548</v>
       </c>
       <c r="J44" s="1">
         <v>1.84</v>
@@ -3263,10 +3263,10 @@
         <v>68</v>
       </c>
       <c r="H45" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I45" s="1">
-        <v>18.579</v>
+        <v>19.91</v>
       </c>
       <c r="J45" s="1">
         <v>1.84</v>
@@ -3307,10 +3307,10 @@
         <v>68</v>
       </c>
       <c r="H46" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I46" s="1">
-        <v>10.489</v>
+        <v>11.24</v>
       </c>
       <c r="J46" s="1">
         <v>1.84</v>
@@ -3351,10 +3351,10 @@
         <v>68</v>
       </c>
       <c r="H47" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I47" s="1">
-        <v>7.55</v>
+        <v>8.090999999999999</v>
       </c>
       <c r="J47" s="1">
         <v>1.84</v>
@@ -3395,10 +3395,10 @@
         <v>68</v>
       </c>
       <c r="H48" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I48" s="1">
-        <v>8.614000000000001</v>
+        <v>9.231</v>
       </c>
       <c r="J48" s="1">
         <v>1.84</v>
@@ -3439,10 +3439,10 @@
         <v>68</v>
       </c>
       <c r="H49" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I49" s="1">
-        <v>9.239000000000001</v>
+        <v>9.901</v>
       </c>
       <c r="J49" s="1">
         <v>1.84</v>
@@ -3483,10 +3483,10 @@
         <v>68</v>
       </c>
       <c r="H50" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I50" s="1">
-        <v>5.54</v>
+        <v>5.937</v>
       </c>
       <c r="J50" s="1">
         <v>1.84</v>
@@ -3527,10 +3527,10 @@
         <v>68</v>
       </c>
       <c r="H51" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I51" s="1">
-        <v>73.134</v>
+        <v>78.373</v>
       </c>
       <c r="J51" s="1">
         <v>1.84</v>
@@ -3571,10 +3571,10 @@
         <v>68</v>
       </c>
       <c r="H52" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I52" s="1">
-        <v>39.489</v>
+        <v>42.318</v>
       </c>
       <c r="J52" s="1">
         <v>1.84</v>
@@ -3615,10 +3615,10 @@
         <v>68</v>
       </c>
       <c r="H53" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I53" s="1">
-        <v>70.854</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J53" s="1">
         <v>1.84</v>
@@ -3659,10 +3659,10 @@
         <v>68</v>
       </c>
       <c r="H54" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I54" s="1">
-        <v>6.587</v>
+        <v>7.059</v>
       </c>
       <c r="J54" s="1">
         <v>1.84</v>
@@ -3703,10 +3703,10 @@
         <v>68</v>
       </c>
       <c r="H55" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I55" s="1">
-        <v>5.912</v>
+        <v>6.335</v>
       </c>
       <c r="J55" s="1">
         <v>1.84</v>
@@ -3747,10 +3747,10 @@
         <v>68</v>
       </c>
       <c r="H56" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I56" s="1">
-        <v>14.509</v>
+        <v>15.548</v>
       </c>
       <c r="J56" s="1">
         <v>1.84</v>
@@ -3791,10 +3791,10 @@
         <v>68</v>
       </c>
       <c r="H57" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I57" s="1">
-        <v>8.445</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J57" s="1">
         <v>1.84</v>
@@ -3835,10 +3835,10 @@
         <v>68</v>
       </c>
       <c r="H58" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I58" s="1">
-        <v>4.155</v>
+        <v>4.453</v>
       </c>
       <c r="J58" s="1">
         <v>1.84</v>
@@ -3879,10 +3879,10 @@
         <v>68</v>
       </c>
       <c r="H59" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I59" s="1">
-        <v>43.914</v>
+        <v>47.06</v>
       </c>
       <c r="J59" s="1">
         <v>1.84</v>
@@ -3923,10 +3923,10 @@
         <v>68</v>
       </c>
       <c r="H60" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I60" s="1">
-        <v>3.631</v>
+        <v>3.891</v>
       </c>
       <c r="J60" s="1">
         <v>1.84</v>
@@ -3967,10 +3967,10 @@
         <v>68</v>
       </c>
       <c r="H61" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I61" s="1">
-        <v>4.307</v>
+        <v>4.616</v>
       </c>
       <c r="J61" s="1">
         <v>1.84</v>
@@ -4011,10 +4011,10 @@
         <v>68</v>
       </c>
       <c r="H62" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I62" s="1">
-        <v>13.512</v>
+        <v>14.48</v>
       </c>
       <c r="J62" s="1">
         <v>1.84</v>
@@ -4055,10 +4055,10 @@
         <v>68</v>
       </c>
       <c r="H63" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I63" s="1">
-        <v>11.536</v>
+        <v>12.362</v>
       </c>
       <c r="J63" s="1">
         <v>1.84</v>
@@ -4099,10 +4099,10 @@
         <v>68</v>
       </c>
       <c r="H64" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I64" s="1">
-        <v>5.202</v>
+        <v>5.575</v>
       </c>
       <c r="J64" s="1">
         <v>1.84</v>
@@ -4143,10 +4143,10 @@
         <v>68</v>
       </c>
       <c r="H65" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I65" s="1">
-        <v>20.268</v>
+        <v>21.72</v>
       </c>
       <c r="J65" s="1">
         <v>1.84</v>
@@ -4187,10 +4187,10 @@
         <v>68</v>
       </c>
       <c r="H66" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I66" s="1">
-        <v>12.058</v>
+        <v>12.849</v>
       </c>
       <c r="J66" s="1">
         <v>1.85</v>
@@ -4231,10 +4231,10 @@
         <v>68</v>
       </c>
       <c r="H67" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I67" s="1">
-        <v>7.737</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="J67" s="1">
         <v>1.85</v>
@@ -4275,10 +4275,10 @@
         <v>68</v>
       </c>
       <c r="H68" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I68" s="1">
-        <v>9.24</v>
+        <v>9.846</v>
       </c>
       <c r="J68" s="1">
         <v>1.85</v>
@@ -4319,10 +4319,10 @@
         <v>68</v>
       </c>
       <c r="H69" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I69" s="1">
-        <v>7.379</v>
+        <v>7.862</v>
       </c>
       <c r="J69" s="1">
         <v>1.85</v>
@@ -4363,10 +4363,10 @@
         <v>68</v>
       </c>
       <c r="H70" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I70" s="1">
-        <v>51.24</v>
+        <v>54.6</v>
       </c>
       <c r="J70" s="1">
         <v>1.85</v>
@@ -4407,10 +4407,10 @@
         <v>68</v>
       </c>
       <c r="H71" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I71" s="1">
-        <v>17.319</v>
+        <v>18.455</v>
       </c>
       <c r="J71" s="1">
         <v>1.85</v>
@@ -4451,10 +4451,10 @@
         <v>68</v>
       </c>
       <c r="H72" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I72" s="1">
-        <v>11.444</v>
+        <v>12.194</v>
       </c>
       <c r="J72" s="1">
         <v>1.85</v>
@@ -4495,10 +4495,10 @@
         <v>68</v>
       </c>
       <c r="H73" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I73" s="1">
-        <v>6.234</v>
+        <v>6.643</v>
       </c>
       <c r="J73" s="1">
         <v>1.85</v>
@@ -4539,10 +4539,10 @@
         <v>68</v>
       </c>
       <c r="H74" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I74" s="1">
-        <v>7.357</v>
+        <v>7.79</v>
       </c>
       <c r="J74" s="1">
         <v>1.85</v>
@@ -4583,10 +4583,10 @@
         <v>68</v>
       </c>
       <c r="H75" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I75" s="1">
-        <v>4.865</v>
+        <v>5.151</v>
       </c>
       <c r="J75" s="1">
         <v>1.85</v>
@@ -4627,10 +4627,10 @@
         <v>68</v>
       </c>
       <c r="H76" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I76" s="1">
-        <v>9.454000000000001</v>
+        <v>10.044</v>
       </c>
       <c r="J76" s="1">
         <v>1.58</v>
@@ -4671,10 +4671,10 @@
         <v>68</v>
       </c>
       <c r="H77" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I77" s="1">
-        <v>17.345</v>
+        <v>18.364</v>
       </c>
       <c r="J77" s="1">
         <v>1.85</v>
@@ -4715,10 +4715,10 @@
         <v>68</v>
       </c>
       <c r="H78" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I78" s="1">
-        <v>5.879</v>
+        <v>6.224</v>
       </c>
       <c r="J78" s="1">
         <v>1.85</v>
@@ -4759,10 +4759,10 @@
         <v>68</v>
       </c>
       <c r="H79" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I79" s="1">
-        <v>37.818</v>
+        <v>40.04</v>
       </c>
       <c r="J79" s="1">
         <v>1.85</v>
@@ -4803,10 +4803,10 @@
         <v>68</v>
       </c>
       <c r="H80" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I80" s="1">
-        <v>11.414</v>
+        <v>12.085</v>
       </c>
       <c r="J80" s="1">
         <v>1.85</v>
@@ -4847,10 +4847,10 @@
         <v>68</v>
       </c>
       <c r="H81" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I81" s="1">
-        <v>17.379</v>
+        <v>18.4</v>
       </c>
       <c r="J81" s="1">
         <v>1.85</v>
@@ -4891,10 +4891,10 @@
         <v>68</v>
       </c>
       <c r="H82" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I82" s="1">
-        <v>12.291</v>
+        <v>13.013</v>
       </c>
       <c r="J82" s="1">
         <v>1.85</v>
@@ -4935,10 +4935,10 @@
         <v>68</v>
       </c>
       <c r="H83" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I83" s="1">
-        <v>17.964</v>
+        <v>19.019</v>
       </c>
       <c r="J83" s="1">
         <v>1.85</v>
@@ -4979,10 +4979,10 @@
         <v>68</v>
       </c>
       <c r="H84" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I84" s="1">
-        <v>15.746</v>
+        <v>16.671</v>
       </c>
       <c r="J84" s="1">
         <v>1.85</v>
@@ -5023,10 +5023,10 @@
         <v>68</v>
       </c>
       <c r="H85" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I85" s="1">
-        <v>6.515</v>
+        <v>6.898</v>
       </c>
       <c r="J85" s="1">
         <v>1.85</v>
@@ -5067,10 +5067,10 @@
         <v>68</v>
       </c>
       <c r="H86" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I86" s="1">
-        <v>6.102</v>
+        <v>6.461</v>
       </c>
       <c r="J86" s="1">
         <v>1.85</v>
@@ -5111,10 +5111,10 @@
         <v>68</v>
       </c>
       <c r="H87" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I87" s="1">
-        <v>67.746</v>
+        <v>71.726</v>
       </c>
       <c r="J87" s="1">
         <v>1.85</v>
@@ -5155,10 +5155,10 @@
         <v>68</v>
       </c>
       <c r="H88" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I88" s="1">
-        <v>110.016</v>
+        <v>116.48</v>
       </c>
       <c r="J88" s="1">
         <v>1.85</v>
@@ -5199,10 +5199,10 @@
         <v>68</v>
       </c>
       <c r="H89" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I89" s="1">
-        <v>4.899</v>
+        <v>5.187</v>
       </c>
       <c r="J89" s="1">
         <v>1.85</v>
@@ -5243,10 +5243,10 @@
         <v>68</v>
       </c>
       <c r="H90" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I90" s="1">
-        <v>14.955</v>
+        <v>15.834</v>
       </c>
       <c r="J90" s="1">
         <v>1.85</v>
@@ -5287,10 +5287,10 @@
         <v>68</v>
       </c>
       <c r="H91" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I91" s="1">
-        <v>12.153</v>
+        <v>12.867</v>
       </c>
       <c r="J91" s="1">
         <v>1.85</v>
@@ -5331,10 +5331,10 @@
         <v>68</v>
       </c>
       <c r="H92" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I92" s="1">
-        <v>17.19</v>
+        <v>18.2</v>
       </c>
       <c r="J92" s="1">
         <v>1.85</v>
@@ -5375,10 +5375,10 @@
         <v>68</v>
       </c>
       <c r="H93" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I93" s="1">
-        <v>27.504</v>
+        <v>29.12</v>
       </c>
       <c r="J93" s="1">
         <v>1.85</v>
@@ -5419,10 +5419,10 @@
         <v>68</v>
       </c>
       <c r="H94" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I94" s="1">
-        <v>7.392</v>
+        <v>7.826</v>
       </c>
       <c r="J94" s="1">
         <v>1.85</v>
@@ -5463,10 +5463,10 @@
         <v>68</v>
       </c>
       <c r="H95" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I95" s="1">
-        <v>8.595000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J95" s="1">
         <v>1.85</v>
@@ -5507,10 +5507,10 @@
         <v>68</v>
       </c>
       <c r="H96" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I96" s="1">
-        <v>56.727</v>
+        <v>60.06</v>
       </c>
       <c r="J96" s="1">
         <v>1.85</v>
@@ -5551,10 +5551,10 @@
         <v>68</v>
       </c>
       <c r="H97" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I97" s="1">
-        <v>10.314</v>
+        <v>10.92</v>
       </c>
       <c r="J97" s="1">
         <v>1.85</v>
@@ -5595,10 +5595,10 @@
         <v>68</v>
       </c>
       <c r="H98" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I98" s="1">
-        <v>29.779</v>
+        <v>19.552</v>
       </c>
       <c r="J98" s="1">
         <v>0.66</v>
@@ -5639,10 +5639,10 @@
         <v>68</v>
       </c>
       <c r="H99" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I99" s="1">
-        <v>4.383</v>
+        <v>4.641</v>
       </c>
       <c r="J99" s="1">
         <v>1.85</v>
@@ -5683,10 +5683,10 @@
         <v>68</v>
       </c>
       <c r="H100" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I100" s="1">
-        <v>11.483</v>
+        <v>12.158</v>
       </c>
       <c r="J100" s="1">
         <v>1.85</v>
@@ -5727,10 +5727,10 @@
         <v>68</v>
       </c>
       <c r="H101" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I101" s="1">
-        <v>5.157</v>
+        <v>5.46</v>
       </c>
       <c r="J101" s="1">
         <v>1.85</v>
@@ -5771,10 +5771,10 @@
         <v>68</v>
       </c>
       <c r="H102" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I102" s="1">
-        <v>11.827</v>
+        <v>12.522</v>
       </c>
       <c r="J102" s="1">
         <v>1.85</v>
@@ -5815,10 +5815,10 @@
         <v>68</v>
       </c>
       <c r="H103" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I103" s="1">
-        <v>15.78</v>
+        <v>16.708</v>
       </c>
       <c r="J103" s="1">
         <v>1.85</v>
@@ -5859,10 +5859,10 @@
         <v>68</v>
       </c>
       <c r="H104" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I104" s="1">
-        <v>20.628</v>
+        <v>21.84</v>
       </c>
       <c r="J104" s="1">
         <v>1.85</v>
@@ -5903,10 +5903,10 @@
         <v>68</v>
       </c>
       <c r="H105" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I105" s="1">
-        <v>42.511</v>
+        <v>45.009</v>
       </c>
       <c r="J105" s="1">
         <v>1.85</v>
@@ -5947,10 +5947,10 @@
         <v>68</v>
       </c>
       <c r="H106" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I106" s="1">
-        <v>17.362</v>
+        <v>18.382</v>
       </c>
       <c r="J106" s="1">
         <v>1.85</v>
@@ -5991,10 +5991,10 @@
         <v>68</v>
       </c>
       <c r="H107" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I107" s="1">
-        <v>17.19</v>
+        <v>18.2</v>
       </c>
       <c r="J107" s="1">
         <v>1.85</v>
@@ -6035,10 +6035,10 @@
         <v>68</v>
       </c>
       <c r="H108" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I108" s="1">
-        <v>11.019</v>
+        <v>11.602</v>
       </c>
       <c r="J108" s="1">
         <v>1.84</v>
@@ -6079,10 +6079,10 @@
         <v>68</v>
       </c>
       <c r="H109" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I109" s="1">
-        <v>4.83</v>
+        <v>5.086</v>
       </c>
       <c r="J109" s="1">
         <v>1.84</v>
@@ -6123,10 +6123,10 @@
         <v>68</v>
       </c>
       <c r="H110" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I110" s="1">
-        <v>8.32</v>
+        <v>8.76</v>
       </c>
       <c r="J110" s="1">
         <v>1.84</v>
@@ -6167,10 +6167,10 @@
         <v>68</v>
       </c>
       <c r="H111" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I111" s="1">
-        <v>4.762</v>
+        <v>5.014</v>
       </c>
       <c r="J111" s="1">
         <v>1.84</v>
@@ -6211,10 +6211,10 @@
         <v>68</v>
       </c>
       <c r="H112" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I112" s="1">
-        <v>7.736</v>
+        <v>8.145</v>
       </c>
       <c r="J112" s="1">
         <v>1.84</v>
@@ -6255,10 +6255,10 @@
         <v>68</v>
       </c>
       <c r="H113" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I113" s="1">
-        <v>11.758</v>
+        <v>12.38</v>
       </c>
       <c r="J113" s="1">
         <v>1.84</v>
@@ -6299,10 +6299,10 @@
         <v>68</v>
       </c>
       <c r="H114" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I114" s="1">
-        <v>10.198</v>
+        <v>11.044</v>
       </c>
       <c r="J114" s="1">
         <v>1.61</v>
@@ -6343,10 +6343,10 @@
         <v>68</v>
       </c>
       <c r="H115" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I115" s="1">
-        <v>17.19</v>
+        <v>18.1</v>
       </c>
       <c r="J115" s="1">
         <v>1.84</v>
@@ -6387,10 +6387,10 @@
         <v>68</v>
       </c>
       <c r="H116" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I116" s="1">
-        <v>9.196999999999999</v>
+        <v>9.683999999999999</v>
       </c>
       <c r="J116" s="1">
         <v>1.84</v>
@@ -6431,10 +6431,10 @@
         <v>68</v>
       </c>
       <c r="H117" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I117" s="1">
-        <v>30.942</v>
+        <v>32.58</v>
       </c>
       <c r="J117" s="1">
         <v>1.84</v>
@@ -6475,10 +6475,10 @@
         <v>68</v>
       </c>
       <c r="H118" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I118" s="1">
-        <v>21.728</v>
+        <v>22.878</v>
       </c>
       <c r="J118" s="1">
         <v>1.84</v>
@@ -6519,10 +6519,10 @@
         <v>68</v>
       </c>
       <c r="H119" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I119" s="1">
-        <v>28.57</v>
+        <v>30.082</v>
       </c>
       <c r="J119" s="1">
         <v>1.84</v>
@@ -6563,10 +6563,10 @@
         <v>68</v>
       </c>
       <c r="H120" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I120" s="1">
-        <v>70.41</v>
+        <v>74.13800000000001</v>
       </c>
       <c r="J120" s="1">
         <v>1.84</v>
@@ -6625,10 +6625,10 @@
         <v>114</v>
       </c>
       <c r="D125" s="9">
-        <v>1.69555</v>
+        <v>1.79973</v>
       </c>
       <c r="E125" s="7">
-        <v>2240.25</v>
+        <v>2377.9</v>
       </c>
       <c r="F125" s="7">
         <v>2417.54</v>
@@ -6645,10 +6645,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="9">
-        <v>1.43089</v>
+        <v>1.53224</v>
       </c>
       <c r="E126" s="7">
-        <v>305.47</v>
+        <v>327.1</v>
       </c>
       <c r="F126" s="7">
         <v>333.51</v>
@@ -6665,10 +6665,10 @@
         <v>2</v>
       </c>
       <c r="D127" s="9">
-        <v>0.98999</v>
+        <v>0.64999</v>
       </c>
       <c r="E127" s="7">
-        <v>60.24</v>
+        <v>39.55</v>
       </c>
       <c r="F127" s="7">
         <v>40.16</v>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="D128" s="9"/>
       <c r="E128" s="11">
-        <v>2605.96</v>
+        <v>2744.55</v>
       </c>
       <c r="F128" s="11">
         <v>2791.21</v>
